--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>579.3305807903557</v>
+        <v>580.2174776783939</v>
       </c>
       <c r="E2" t="n">
-        <v>7982.238222729284</v>
+        <v>8073.688672236973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6747852833921331</v>
+        <v>0.6781918971866396</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018356734644871</v>
+        <v>0.5018318255656267</v>
       </c>
       <c r="H2" t="n">
-        <v>1.344633949064773</v>
+        <v>1.351432616738154</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.3495594947205</v>
+        <v>224.744741067709</v>
       </c>
       <c r="E3" t="n">
-        <v>4199.229721733128</v>
+        <v>4358.371797478761</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2635391523219901</v>
+        <v>0.2684627040045393</v>
       </c>
       <c r="G3" t="n">
-        <v>0.60267118921475</v>
+        <v>0.6026635284313715</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4372851349761189</v>
+        <v>0.4454603461790713</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908252465203097</v>
+        <v>0.8908232083285694</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069821734665721</v>
+        <v>1.06981389100768</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.1125532607994</v>
+        <v>38.42676230850138</v>
       </c>
       <c r="E4" t="n">
-        <v>1704.714143812593</v>
+        <v>1783.263058918352</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8524122692916574</v>
+        <v>0.8707091524898882</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117316311262477</v>
+        <v>1.117237496684573</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7629104316292495</v>
+        <v>0.7793411473153533</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715409145766978</v>
+        <v>0.4715285563156264</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049866287199</v>
+        <v>1.049772766562945</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.09562511169835</v>
+        <v>37.20015441032619</v>
       </c>
       <c r="E5" t="n">
-        <v>310.1123815642566</v>
+        <v>307.6438153573275</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3387940825012349</v>
+        <v>-0.3369054555592791</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5662803061149108</v>
+        <v>0.5662909456681654</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5982798251021749</v>
+        <v>-0.5949335021801648</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367833156210297</v>
+        <v>0.7367806724180713</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8313994073595108</v>
+        <v>0.8314184204307564</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.83045889596212</v>
+        <v>10.9643800509222</v>
       </c>
       <c r="E6" t="n">
-        <v>180.1381838041217</v>
+        <v>182.4223145203161</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3094949842753907</v>
+        <v>-0.2996551964421639</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7191399305176195</v>
+        <v>0.7192403256172414</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4303682373090084</v>
+        <v>-0.4166273577402716</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500838325593484</v>
+        <v>0.7499760919368029</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074884197660157</v>
+        <v>1.074888082201217</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.88050340247025</v>
+        <v>9.910792868998154</v>
       </c>
       <c r="E7" t="n">
-        <v>344.7136526762913</v>
+        <v>351.1731095810122</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3267761783946556</v>
+        <v>-0.3237378056332898</v>
       </c>
       <c r="G7" t="n">
-        <v>1.176821526408005</v>
+        <v>1.176810363551117</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2776769213187914</v>
+        <v>-0.2750976840961749</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7385616204334662</v>
+        <v>0.7385569974891402</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731951830973984</v>
+        <v>1.731937841404908</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.872851511863283</v>
+        <v>9.901313443402996</v>
       </c>
       <c r="E8" t="n">
-        <v>348.3483980541559</v>
+        <v>336.0940874483366</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5557240843272898</v>
+        <v>-0.5542455361729419</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8096190874954216</v>
+        <v>0.8096246902513292</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6864019054274489</v>
+        <v>-0.6845709411367992</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6835599321121067</v>
+        <v>0.6835595108720706</v>
       </c>
       <c r="N8" t="n">
-        <v>1.10279758444514</v>
+        <v>1.102812992448954</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.531326892345558</v>
+        <v>7.537580691127874</v>
       </c>
       <c r="E9" t="n">
-        <v>834.270555385167</v>
+        <v>839.0245639730322</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4759619112414506</v>
+        <v>0.4762041915872155</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833591265408581</v>
+        <v>0.4833587185757646</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9846962333113571</v>
+        <v>0.9851983077710272</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.678159687596863</v>
+        <v>0.6781547467455867</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531912567894352</v>
+        <v>0.6531909549848832</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.941024800684755</v>
+        <v>6.965115413525801</v>
       </c>
       <c r="E10" t="n">
-        <v>219.5262527157759</v>
+        <v>223.4693576954826</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2338243018645592</v>
+        <v>-0.2302755476998619</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653184565081637</v>
+        <v>0.9653099632050612</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2422250401285907</v>
+        <v>-0.238550886738278</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131624564667646</v>
+        <v>0.713157695541539</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371821331399999</v>
+        <v>1.371810622147522</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.757029411553039</v>
+        <v>6.76233951652539</v>
       </c>
       <c r="E11" t="n">
-        <v>443.6246527443215</v>
+        <v>112.6423691927884</v>
       </c>
       <c r="F11" t="n">
-        <v>1.029399860539063</v>
+        <v>-0.2577117503711984</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272284915274973</v>
+        <v>0.6630314667818615</v>
       </c>
       <c r="H11" t="n">
-        <v>1.244396041821833</v>
+        <v>-0.3886870582810303</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3268819295856837</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="J11" t="n">
         <v>265</v>
@@ -1030,45 +1030,45 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626729180621437</v>
+        <v>0.7881909900751489</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092353428364762</v>
+        <v>1.041375619540957</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.720678428084022</v>
+        <v>6.757583540167728</v>
       </c>
       <c r="E12" t="n">
-        <v>113.9793957942515</v>
+        <v>415.7487309414199</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2621183474843509</v>
+        <v>1.028184122520537</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6630186622149482</v>
+        <v>0.8272317064766811</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3953408288820883</v>
+        <v>1.242921559305005</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4207389749702026</v>
+        <v>0.3268819295856837</v>
       </c>
       <c r="J12" t="n">
         <v>265</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7882084770596228</v>
+        <v>0.6626550155065719</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041370627159161</v>
+        <v>1.092336538570423</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.672609912763014</v>
+        <v>4.679296334508988</v>
       </c>
       <c r="E13" t="n">
-        <v>100.9550068581665</v>
+        <v>101.9452689141695</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3872763178327064</v>
+        <v>-0.3866515524650511</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8571843260757704</v>
+        <v>0.8571834144735836</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4518005125054904</v>
+        <v>-0.4510721345471936</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7601393638179975</v>
+        <v>0.7601401247534031</v>
       </c>
       <c r="N13" t="n">
-        <v>1.298392248202946</v>
+        <v>1.298402122822894</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.659212919424029</v>
+        <v>4.674263422358832</v>
       </c>
       <c r="E14" t="n">
-        <v>161.9243887229294</v>
+        <v>162.7190768995887</v>
       </c>
       <c r="F14" t="n">
-        <v>1.746862937584062</v>
+        <v>1.759508608774359</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8655688671043851</v>
+        <v>0.8655601840137873</v>
       </c>
       <c r="H14" t="n">
-        <v>2.018167478028522</v>
+        <v>2.032797535366221</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021195772529391</v>
+        <v>0.6021125278518454</v>
       </c>
       <c r="N14" t="n">
-        <v>1.038539083413884</v>
+        <v>1.038524469461523</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.237198643205192</v>
+        <v>4.265752063063784</v>
       </c>
       <c r="E15" t="n">
-        <v>388.8213974165096</v>
+        <v>386.6945318122105</v>
       </c>
       <c r="F15" t="n">
-        <v>0.004736257420462797</v>
+        <v>0.01299545632522814</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7965071859646448</v>
+        <v>0.7965323364307484</v>
       </c>
       <c r="H15" t="n">
-        <v>0.005946283353020533</v>
+        <v>0.01631503924054184</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7167016808706447</v>
+        <v>0.7166774414727783</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137539774853821</v>
+        <v>1.137545942368436</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.224224892400128</v>
+        <v>4.237105070564589</v>
       </c>
       <c r="E16" t="n">
-        <v>296.7588731486368</v>
+        <v>305.20115289003</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5808323609932724</v>
+        <v>0.5850427347243181</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624439931676018</v>
+        <v>0.9624332193272742</v>
       </c>
       <c r="H16" t="n">
-        <v>0.603497310094516</v>
+        <v>0.6078787836658982</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5130268690729749</v>
+        <v>0.5130148840214426</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9839069930284813</v>
+        <v>0.9838805377380284</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.477081259524122</v>
+        <v>3.493504934073965</v>
       </c>
       <c r="E17" t="n">
-        <v>83.12336266557062</v>
+        <v>84.62791611241303</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1805794001133382</v>
+        <v>-0.1730745140231396</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7565765364609124</v>
+        <v>0.7566757504341666</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2386796198545176</v>
+        <v>-0.2287300920160751</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.722587530431585</v>
+        <v>0.7225190581393514</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089386028078891</v>
+        <v>1.089433994953126</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.214960833686729</v>
+        <v>3.22213399361664</v>
       </c>
       <c r="E18" t="n">
-        <v>67.8700107648246</v>
+        <v>68.75021190793207</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4492672637985917</v>
+        <v>-0.4478780852932678</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519573253791138</v>
+        <v>0.7519707388275304</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5974637770462373</v>
+        <v>-0.5956057359247747</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641706185894994</v>
+        <v>0.7641779956501902</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145043536902975</v>
+        <v>1.145083796423483</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.962306720807197</v>
+        <v>2.988978888757534</v>
       </c>
       <c r="E19" t="n">
-        <v>93.7623733816458</v>
+        <v>94.34938319964225</v>
       </c>
       <c r="F19" t="n">
-        <v>0.117819820289401</v>
+        <v>0.127323071337119</v>
       </c>
       <c r="G19" t="n">
-        <v>0.485045486659036</v>
+        <v>0.4850769752705503</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2429046832307147</v>
+        <v>0.2624801378505027</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173721763126082</v>
+        <v>0.7173130410426296</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6933706684760516</v>
+        <v>0.6933638373351348</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.626205566439311</v>
+        <v>2.635382395646883</v>
       </c>
       <c r="E20" t="n">
-        <v>110.7048305055534</v>
+        <v>106.9660191544827</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3122062374515587</v>
+        <v>-0.3086152711468384</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7844987534560257</v>
+        <v>0.78451241162631</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3979690676067583</v>
+        <v>-0.3933848165729752</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320682855200844</v>
+        <v>0.7320591788594444</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144411782188373</v>
+        <v>1.144426245212489</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.2174776783939</v>
+        <v>580.8055106491609</v>
       </c>
       <c r="E2" t="n">
-        <v>8073.688672236973</v>
+        <v>8079.630549504601</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6781918971866396</v>
+        <v>0.6812942684431456</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018318255656267</v>
+        <v>0.5018334534239551</v>
       </c>
       <c r="H2" t="n">
-        <v>1.351432616738154</v>
+        <v>1.357610306357117</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.744741067709</v>
+        <v>225.0029032893285</v>
       </c>
       <c r="E3" t="n">
-        <v>4358.371797478761</v>
+        <v>4408.95344070198</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2684627040045393</v>
+        <v>0.2710340015181369</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026635284313715</v>
+        <v>0.6026666658272678</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4454603461790713</v>
+        <v>0.4497245606675364</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908232083285694</v>
+        <v>0.8908243450254674</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06981389100768</v>
+        <v>1.069817355123002</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.42676230850138</v>
+        <v>38.66775464194963</v>
       </c>
       <c r="E4" t="n">
-        <v>1783.263058918352</v>
+        <v>1814.313060570064</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8707091524898882</v>
+        <v>0.8890551971486533</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117237496684573</v>
+        <v>1.117219856637636</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7793411473153533</v>
+        <v>0.7957746112965957</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715285563156264</v>
+        <v>0.4715355023536144</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049772766562945</v>
+        <v>1.049768250292406</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.20015441032619</v>
+        <v>37.2438768045411</v>
       </c>
       <c r="E5" t="n">
-        <v>307.6438153573275</v>
+        <v>306.0434818900594</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3369054555592791</v>
+        <v>-0.3353934919844849</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5662909456681654</v>
+        <v>0.5663068854032624</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5949335021801648</v>
+        <v>-0.5922468905629745</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367806724180713</v>
+        <v>0.7367868218085086</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314184204307564</v>
+        <v>0.8314460652587244</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.9643800509222</v>
+        <v>11.07173443951698</v>
       </c>
       <c r="E6" t="n">
-        <v>182.4223145203161</v>
+        <v>192.3052743462028</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2996551964421639</v>
+        <v>-0.2869924329167138</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7192403256172414</v>
+        <v>0.7196629513966681</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4166273577402716</v>
+        <v>-0.3987872827963984</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499760919368029</v>
+        <v>0.7496410426048412</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074888082201217</v>
+        <v>1.075035714594556</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.910792868998154</v>
+        <v>9.968208908122126</v>
       </c>
       <c r="E7" t="n">
-        <v>351.1731095810122</v>
+        <v>356.3649856574507</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3237378056332898</v>
+        <v>-0.317268839592406</v>
       </c>
       <c r="G7" t="n">
-        <v>1.176810363551117</v>
+        <v>1.176827442993672</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2750976840961749</v>
+        <v>-0.269596737806625</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7385569974891402</v>
+        <v>0.7385576162147801</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731937841404908</v>
+        <v>1.731958810365057</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.901313443402996</v>
+        <v>9.941755039578251</v>
       </c>
       <c r="E8" t="n">
-        <v>336.0940874483366</v>
+        <v>332.7376904142301</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5542455361729419</v>
+        <v>-0.550848494417111</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8096246902513292</v>
+        <v>0.8096744387131716</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6845709411367992</v>
+        <v>-0.6803333143288842</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6835595108720706</v>
+        <v>0.6835476454256439</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102812992448954</v>
+        <v>1.102858034608059</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.537580691127874</v>
+        <v>7.55803953589788</v>
       </c>
       <c r="E9" t="n">
-        <v>839.0245639730322</v>
+        <v>839.2600357575969</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4762041915872155</v>
+        <v>0.4868753011408993</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833587185757646</v>
+        <v>0.4833802950311095</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9851983077710272</v>
+        <v>1.007230344607996</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6781547467455867</v>
+        <v>0.678146435789068</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531909549848832</v>
+        <v>0.653209988233055</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.965115413525801</v>
+        <v>6.991419752019068</v>
       </c>
       <c r="E10" t="n">
-        <v>223.4693576954826</v>
+        <v>223.2808589611627</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2302755476998619</v>
+        <v>-0.2231645840629187</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653099632050612</v>
+        <v>0.9653403780847349</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.238550886738278</v>
+        <v>-0.2311770947628692</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713157695541539</v>
+        <v>0.7131534756444829</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371810622147522</v>
+        <v>1.371841277447657</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.76233951652539</v>
+        <v>6.784403609291004</v>
       </c>
       <c r="E11" t="n">
-        <v>112.6423691927884</v>
+        <v>412.956367163937</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2577117503711984</v>
+        <v>1.047355148677342</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6630314667818615</v>
+        <v>0.8272170597716139</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3886870582810303</v>
+        <v>1.266118893832419</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4207389749702026</v>
+        <v>0.3268819295856837</v>
       </c>
       <c r="J11" t="n">
         <v>265</v>
@@ -1030,45 +1030,45 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7881909900751489</v>
+        <v>0.6626688828804205</v>
       </c>
       <c r="N11" t="n">
-        <v>1.041375619540957</v>
+        <v>1.092336513555185</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.757583540167728</v>
+        <v>6.487059586657553</v>
       </c>
       <c r="E12" t="n">
-        <v>415.7487309414199</v>
+        <v>111.8353338347149</v>
       </c>
       <c r="F12" t="n">
-        <v>1.028184122520537</v>
+        <v>-0.249838720050612</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8272317064766811</v>
+        <v>0.6631494763909145</v>
       </c>
       <c r="H12" t="n">
-        <v>1.242921559305005</v>
+        <v>-0.3767457095952477</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3268819295856837</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="J12" t="n">
         <v>265</v>
@@ -1084,45 +1084,45 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.6626550155065719</v>
+        <v>0.7881032219901835</v>
       </c>
       <c r="N12" t="n">
-        <v>1.092336538570423</v>
+        <v>1.041441608643134</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.679296334508988</v>
+        <v>4.72657554761939</v>
       </c>
       <c r="E13" t="n">
-        <v>101.9452689141695</v>
+        <v>163.8727158017097</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3866515524650511</v>
+        <v>1.81820110399584</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8571834144735836</v>
+        <v>0.8657479833875532</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4510721345471936</v>
+        <v>2.100150550604194</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4691011235955056</v>
+        <v>0.3000688231245698</v>
       </c>
       <c r="J13" t="n">
         <v>265</v>
@@ -1138,45 +1138,45 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7601401247534031</v>
+        <v>0.6020341248160784</v>
       </c>
       <c r="N13" t="n">
-        <v>1.298402122822894</v>
+        <v>1.038611168573662</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.674263422358832</v>
+        <v>4.687113708216585</v>
       </c>
       <c r="E14" t="n">
-        <v>162.7190768995887</v>
+        <v>102.6413826943192</v>
       </c>
       <c r="F14" t="n">
-        <v>1.759508608774359</v>
+        <v>-0.3841507477623464</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8655601840137873</v>
+        <v>0.8571884254440747</v>
       </c>
       <c r="H14" t="n">
-        <v>2.032797535366221</v>
+        <v>-0.4481520472740091</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3000688231245698</v>
+        <v>0.4691011235955056</v>
       </c>
       <c r="J14" t="n">
         <v>265</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021125278518454</v>
+        <v>0.7601419320985849</v>
       </c>
       <c r="N14" t="n">
-        <v>1.038524469461523</v>
+        <v>1.298408588434888</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.265752063063784</v>
+        <v>4.271314678507935</v>
       </c>
       <c r="E15" t="n">
-        <v>386.6945318122105</v>
+        <v>305.8847429961742</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01299545632522814</v>
+        <v>0.6033230739844826</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7965323364307484</v>
+        <v>0.9624471640836789</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01631503924054184</v>
+        <v>0.6268635791128242</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J15" t="n">
         <v>265</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166774414727783</v>
+        <v>0.5130207715894605</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137545942368436</v>
+        <v>0.9839028932078111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.237105070564589</v>
+        <v>4.270450961434441</v>
       </c>
       <c r="E16" t="n">
-        <v>305.20115289003</v>
+        <v>376.6462370373786</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5850427347243181</v>
+        <v>0.01722005559166107</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624332193272742</v>
+        <v>0.7965685735776964</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6078787836658982</v>
+        <v>0.02161779432788713</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J16" t="n">
         <v>265</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5130148840214426</v>
+        <v>0.7166790102793772</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9838805377380284</v>
+        <v>1.137596493490499</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.493504934073965</v>
+        <v>3.492617468890247</v>
       </c>
       <c r="E17" t="n">
-        <v>84.62791611241303</v>
+        <v>84.17393613997847</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1730745140231396</v>
+        <v>-0.1753279476288044</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7566757504341666</v>
+        <v>0.7566375865889738</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2287300920160751</v>
+        <v>-0.2317198494185399</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7225190581393514</v>
+        <v>0.722600985145426</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089433994953126</v>
+        <v>1.089499039445964</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.22213399361664</v>
+        <v>3.227127367671756</v>
       </c>
       <c r="E18" t="n">
-        <v>68.75021190793207</v>
+        <v>68.08866536379267</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4478780852932678</v>
+        <v>-0.4458334352345357</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519707388275304</v>
+        <v>0.7520015127110512</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5956057359247747</v>
+        <v>-0.5928624180917607</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641779956501902</v>
+        <v>0.7641791321716052</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145083796423483</v>
+        <v>1.145128646674302</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.988978888757534</v>
+        <v>3.001713665170832</v>
       </c>
       <c r="E19" t="n">
-        <v>94.34938319964225</v>
+        <v>94.92549284034224</v>
       </c>
       <c r="F19" t="n">
-        <v>0.127323071337119</v>
+        <v>0.134941515754567</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4850769752705503</v>
+        <v>0.4851787040101186</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2624801378505027</v>
+        <v>0.2781274500287069</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173130410426296</v>
+        <v>0.7172278825420918</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6933638373351348</v>
+        <v>0.6934246654092885</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.635382395646883</v>
+        <v>2.647845446633871</v>
       </c>
       <c r="E20" t="n">
-        <v>106.9660191544827</v>
+        <v>107.9386803008518</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3086152711468384</v>
+        <v>-0.3034764455360498</v>
       </c>
       <c r="G20" t="n">
-        <v>0.78451241162631</v>
+        <v>0.7845750200871737</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3933848165729752</v>
+        <v>-0.3868036042013301</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320591788594444</v>
+        <v>0.7320377240092637</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144426245212489</v>
+        <v>1.144480321310761</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.8055106491609</v>
+        <v>580.5568324006931</v>
       </c>
       <c r="E2" t="n">
-        <v>8079.630549504601</v>
+        <v>7947.458481457907</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6812942684431456</v>
+        <v>0.6800504970525392</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018334534239551</v>
+        <v>0.5018322137943395</v>
       </c>
       <c r="H2" t="n">
-        <v>1.357610306357117</v>
+        <v>1.355135199294394</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.0029032893285</v>
+        <v>224.8966438207705</v>
       </c>
       <c r="E3" t="n">
-        <v>4408.95344070198</v>
+        <v>4402.356672457002</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2710340015181369</v>
+        <v>0.2702671380905031</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026666658272678</v>
+        <v>0.6026652183308049</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4497245606675364</v>
+        <v>0.4484531873915985</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908243450254674</v>
+        <v>0.8908234707849977</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069817355123002</v>
+        <v>1.069816378377943</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.66775464194963</v>
+        <v>38.53696904458869</v>
       </c>
       <c r="E4" t="n">
-        <v>1814.313060570064</v>
+        <v>1910.601829337454</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8890551971486533</v>
+        <v>0.8770541540616019</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117219856637636</v>
+        <v>1.11722446729893</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7957746112965957</v>
+        <v>0.7850294902527705</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715355023536144</v>
+        <v>0.4715262357380428</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049768250292406</v>
+        <v>1.049754545561711</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.2438768045411</v>
+        <v>37.22509822807677</v>
       </c>
       <c r="E5" t="n">
-        <v>306.0434818900594</v>
+        <v>303.9670076772742</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3353934919844849</v>
+        <v>-0.3357715713191812</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663068854032624</v>
+        <v>0.5663022814912139</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5922468905629745</v>
+        <v>-0.5929193335315756</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367868218085086</v>
+        <v>0.7367810308231557</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314460652587244</v>
+        <v>0.8314348247193125</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.07173443951698</v>
+        <v>11.03004639837392</v>
       </c>
       <c r="E6" t="n">
-        <v>192.3052743462028</v>
+        <v>203.4742273747142</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2869924329167138</v>
+        <v>-0.2931771565789693</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7196629513966681</v>
+        <v>0.7194155605459849</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3987872827963984</v>
+        <v>-0.4075212890258709</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7496410426048412</v>
+        <v>0.7498388735893607</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075035714594556</v>
+        <v>1.074952421813907</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.968208908122126</v>
+        <v>9.978039478353582</v>
       </c>
       <c r="E7" t="n">
-        <v>356.3649856574507</v>
+        <v>364.73924096009</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.317268839592406</v>
+        <v>-0.3153629950512642</v>
       </c>
       <c r="G7" t="n">
-        <v>1.176827442993672</v>
+        <v>1.17684302626033</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.269596737806625</v>
+        <v>-0.2679737127332924</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7385576162147801</v>
+        <v>0.7385454447947321</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731958810365057</v>
+        <v>1.731957479794649</v>
       </c>
     </row>
     <row r="8">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.941755039578251</v>
+        <v>9.948913806205409</v>
       </c>
       <c r="E8" t="n">
-        <v>332.7376904142301</v>
+        <v>327.4863270117912</v>
       </c>
       <c r="F8" t="n">
         <v>-0.550848494417111</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6835476454256439</v>
+        <v>0.6835347008361177</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102858034608059</v>
+        <v>1.102839873622122</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.55803953589788</v>
+        <v>7.545417090372833</v>
       </c>
       <c r="E9" t="n">
-        <v>839.2600357575969</v>
+        <v>587.9651673402236</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4868753011408993</v>
+        <v>0.4800821582539367</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833802950311095</v>
+        <v>0.4833576211581168</v>
       </c>
       <c r="H9" t="n">
-        <v>1.007230344607996</v>
+        <v>0.9932235207208856</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.678146435789068</v>
+        <v>0.6781567407485144</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653209988233055</v>
+        <v>0.653190887253163</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.991419752019068</v>
+        <v>7.005088781792612</v>
       </c>
       <c r="E10" t="n">
-        <v>223.2808589611627</v>
+        <v>224.2748298317078</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2231645840629187</v>
+        <v>-0.2220251688387778</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653403780847349</v>
+        <v>0.9653511093567646</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2311770947628692</v>
+        <v>-0.2299942131798224</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131534756444829</v>
+        <v>0.7131391220457919</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371841277447657</v>
+        <v>1.3718323050396</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.784403609291004</v>
+        <v>6.795377600802601</v>
       </c>
       <c r="E11" t="n">
-        <v>412.956367163937</v>
+        <v>408.9141405328996</v>
       </c>
       <c r="F11" t="n">
-        <v>1.047355148677342</v>
+        <v>1.047659848783809</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272170597716139</v>
+        <v>0.8272174469545167</v>
       </c>
       <c r="H11" t="n">
-        <v>1.266118893832419</v>
+        <v>1.266486644643283</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626688828804205</v>
+        <v>0.6626666842094333</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092336513555185</v>
+        <v>1.092336098850347</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.487059586657553</v>
+        <v>6.518810292804087</v>
       </c>
       <c r="E12" t="n">
-        <v>111.8353338347149</v>
+        <v>112.9062622702306</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.249838720050612</v>
+        <v>-0.2430998734813077</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6631494763909145</v>
+        <v>0.6633466616740625</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3767457095952477</v>
+        <v>-0.3664748577580927</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7881032219901835</v>
+        <v>0.7878616132082191</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041441608643134</v>
+        <v>1.041434480722666</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.72657554761939</v>
+        <v>4.725617921308047</v>
       </c>
       <c r="E13" t="n">
-        <v>163.8727158017097</v>
+        <v>169.206628927122</v>
       </c>
       <c r="F13" t="n">
-        <v>1.81820110399584</v>
+        <v>1.802304919331435</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8657479833875532</v>
+        <v>0.8656602662740343</v>
       </c>
       <c r="H13" t="n">
-        <v>2.100150550604194</v>
+        <v>2.082000282961926</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6020341248160784</v>
+        <v>0.6020629688541995</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038611168573662</v>
+        <v>1.038558258329849</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.687113708216585</v>
+        <v>4.693667466090852</v>
       </c>
       <c r="E14" t="n">
-        <v>102.6413826943192</v>
+        <v>104.0768703884898</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3841507477623464</v>
+        <v>-0.3828993005931776</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571884254440747</v>
+        <v>0.8571961252945427</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4481520472740091</v>
+        <v>-0.4466880907349048</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601419320985849</v>
+        <v>0.7601353583849061</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298408588434888</v>
+        <v>1.298412230215959</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.271314678507935</v>
+        <v>4.260681557208481</v>
       </c>
       <c r="E15" t="n">
-        <v>305.8847429961742</v>
+        <v>372.2244592423762</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6033230739844826</v>
+        <v>0.01176418933770074</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9624471640836789</v>
+        <v>0.7965247463278974</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6268635791128242</v>
+        <v>0.0147693959188782</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J15" t="n">
         <v>265</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5130207715894605</v>
+        <v>0.7166968898251534</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9839028932078111</v>
+        <v>1.137565091817572</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.270450961434441</v>
+        <v>4.244282844373166</v>
       </c>
       <c r="E16" t="n">
-        <v>376.6462370373786</v>
+        <v>307.36145637905</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01722005559166107</v>
+        <v>0.596285379144837</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7965685735776964</v>
+        <v>0.9624301408191985</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02161779432788713</v>
+        <v>0.6195622454605303</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J16" t="n">
         <v>265</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7166790102793772</v>
+        <v>0.5130177430886528</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137596493490499</v>
+        <v>0.9838821126893721</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.492617468890247</v>
+        <v>3.489327349039558</v>
       </c>
       <c r="E17" t="n">
-        <v>84.17393613997847</v>
+        <v>83.16204422183087</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1753279476288044</v>
+        <v>-0.1758910427145922</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7566375865889738</v>
+        <v>0.756629170482997</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2317198494185399</v>
+        <v>-0.232466642281729</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.722600985145426</v>
+        <v>0.722591240260008</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089499039445964</v>
+        <v>1.089474919480302</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.227127367671756</v>
+        <v>3.227146786636283</v>
       </c>
       <c r="E18" t="n">
-        <v>68.08866536379267</v>
+        <v>67.26018800025081</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4458334352345357</v>
+        <v>-0.4463243400647249</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7520015127110512</v>
+        <v>0.7519929275212724</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5928624180917607</v>
+        <v>-0.5935219916707252</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641791321716052</v>
+        <v>0.7641735315253926</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145128646674302</v>
+        <v>1.14511000950121</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.001713665170832</v>
+        <v>3.000493301570806</v>
       </c>
       <c r="E19" t="n">
-        <v>94.92549284034224</v>
+        <v>95.05934693621354</v>
       </c>
       <c r="F19" t="n">
         <v>0.134941515754567</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7172278825420918</v>
+        <v>0.7172000944604069</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934246654092885</v>
+        <v>0.6933995123892942</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.647845446633871</v>
+        <v>2.639995579219856</v>
       </c>
       <c r="E20" t="n">
-        <v>107.9386803008518</v>
+        <v>108.1398844563629</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3034764455360498</v>
+        <v>-0.3075883403604991</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845750200871737</v>
+        <v>0.7845208773529617</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3868036042013301</v>
+        <v>-0.3920715805528689</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320377240092637</v>
+        <v>0.732063929002574</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144480321310761</v>
+        <v>1.144445135391253</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.5568324006931</v>
+        <v>580.413039073943</v>
       </c>
       <c r="E2" t="n">
-        <v>7947.458481457907</v>
+        <v>7920.849796286861</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6800504970525392</v>
+        <v>0.6795127699562968</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018322137943395</v>
+        <v>0.501831921060693</v>
       </c>
       <c r="H2" t="n">
-        <v>1.355135199294394</v>
+        <v>1.354064461503466</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.8966438207705</v>
+        <v>224.8189351221915</v>
       </c>
       <c r="E3" t="n">
-        <v>4402.356672457002</v>
+        <v>4380.273304117791</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2702671380905031</v>
+        <v>0.2693040625051522</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026652183308049</v>
+        <v>0.6026640165754006</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4484531873915985</v>
+        <v>0.4468560509642754</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908234707849977</v>
+        <v>0.8908236052271417</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069816378377943</v>
+        <v>1.069815030601527</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.53696904458869</v>
+        <v>38.80597296492457</v>
       </c>
       <c r="E4" t="n">
-        <v>1910.601829337454</v>
+        <v>1822.046877483848</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8770541540616019</v>
+        <v>0.8982465873004597</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11722446729893</v>
+        <v>1.117233978361335</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7850294902527705</v>
+        <v>0.8039914688397969</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715262357380428</v>
+        <v>0.4715311635854105</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049754545561711</v>
+        <v>1.049775065524706</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.22509822807677</v>
+        <v>37.22357193178944</v>
       </c>
       <c r="E5" t="n">
-        <v>303.9670076772742</v>
+        <v>301.7081406802943</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3357715713191812</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367810308231557</v>
+        <v>0.7367765392583056</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314348247193125</v>
+        <v>0.8314302411239346</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.03004639837392</v>
+        <v>11.02988042685669</v>
       </c>
       <c r="E6" t="n">
-        <v>203.4742273747142</v>
+        <v>194.6526914648265</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2931771565789693</v>
+        <v>-0.2937948163986482</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7194155605459849</v>
+        <v>0.7193951398264802</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4075212890258709</v>
+        <v>-0.408391439049077</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7498388735893607</v>
+        <v>0.7498447768379952</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074952421813907</v>
+        <v>1.074930998692458</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.978039478353582</v>
+        <v>9.967503751428561</v>
       </c>
       <c r="E7" t="n">
-        <v>364.73924096009</v>
+        <v>354.0703712196659</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3153629950512642</v>
+        <v>-0.318411647330507</v>
       </c>
       <c r="G7" t="n">
-        <v>1.17684302626033</v>
+        <v>1.176820396959587</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2679737127332924</v>
+        <v>-0.2705694498099708</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7385454447947321</v>
+        <v>0.7385533736372214</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731957479794649</v>
+        <v>1.73194378010577</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.948913806205409</v>
+        <v>9.965535289556652</v>
       </c>
       <c r="E8" t="n">
-        <v>327.4863270117912</v>
+        <v>325.1530358983604</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.550848494417111</v>
+        <v>-0.5498890780595872</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8096744387131716</v>
+        <v>0.8096977607324263</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6803333143288842</v>
+        <v>-0.6791288116718706</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6835347008361177</v>
+        <v>0.6835108992382637</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102839873622122</v>
+        <v>1.102833879876874</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.545417090372833</v>
+        <v>7.518377125259416</v>
       </c>
       <c r="E9" t="n">
-        <v>587.9651673402236</v>
+        <v>477.5489800223225</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4800821582539367</v>
+        <v>0.4725711308007232</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833576211581168</v>
+        <v>0.4833690302456716</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9932235207208856</v>
+        <v>0.9776611682393876</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6781567407485144</v>
+        <v>0.6781329564010149</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653190887253163</v>
+        <v>0.6531837767919616</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.005088781792612</v>
+        <v>7.009996484947451</v>
       </c>
       <c r="E10" t="n">
-        <v>224.2748298317078</v>
+        <v>221.158694985603</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2220251688387778</v>
+        <v>-0.2225949336426579</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653511093567646</v>
+        <v>0.9653455414944336</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2299942131798224</v>
+        <v>-0.2305857582333294</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131391220457919</v>
+        <v>0.7131381327196319</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3718323050396</v>
+        <v>1.371823289828752</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.795377600802601</v>
+        <v>6.791504282799622</v>
       </c>
       <c r="E11" t="n">
-        <v>408.9141405328996</v>
+        <v>400.8200169101897</v>
       </c>
       <c r="F11" t="n">
-        <v>1.047659848783809</v>
+        <v>1.044917995139248</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272174469545167</v>
+        <v>0.8272146594356714</v>
       </c>
       <c r="H11" t="n">
-        <v>1.266486644643283</v>
+        <v>1.263176351168745</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626666842094333</v>
+        <v>0.6626664951256042</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092336098850347</v>
+        <v>1.092332743453479</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.518810292804087</v>
+        <v>6.579067084923997</v>
       </c>
       <c r="E12" t="n">
-        <v>112.9062622702306</v>
+        <v>114.8845801136344</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2430998734813077</v>
+        <v>-0.2359580340564639</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6633466616740625</v>
+        <v>0.6636516136268149</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3664748577580927</v>
+        <v>-0.3555450317779955</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7878616132082191</v>
+        <v>0.787492905752892</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041434480722666</v>
+        <v>1.041426253869907</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.725617921308047</v>
+        <v>4.724678682339449</v>
       </c>
       <c r="E13" t="n">
-        <v>169.206628927122</v>
+        <v>164.592240399506</v>
       </c>
       <c r="F13" t="n">
-        <v>1.802304919331435</v>
+        <v>1.795953348496985</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8656602662740343</v>
+        <v>0.8656328441004383</v>
       </c>
       <c r="H13" t="n">
-        <v>2.082000282961926</v>
+        <v>2.074728749881634</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6020629688541995</v>
+        <v>0.6020723488584004</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038558258329849</v>
+        <v>1.0385421449376</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.693667466090852</v>
+        <v>4.694202447287883</v>
       </c>
       <c r="E14" t="n">
-        <v>104.0768703884898</v>
+        <v>103.5262964243154</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3828993005931776</v>
+        <v>-0.3835251111792812</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571961252945427</v>
+        <v>0.8571918425125286</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4466880907349048</v>
+        <v>-0.4474203931469118</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601353583849061</v>
+        <v>0.7601358264040072</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298412230215959</v>
+        <v>1.298407299834222</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.260681557208481</v>
+        <v>4.257380446221386</v>
       </c>
       <c r="E15" t="n">
-        <v>372.2244592423762</v>
+        <v>368.010512791422</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01176418933770074</v>
+        <v>0.01053333273150314</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7965247463278974</v>
+        <v>0.7965185016863296</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0147693959188782</v>
+        <v>0.01322421602160245</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166968898251534</v>
+        <v>0.7166982619838428</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137565091817572</v>
+        <v>1.137559014958567</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.244282844373166</v>
+        <v>4.252687314151314</v>
       </c>
       <c r="E16" t="n">
-        <v>307.36145637905</v>
+        <v>301.5023944023873</v>
       </c>
       <c r="F16" t="n">
-        <v>0.596285379144837</v>
+        <v>0.5934726776058894</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624301408191985</v>
+        <v>0.962427412446229</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6195622454605303</v>
+        <v>0.6166414941335089</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5130177430886528</v>
+        <v>0.5130168330267241</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9838821126893721</v>
+        <v>0.9838781520866122</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.489327349039558</v>
+        <v>3.483925316045871</v>
       </c>
       <c r="E17" t="n">
-        <v>83.16204422183087</v>
+        <v>82.33577631583357</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1758910427145922</v>
+        <v>-0.1792673988716788</v>
       </c>
       <c r="G17" t="n">
-        <v>0.756629170482997</v>
+        <v>0.7565881237570992</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.232466642281729</v>
+        <v>-0.2369418620813986</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.722591240260008</v>
+        <v>0.7226195317815755</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089474919480302</v>
+        <v>1.089459105322105</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.227146786636283</v>
+        <v>3.225001282833483</v>
       </c>
       <c r="E18" t="n">
-        <v>67.26018800025081</v>
+        <v>66.01062780717054</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4463243400647249</v>
+        <v>-0.4485319357905072</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519929275212724</v>
+        <v>0.7519636689918223</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5935219916707252</v>
+        <v>-0.5964808597626344</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641735315253926</v>
+        <v>0.7641941802170028</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14511000950121</v>
+        <v>1.145097064299096</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.000493301570806</v>
+        <v>3.006399118288988</v>
       </c>
       <c r="E19" t="n">
-        <v>95.05934693621354</v>
+        <v>94.50295616795739</v>
       </c>
       <c r="F19" t="n">
-        <v>0.134941515754567</v>
+        <v>0.13398844169099</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4851787040101186</v>
+        <v>0.4851622686043967</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2781274500287069</v>
+        <v>0.2761724279928386</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7172000944604069</v>
+        <v>0.717210831113363</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6933995123892942</v>
+        <v>0.6933868079876898</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.639995579219856</v>
+        <v>2.640414295683701</v>
       </c>
       <c r="E20" t="n">
-        <v>108.1398844563629</v>
+        <v>107.2395926148714</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3075883403604991</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732063929002574</v>
+        <v>0.7320602902715584</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144445135391253</v>
+        <v>1.1444401145013</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.413039073943</v>
+        <v>582.5322844591568</v>
       </c>
       <c r="E2" t="n">
-        <v>7920.849796286861</v>
+        <v>8098.655208898979</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6795127699562968</v>
+        <v>0.6883416350714164</v>
       </c>
       <c r="G2" t="n">
-        <v>0.501831921060693</v>
+        <v>0.5018552896815355</v>
       </c>
       <c r="H2" t="n">
-        <v>1.354064461503466</v>
+        <v>1.371593862263005</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.8189351221915</v>
+        <v>225.801977527086</v>
       </c>
       <c r="E3" t="n">
-        <v>4380.273304117791</v>
+        <v>4479.052222083207</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2693040625051522</v>
+        <v>0.2768457024587718</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026640165754006</v>
+        <v>0.6026917505642327</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4468560509642754</v>
+        <v>0.4593487503347976</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908236052271417</v>
+        <v>0.8908338515979665</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069815030601527</v>
+        <v>1.069826749902662</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.80597296492457</v>
+        <v>39.13080213500397</v>
       </c>
       <c r="E4" t="n">
-        <v>1822.046877483848</v>
+        <v>1886.05616381457</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8982465873004597</v>
+        <v>0.9134745136544424</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117233978361335</v>
+        <v>1.117290895913872</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8039914688397969</v>
+        <v>0.81757984155709</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715311635854105</v>
+        <v>0.4715911832759099</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049775065524706</v>
+        <v>1.049913284767377</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.22357193178944</v>
+        <v>37.30764955625762</v>
       </c>
       <c r="E5" t="n">
-        <v>301.7081406802943</v>
+        <v>301.6470977035536</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3357715713191812</v>
+        <v>-0.3338805854433086</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663022814912139</v>
+        <v>0.5663294272989022</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5929193335315756</v>
+        <v>-0.5895518921482605</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367765392583056</v>
+        <v>0.7368289901663687</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314302411239346</v>
+        <v>0.8314905682929998</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.02988042685669</v>
+        <v>11.06766310441181</v>
       </c>
       <c r="E6" t="n">
-        <v>194.6526914648265</v>
+        <v>197.2249394137018</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2937948163986482</v>
+        <v>-0.2900866399888797</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7193951398264802</v>
+        <v>0.7195294434324139</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.408391439049077</v>
+        <v>-0.4031615976756452</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,45 +760,45 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7498447768379952</v>
+        <v>0.7499669969228414</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074930998692458</v>
+        <v>1.07525684591469</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>Dogecoin</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.967503751428561</v>
+        <v>10.06817301996223</v>
       </c>
       <c r="E7" t="n">
-        <v>354.0703712196659</v>
+        <v>332.6212168593628</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.318411647330507</v>
+        <v>-0.544470989479259</v>
       </c>
       <c r="G7" t="n">
-        <v>1.176820396959587</v>
+        <v>0.8099056392058179</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2705694498099708</v>
+        <v>-0.6722647221139978</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7387533875338753</v>
+        <v>0.5751178664414889</v>
       </c>
       <c r="J7" t="n">
         <v>265</v>
@@ -814,45 +814,45 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7385533736372214</v>
+        <v>0.6835499782427105</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73194378010577</v>
+        <v>1.103128717461746</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dogecoin</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.965535289556652</v>
+        <v>10.04961654157475</v>
       </c>
       <c r="E8" t="n">
-        <v>325.1530358983604</v>
+        <v>361.0078610731462</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5498890780595872</v>
+        <v>-0.3111650193265807</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8096977607324263</v>
+        <v>1.1768942039488</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6791288116718706</v>
+        <v>-0.2643950648091711</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5751178664414889</v>
+        <v>0.7387533875338753</v>
       </c>
       <c r="J8" t="n">
         <v>265</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6835108992382637</v>
+        <v>0.7385854608471384</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102833879876874</v>
+        <v>1.732046998136545</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.518377125259416</v>
+        <v>7.575593116110295</v>
       </c>
       <c r="E9" t="n">
-        <v>477.5489800223225</v>
+        <v>453.3984118913561</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4725711308007232</v>
+        <v>0.4873608516210159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833690302456716</v>
+        <v>0.4833831122940671</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9776611682393876</v>
+        <v>1.008228957995804</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6781329564010149</v>
+        <v>0.6781883391406915</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531837767919616</v>
+        <v>0.6532257342617649</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.009996484947451</v>
+        <v>7.049475286303903</v>
       </c>
       <c r="E10" t="n">
-        <v>221.158694985603</v>
+        <v>223.5880906475487</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2225949336426579</v>
+        <v>-0.2158929833019441</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653455414944336</v>
+        <v>0.9654365053775235</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2305857582333294</v>
+        <v>-0.2236221461477899</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131381327196319</v>
+        <v>0.713187595638908</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371823289828752</v>
+        <v>1.371983825156359</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.791504282799622</v>
+        <v>6.821813207855182</v>
       </c>
       <c r="E11" t="n">
-        <v>400.8200169101897</v>
+        <v>394.755490904849</v>
       </c>
       <c r="F11" t="n">
-        <v>1.044917995139248</v>
+        <v>1.057416806766676</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272146594356714</v>
+        <v>0.8272400610857716</v>
       </c>
       <c r="H11" t="n">
-        <v>1.263176351168745</v>
+        <v>1.278246613659876</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626664951256042</v>
+        <v>0.6626916473488241</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092332743453479</v>
+        <v>1.092356880768854</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.579067084923997</v>
+        <v>6.577004347526367</v>
       </c>
       <c r="E12" t="n">
-        <v>114.8845801136344</v>
+        <v>115.7023110657191</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2359580340564639</v>
+        <v>-0.2367310102194866</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6636516136268149</v>
+        <v>0.6636138680612684</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3555450317779955</v>
+        <v>-0.3567300528409547</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.787492905752892</v>
+        <v>0.7878759839707848</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041426253869907</v>
+        <v>1.041825083894632</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.724678682339449</v>
+        <v>4.755112807029098</v>
       </c>
       <c r="E13" t="n">
-        <v>164.592240399506</v>
+        <v>167.8193801739946</v>
       </c>
       <c r="F13" t="n">
-        <v>1.795953348496985</v>
+        <v>1.824566470310173</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8656328441004383</v>
+        <v>0.865790733506997</v>
       </c>
       <c r="H13" t="n">
-        <v>2.074728749881634</v>
+        <v>2.107398935675289</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6020723488584004</v>
+        <v>0.6021475270384373</v>
       </c>
       <c r="N13" t="n">
-        <v>1.0385421449376</v>
+        <v>1.038812900517314</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.694202447287883</v>
+        <v>4.722195525131305</v>
       </c>
       <c r="E14" t="n">
-        <v>103.5262964243154</v>
+        <v>104.3835168528551</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3835251111792812</v>
+        <v>-0.3772591883157193</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571918425125286</v>
+        <v>0.857273624436548</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4474203931469118</v>
+        <v>-0.4400685820279106</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601358264040072</v>
+        <v>0.7601648960711007</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298407299834222</v>
+        <v>1.298520368367218</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.257380446221386</v>
+        <v>4.311894401985453</v>
       </c>
       <c r="E15" t="n">
-        <v>368.010512791422</v>
+        <v>380.5423469005464</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01053333273150314</v>
+        <v>0.02797921769882605</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7965185016863296</v>
+        <v>0.7967318426758291</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01322421602160245</v>
+        <v>0.0351174839515108</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166982619838428</v>
+        <v>0.7166987090270514</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137559014958567</v>
+        <v>1.137811426574508</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.252687314151314</v>
+        <v>4.28578727910009</v>
       </c>
       <c r="E16" t="n">
-        <v>301.5023944023873</v>
+        <v>306.1253877314151</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5934726776058894</v>
+        <v>0.6075497593152561</v>
       </c>
       <c r="G16" t="n">
-        <v>0.962427412446229</v>
+        <v>0.962464373669137</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6166414941335089</v>
+        <v>0.6312438942535981</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5130168330267241</v>
+        <v>0.5130578689608392</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9838781520866122</v>
+        <v>0.9839488208219723</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.483925316045871</v>
+        <v>3.519284555618283</v>
       </c>
       <c r="E17" t="n">
-        <v>82.33577631583357</v>
+        <v>82.26397664792057</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1792673988716788</v>
+        <v>-0.1642323740002859</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7565881237570992</v>
+        <v>0.7568945203989875</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2369418620813986</v>
+        <v>-0.2169818509370537</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7226195317815755</v>
+        <v>0.7225759614242626</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089459105322105</v>
+        <v>1.089783842113355</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.225001282833483</v>
+        <v>3.236090264954348</v>
       </c>
       <c r="E18" t="n">
-        <v>66.01062780717054</v>
+        <v>64.85289552786799</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4485319357905072</v>
+        <v>-0.44468752727438</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519636689918223</v>
+        <v>0.7520244906424829</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5964808597626344</v>
+        <v>-0.5913205391681682</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641941802170028</v>
+        <v>0.7642293411912663</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145097064299096</v>
+        <v>1.145189047241296</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.006399118288988</v>
+        <v>3.018276246458397</v>
       </c>
       <c r="E19" t="n">
-        <v>94.50295616795739</v>
+        <v>94.87618251336967</v>
       </c>
       <c r="F19" t="n">
-        <v>0.13398844169099</v>
+        <v>0.1406645630379924</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4851622686043967</v>
+        <v>0.4852996219144791</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2761724279928386</v>
+        <v>0.2898509635822067</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.717210831113363</v>
+        <v>0.7172712859626416</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6933868079876898</v>
+        <v>0.6936092755118159</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.640414295683701</v>
+        <v>2.654915455138971</v>
       </c>
       <c r="E20" t="n">
-        <v>107.2395926148714</v>
+        <v>107.8896411903137</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3075883403604991</v>
+        <v>-0.3024474303049676</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845208773529617</v>
+        <v>0.7845936252028315</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3920715805528689</v>
+        <v>-0.3854829055318663</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320602902715584</v>
+        <v>0.7321028751138833</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1444401145013</v>
+        <v>1.144559518684199</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>582.5322844591568</v>
+        <v>581.3728325665625</v>
       </c>
       <c r="E2" t="n">
-        <v>8098.655208898979</v>
+        <v>8216.070082975119</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6883416350714164</v>
+        <v>0.6824778289227535</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018552896815355</v>
+        <v>0.501835362044304</v>
       </c>
       <c r="H2" t="n">
-        <v>1.371593862263005</v>
+        <v>1.359963606674855</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.801977527086</v>
+        <v>225.2466071976299</v>
       </c>
       <c r="E3" t="n">
-        <v>4479.052222083207</v>
+        <v>4515.821094755268</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2768457024587718</v>
+        <v>0.272137759176448</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026917505642327</v>
+        <v>0.6026695122781273</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4593487503347976</v>
+        <v>0.4515538842304314</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908338515979665</v>
+        <v>0.8908252543304751</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069826749902662</v>
+        <v>1.069819431148394</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.13080213500397</v>
+        <v>38.94061004428601</v>
       </c>
       <c r="E4" t="n">
-        <v>1886.05616381457</v>
+        <v>1919.029652185935</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9134745136544424</v>
+        <v>0.9021389293761937</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117290895913872</v>
+        <v>1.117244557009525</v>
       </c>
       <c r="H4" t="n">
-        <v>0.81757984155709</v>
+        <v>0.807467732750389</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715911832759099</v>
+        <v>0.47154510513278</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049913284767377</v>
+        <v>1.049808845570296</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.30764955625762</v>
+        <v>37.26002693423533</v>
       </c>
       <c r="E5" t="n">
-        <v>301.6470977035536</v>
+        <v>301.8053918010255</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3338805854433086</v>
+        <v>-0.3350153537144025</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663294272989022</v>
+        <v>0.5663119019514719</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5895518921482605</v>
+        <v>-0.5915739234156349</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7368289901663687</v>
+        <v>0.7367925727469496</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314905682929998</v>
+        <v>0.8314567580815599</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.06766310441181</v>
+        <v>11.03999445693194</v>
       </c>
       <c r="E6" t="n">
-        <v>197.2249394137018</v>
+        <v>197.6351416381821</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2900866399888797</v>
+        <v>-0.2937948163986482</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7195294434324139</v>
+        <v>0.7193951398264802</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4031615976756452</v>
+        <v>-0.408391439049077</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499669969228414</v>
+        <v>0.7499190725743067</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07525684591469</v>
+        <v>1.075030133140576</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.06817301996223</v>
+        <v>10.07644961273263</v>
       </c>
       <c r="E7" t="n">
-        <v>332.6212168593628</v>
+        <v>329.9053598820541</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.544470989479259</v>
+        <v>-0.5439457167458218</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8099056392058179</v>
+        <v>0.8099326438358679</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6722647221139978</v>
+        <v>-0.6715937687974605</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6835499782427105</v>
+        <v>0.6834021963950355</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103128717461746</v>
+        <v>1.102970793996386</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.04961654157475</v>
+        <v>10.00098398617986</v>
       </c>
       <c r="E8" t="n">
-        <v>361.0078610731462</v>
+        <v>367.0322571644879</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3111650193265807</v>
+        <v>-0.3165066764491546</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1768942039488</v>
+        <v>1.17683310032578</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2643950648091711</v>
+        <v>-0.2689478026761286</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385854608471384</v>
+        <v>0.7385609214804517</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732046998136545</v>
+        <v>1.731968300250176</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.575593116110295</v>
+        <v>7.594138694668697</v>
       </c>
       <c r="E9" t="n">
-        <v>453.3984118913561</v>
+        <v>430.0990192886155</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4873608516210159</v>
+        <v>0.4934338950305639</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833831122940671</v>
+        <v>0.4834318000993333</v>
       </c>
       <c r="H9" t="n">
-        <v>1.008228957995804</v>
+        <v>1.020689774502164</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6781883391406915</v>
+        <v>0.6781127413256617</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532257342617649</v>
+        <v>0.6532446455624958</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.049475286303903</v>
+        <v>7.020266249196662</v>
       </c>
       <c r="E10" t="n">
-        <v>223.5880906475487</v>
+        <v>223.3078962948142</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2158929833019441</v>
+        <v>-0.2211703072465186</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9654365053775235</v>
+        <v>0.9653602194834987</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2236221461477899</v>
+        <v>-0.2291065063410759</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713187595638908</v>
+        <v>0.7131541432570925</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371983825156359</v>
+        <v>1.371865540634129</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.821813207855182</v>
+        <v>6.803548172720651</v>
       </c>
       <c r="E11" t="n">
-        <v>394.755490904849</v>
+        <v>387.9128299764526</v>
       </c>
       <c r="F11" t="n">
-        <v>1.057416806766676</v>
+        <v>1.045831834513146</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272400610857716</v>
+        <v>0.8272154143264634</v>
       </c>
       <c r="H11" t="n">
-        <v>1.278246613659876</v>
+        <v>1.26427991596927</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626916473488241</v>
+        <v>0.6626683315437657</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092356880768854</v>
+        <v>1.092329277486443</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.577004347526367</v>
+        <v>6.516366543778159</v>
       </c>
       <c r="E12" t="n">
-        <v>115.7023110657191</v>
+        <v>117.2780571548445</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2367310102194866</v>
+        <v>-0.2467601533339628</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6636138680612684</v>
+        <v>0.6632286002128271</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3567300528409547</v>
+        <v>-0.3720589752232919</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7878759839707848</v>
+        <v>0.7880499464649441</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041825083894632</v>
+        <v>1.041491497854222</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.755112807029098</v>
+        <v>4.731814778988794</v>
       </c>
       <c r="E13" t="n">
-        <v>167.8193801739946</v>
+        <v>168.6172372818121</v>
       </c>
       <c r="F13" t="n">
-        <v>1.824566470310173</v>
+        <v>1.800716656470249</v>
       </c>
       <c r="G13" t="n">
-        <v>0.865790733506997</v>
+        <v>0.865653000082805</v>
       </c>
       <c r="H13" t="n">
-        <v>2.107398935675289</v>
+        <v>2.080183002078199</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6021475270384373</v>
+        <v>0.6020992391484006</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038812900517314</v>
+        <v>1.038605590871798</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.722195525131305</v>
+        <v>4.705739491430234</v>
       </c>
       <c r="E14" t="n">
-        <v>104.3835168528551</v>
+        <v>105.5515071189613</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3772591883157193</v>
+        <v>-0.3828993005931776</v>
       </c>
       <c r="G14" t="n">
-        <v>0.857273624436548</v>
+        <v>0.8571961252945427</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4400685820279106</v>
+        <v>-0.4466880907349048</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601648960711007</v>
+        <v>0.7601439547177179</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298520368367218</v>
+        <v>1.298418768250478</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.311894401985453</v>
+        <v>4.294011935449567</v>
       </c>
       <c r="E15" t="n">
-        <v>380.5423469005464</v>
+        <v>380.4663291634154</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02797921769882605</v>
+        <v>0.02268395081137942</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7967318426758291</v>
+        <v>0.7966387837812149</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0351174839515108</v>
+        <v>0.02847457501844303</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166987090270514</v>
+        <v>0.7166497378320236</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137811426574508</v>
+        <v>1.137645966633231</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.28578727910009</v>
+        <v>4.242503047439931</v>
       </c>
       <c r="E16" t="n">
-        <v>306.1253877314151</v>
+        <v>307.3204786773634</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6075497593152561</v>
+        <v>0.5850427347243181</v>
       </c>
       <c r="G16" t="n">
-        <v>0.962464373669137</v>
+        <v>0.9624332193272742</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6312438942535981</v>
+        <v>0.6078787836658982</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5130578689608392</v>
+        <v>0.5129956307516359</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9839488208219723</v>
+        <v>0.9838366798104087</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.519284555618283</v>
+        <v>3.534510609987949</v>
       </c>
       <c r="E17" t="n">
-        <v>82.26397664792057</v>
+        <v>85.30924386340286</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1642323740002859</v>
+        <v>-0.1646091597727685</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7568945203989875</v>
+        <v>0.7568829627742998</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2169818509370537</v>
+        <v>-0.2174829767199482</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7225759614242626</v>
+        <v>0.7224371190834119</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089783842113355</v>
+        <v>1.08960106932781</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.236090264954348</v>
+        <v>3.227535087566374</v>
       </c>
       <c r="E18" t="n">
-        <v>64.85289552786799</v>
+        <v>64.9181251792178</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.44468752727438</v>
+        <v>-0.4473057920240953</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7520244906424829</v>
+        <v>0.7519780297723208</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5913205391681682</v>
+        <v>-0.5948389105989277</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642293411912663</v>
+        <v>0.7642028131410282</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145189047241296</v>
+        <v>1.145124017230021</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.018276246458397</v>
+        <v>3.023847694411135</v>
       </c>
       <c r="E19" t="n">
-        <v>94.87618251336967</v>
+        <v>95.52510961261662</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1406645630379924</v>
+        <v>0.1463954880749849</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4852996219144791</v>
+        <v>0.4854587557719611</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2898509635822067</v>
+        <v>0.3015611240592241</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7172712859626416</v>
+        <v>0.7169067913813864</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6936092755118159</v>
+        <v>0.6935116679118188</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.654915455138971</v>
+        <v>2.646610757738849</v>
       </c>
       <c r="E20" t="n">
-        <v>107.8896411903137</v>
+        <v>108.2356691004291</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3024474303049676</v>
+        <v>-0.3060471615546191</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845936252028315</v>
+        <v>0.7845373785531247</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3854829055318663</v>
+        <v>-0.3900988912969877</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321028751138833</v>
+        <v>0.7320714283171744</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144559518684199</v>
+        <v>1.144473751203871</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.3728325665625</v>
+        <v>581.3699832038172</v>
       </c>
       <c r="E2" t="n">
-        <v>8216.070082975119</v>
+        <v>8203.274291422355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6824778289227535</v>
+        <v>0.6831522581400162</v>
       </c>
       <c r="G2" t="n">
-        <v>0.501835362044304</v>
+        <v>0.5018367674429044</v>
       </c>
       <c r="H2" t="n">
-        <v>1.359963606674855</v>
+        <v>1.361303719575989</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.2466071976299</v>
+        <v>225.2884890107727</v>
       </c>
       <c r="E3" t="n">
-        <v>4515.821094755268</v>
+        <v>4529.744310209435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.272137759176448</v>
+        <v>0.2730265683272335</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026695122781273</v>
+        <v>0.6026724585137303</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4515538842304314</v>
+        <v>0.4530264565275688</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908252543304751</v>
+        <v>0.8908258375190344</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069819431148394</v>
+        <v>1.069822365429276</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.94061004428601</v>
+        <v>38.91958407696455</v>
       </c>
       <c r="E4" t="n">
-        <v>1919.029652185935</v>
+        <v>1927.852489115342</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9021389293761937</v>
+        <v>0.9003694121889099</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117244557009525</v>
+        <v>1.117239409174175</v>
       </c>
       <c r="H4" t="n">
-        <v>0.807467732750389</v>
+        <v>0.8058876233648367</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.47154510513278</v>
+        <v>0.4715474109963007</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049808845570296</v>
+        <v>1.049806202011809</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.26002693423533</v>
+        <v>37.29478957986982</v>
       </c>
       <c r="E5" t="n">
-        <v>301.8053918010255</v>
+        <v>299.1680967710803</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3350153537144025</v>
+        <v>-0.3342589004286773</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663119019514719</v>
+        <v>0.5663231729116096</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5915739234156349</v>
+        <v>-0.5902264226804784</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367925727469496</v>
+        <v>0.736790801462704</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314567580815599</v>
+        <v>0.8314689786134882</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.03999445693194</v>
+        <v>11.02513232771796</v>
       </c>
       <c r="E6" t="n">
-        <v>197.6351416381821</v>
+        <v>197.0942087909602</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2937948163986482</v>
+        <v>-0.2931771565789693</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7193951398264802</v>
+        <v>0.7194155605459849</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.408391439049077</v>
+        <v>-0.4075212890258709</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499190725743067</v>
+        <v>0.7499184193058285</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075030133140576</v>
+        <v>1.075056701679481</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.07644961273263</v>
+        <v>10.04477675965241</v>
       </c>
       <c r="E7" t="n">
-        <v>329.9053598820541</v>
+        <v>328.7498013490843</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5439457167458218</v>
+        <v>-0.545346075344866</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8099326438358679</v>
+        <v>0.8098633317475828</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6715937687974605</v>
+        <v>-0.6733803766224087</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6834021963950355</v>
+        <v>0.6834630421184982</v>
       </c>
       <c r="N7" t="n">
-        <v>1.102970793996386</v>
+        <v>1.102971508518256</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.00098398617986</v>
+        <v>9.978922105283868</v>
       </c>
       <c r="E8" t="n">
-        <v>367.0322571644879</v>
+        <v>370.02625341564</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3165066764491546</v>
+        <v>-0.3180307697009837</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17683310032578</v>
+        <v>1.176822553640779</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2689478026761286</v>
+        <v>-0.2702453047972953</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385609214804517</v>
+        <v>0.7385625622834519</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731968300250176</v>
+        <v>1.731951775870578</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.594138694668697</v>
+        <v>7.535955245100467</v>
       </c>
       <c r="E9" t="n">
-        <v>430.0990192886155</v>
+        <v>412.9351790472057</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4934338950305639</v>
+        <v>0.4771734219095267</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4834318000993333</v>
+        <v>0.4833574859798839</v>
       </c>
       <c r="H9" t="n">
-        <v>1.020689774502164</v>
+        <v>0.9872060240097026</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6781127413256617</v>
+        <v>0.6781409984398443</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532446455624958</v>
+        <v>0.6531696149247667</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.020266249196662</v>
+        <v>7.002192032420842</v>
       </c>
       <c r="E10" t="n">
-        <v>223.3078962948142</v>
+        <v>223.7196970555683</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2211703072465186</v>
+        <v>-0.2243035416009127</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653602194834987</v>
+        <v>0.965331264648685</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2291065063410759</v>
+        <v>-0.2323591391008598</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131541432570925</v>
+        <v>0.7131645493532843</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371865540634129</v>
+        <v>1.371840568473575</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.803548172720651</v>
+        <v>6.796006521764022</v>
       </c>
       <c r="E11" t="n">
-        <v>387.9128299764526</v>
+        <v>388.5664745140727</v>
       </c>
       <c r="F11" t="n">
-        <v>1.045831834513146</v>
+        <v>1.047964561312869</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272154143264634</v>
+        <v>0.8272178535019836</v>
       </c>
       <c r="H11" t="n">
-        <v>1.26427991596927</v>
+        <v>1.266854380471076</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626683315437657</v>
+        <v>0.6626708115018541</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092329277486443</v>
+        <v>1.092333527218786</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.516366543778159</v>
+        <v>6.544061181742498</v>
       </c>
       <c r="E12" t="n">
-        <v>117.2780571548445</v>
+        <v>115.7666660655485</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2467601533339628</v>
+        <v>-0.2413643611853407</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6632286002128271</v>
+        <v>0.6634117151971058</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3720589752232919</v>
+        <v>-0.3638228805073619</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7880499464649441</v>
+        <v>0.7878886675510218</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041491497854222</v>
+        <v>1.041562926901036</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.731814778988794</v>
+        <v>4.731246863644973</v>
       </c>
       <c r="E13" t="n">
-        <v>168.6172372818121</v>
+        <v>168.4942443083138</v>
       </c>
       <c r="F13" t="n">
-        <v>1.800716656470249</v>
+        <v>1.79912864033526</v>
       </c>
       <c r="G13" t="n">
-        <v>0.865653000082805</v>
+        <v>0.8656460076524164</v>
       </c>
       <c r="H13" t="n">
-        <v>2.080183002078199</v>
+        <v>2.078365318422015</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6020992391484006</v>
+        <v>0.6021098346081848</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038605590871798</v>
+        <v>1.038612569486814</v>
       </c>
     </row>
     <row r="14">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.705739491430234</v>
+        <v>4.700375237599169</v>
       </c>
       <c r="E14" t="n">
-        <v>105.5515071189613</v>
+        <v>106.5173369749674</v>
       </c>
       <c r="F14" t="n">
         <v>-0.3828993005931776</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601439547177179</v>
+        <v>0.7601455384227026</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298418768250478</v>
+        <v>1.298417837170547</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.294011935449567</v>
+        <v>4.296678714998712</v>
       </c>
       <c r="E15" t="n">
-        <v>380.4663291634154</v>
+        <v>379.437172018766</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02268395081137942</v>
+        <v>0.02250757100397216</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966387837812149</v>
+        <v>0.7966361071957424</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02847457501844303</v>
+        <v>0.0282532649482856</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166497378320236</v>
+        <v>0.7166616462281438</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137645966633231</v>
+        <v>1.137657862210418</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.242503047439931</v>
+        <v>4.216352532499704</v>
       </c>
       <c r="E16" t="n">
-        <v>307.3204786773634</v>
+        <v>306.7814282121599</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5850427347243181</v>
+        <v>0.5752233056321956</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624332193272742</v>
+        <v>0.9624665198203557</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6078787836658982</v>
+        <v>0.5976553924593252</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129956307516359</v>
+        <v>0.512949641568501</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9838366798104087</v>
+        <v>0.9837797634460962</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.534510609987949</v>
+        <v>3.527088123256886</v>
       </c>
       <c r="E17" t="n">
-        <v>85.30924386340286</v>
+        <v>85.14580541341432</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1646091597727685</v>
+        <v>-0.1655509205114433</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7568829627742998</v>
+        <v>0.7568549428006398</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2174829767199482</v>
+        <v>-0.2187353363893541</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7224371190834119</v>
+        <v>0.7224760744041185</v>
       </c>
       <c r="N17" t="n">
-        <v>1.08960106932781</v>
+        <v>1.089616431960961</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.227535087566374</v>
+        <v>3.223980048692069</v>
       </c>
       <c r="E18" t="n">
-        <v>64.9181251792178</v>
+        <v>65.02128882897179</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4473057920240953</v>
+        <v>-0.4490221843308778</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519780297723208</v>
+        <v>0.7519592505078215</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5948389105989277</v>
+        <v>-0.597136326240603</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642028131410282</v>
+        <v>0.7642100716254289</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145124017230021</v>
+        <v>1.145103089233824</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.023847694411135</v>
+        <v>3.023886161440253</v>
       </c>
       <c r="E19" t="n">
-        <v>95.52510961261662</v>
+        <v>96.13949442922046</v>
       </c>
       <c r="F19" t="n">
         <v>0.1463954880749849</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7169067913813864</v>
+        <v>0.7169328364750099</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935116679118188</v>
+        <v>0.6935349208083267</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.646610757738849</v>
+        <v>2.645534668204546</v>
       </c>
       <c r="E20" t="n">
-        <v>108.2356691004291</v>
+        <v>108.3066338677396</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3060471615546191</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320714283171744</v>
+        <v>0.7320761104908039</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144473751203871</v>
+        <v>1.14447786588528</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.3699832038172</v>
+        <v>581.1905272700571</v>
       </c>
       <c r="E2" t="n">
-        <v>8203.274291422355</v>
+        <v>8165.91119161382</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6831522581400162</v>
+        <v>0.6820104231603104</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018367674429044</v>
+        <v>0.5018345233896537</v>
       </c>
       <c r="H2" t="n">
-        <v>1.361303719575989</v>
+        <v>1.359034485219658</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.2884890107727</v>
+        <v>225.2388718792107</v>
       </c>
       <c r="E3" t="n">
-        <v>4529.744310209435</v>
+        <v>4524.701200554677</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2730265683272335</v>
+        <v>0.2725213296328308</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026724585137303</v>
+        <v>0.6026707121891101</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4530264565275688</v>
+        <v>0.4521894363224295</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908258375190344</v>
+        <v>0.8908242766862818</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069822365429276</v>
+        <v>1.069822174926395</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.91958407696455</v>
+        <v>38.86846970466579</v>
       </c>
       <c r="E4" t="n">
-        <v>1927.852489115342</v>
+        <v>1930.5407653246</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9003694121889099</v>
+        <v>0.8940028884654505</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117239409174175</v>
+        <v>1.117225560163277</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8058876233648367</v>
+        <v>0.8001991006496454</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715474109963007</v>
+        <v>0.4715398327219699</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049806202011809</v>
+        <v>1.049781011863645</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.29478957986982</v>
+        <v>37.29168684752985</v>
       </c>
       <c r="E5" t="n">
-        <v>299.1680967710803</v>
+        <v>298.0582517250178</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3342589004286773</v>
+        <v>-0.3346371565240859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663231729116096</v>
+        <v>0.5663173311248766</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5902264226804784</v>
+        <v>-0.5909004336127164</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.736790801462704</v>
+        <v>0.7367844963528468</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314689786134882</v>
+        <v>0.8314570045328472</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.02513232771796</v>
+        <v>11.02598503396964</v>
       </c>
       <c r="E6" t="n">
-        <v>197.0942087909602</v>
+        <v>196.9062500103166</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2931771565789693</v>
+        <v>-0.2937948163986482</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7194155605459849</v>
+        <v>0.7193951398264802</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4075212890258709</v>
+        <v>-0.408391439049077</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499184193058285</v>
+        <v>0.7499078060225093</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075056701679481</v>
+        <v>1.075015778760299</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.04477675965241</v>
+        <v>10.04607803450863</v>
       </c>
       <c r="E7" t="n">
-        <v>328.7498013490843</v>
+        <v>327.8114730120459</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.545346075344866</v>
+        <v>-0.545783445348989</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8098633317475828</v>
+        <v>0.8098434439037825</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6733803766224087</v>
+        <v>-0.6739369806071228</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6834630421184982</v>
+        <v>0.6834512912323254</v>
       </c>
       <c r="N7" t="n">
-        <v>1.102971508518256</v>
+        <v>1.102930391662816</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.978922105283868</v>
+        <v>9.968847421497768</v>
       </c>
       <c r="E8" t="n">
-        <v>370.02625341564</v>
+        <v>370.2339503174956</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3180307697009837</v>
+        <v>-0.3187924666572269</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176822553640779</v>
+        <v>1.176818432276672</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2702453047972953</v>
+        <v>-0.2708935022716218</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385625622834519</v>
+        <v>0.7385603275578052</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731951775870578</v>
+        <v>1.731948214617871</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.535955245100467</v>
+        <v>7.529750869182746</v>
       </c>
       <c r="E9" t="n">
-        <v>412.9351790472057</v>
+        <v>412.0819910355237</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4771734219095267</v>
+        <v>0.4764464828277137</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833574859798839</v>
+        <v>0.4833583505370342</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9872060240097026</v>
+        <v>0.985700324197066</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6781409984398443</v>
+        <v>0.6781418421891854</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531696149247667</v>
+        <v>0.6531745166846534</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.002192032420842</v>
+        <v>6.998505247906071</v>
       </c>
       <c r="E10" t="n">
-        <v>223.7196970555683</v>
+        <v>224.2473188844104</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2243035416009127</v>
+        <v>-0.2254420411490914</v>
       </c>
       <c r="G10" t="n">
-        <v>0.965331264648685</v>
+        <v>0.9653237690944368</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2323591391008598</v>
+        <v>-0.2335403399012716</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131645493532843</v>
+        <v>0.7131613473518971</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371840568473575</v>
+        <v>1.371829891551047</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.796006521764022</v>
+        <v>6.795951351593373</v>
       </c>
       <c r="E11" t="n">
-        <v>388.5664745140727</v>
+        <v>388.5715698086009</v>
       </c>
       <c r="F11" t="n">
-        <v>1.047964561312869</v>
+        <v>1.045222595834877</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272178535019836</v>
+        <v>0.8272148917011979</v>
       </c>
       <c r="H11" t="n">
-        <v>1.266854380471076</v>
+        <v>1.263544220879943</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626708115018541</v>
+        <v>0.6626677992222987</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092333527218786</v>
+        <v>1.092329535371393</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.544061181742498</v>
+        <v>6.54439104299562</v>
       </c>
       <c r="E12" t="n">
-        <v>115.7666660655485</v>
+        <v>115.5611900598949</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2413643611853407</v>
+        <v>-0.2409785439346752</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6634117151971058</v>
+        <v>0.6634269683210862</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3638228805073619</v>
+        <v>-0.3632329637495926</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7878886675510218</v>
+        <v>0.7878367247149547</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041562926901036</v>
+        <v>1.041522863511372</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.731246863644973</v>
+        <v>4.728281691126901</v>
       </c>
       <c r="E13" t="n">
-        <v>168.4942443083138</v>
+        <v>168.4946423764295</v>
       </c>
       <c r="F13" t="n">
-        <v>1.79912864033526</v>
+        <v>1.795953348496985</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8656460076524164</v>
+        <v>0.8656328441004383</v>
       </c>
       <c r="H13" t="n">
-        <v>2.078365318422015</v>
+        <v>2.074728749881634</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6021098346081848</v>
+        <v>0.6021017794163225</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038612569486814</v>
+        <v>1.038587525293465</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.700375237599169</v>
+        <v>4.698064710145841</v>
       </c>
       <c r="E14" t="n">
-        <v>106.5173369749674</v>
+        <v>106.5480080784263</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3828993005931776</v>
+        <v>-0.3841507477623464</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571961252945427</v>
+        <v>0.8571884254440747</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4466880907349048</v>
+        <v>-0.4481520472740091</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601455384227026</v>
+        <v>0.7601428066172761</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298417837170547</v>
+        <v>1.298407313860656</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.296678714998712</v>
+        <v>4.298426138037959</v>
       </c>
       <c r="E15" t="n">
-        <v>379.437172018766</v>
+        <v>379.063311613755</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02250757100397216</v>
+        <v>0.02497764651847278</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966361071957424</v>
+        <v>0.7966760769297252</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0282532649482856</v>
+        <v>0.03135232403956829</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166616462281438</v>
+        <v>0.7166168504564672</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137657862210418</v>
+        <v>1.137648915078935</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.216352532499704</v>
+        <v>4.21488532852031</v>
       </c>
       <c r="E16" t="n">
-        <v>306.7814282121599</v>
+        <v>306.8755270106812</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5752233056321956</v>
+        <v>0.5724208273967837</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624665198203557</v>
+        <v>0.9624812807668676</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5976553924593252</v>
+        <v>0.5947345042811649</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.512949641568501</v>
+        <v>0.5129493205816364</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9837797634460962</v>
+        <v>0.9837986348710555</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.527088123256886</v>
+        <v>3.52485359674722</v>
       </c>
       <c r="E17" t="n">
-        <v>85.14580541341432</v>
+        <v>85.06086489722115</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1655509205114433</v>
+        <v>-0.1678099582803586</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7568549428006398</v>
+        <v>0.756792790249364</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2187353363893541</v>
+        <v>-0.2217383152197645</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7224760744041185</v>
+        <v>0.7224960522350102</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089616431960961</v>
+        <v>1.089561952856185</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.223980048692069</v>
+        <v>3.223099896880877</v>
       </c>
       <c r="E18" t="n">
-        <v>65.02128882897179</v>
+        <v>65.03083168419269</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4490221843308778</v>
+        <v>-0.4488587814240778</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519592505078215</v>
+        <v>0.7519606391544971</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.597136326240603</v>
+        <v>-0.596917921034768</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642100716254289</v>
+        <v>0.7642070431527487</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145103089233824</v>
+        <v>1.145105786532973</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.023886161440253</v>
+        <v>3.022759921845328</v>
       </c>
       <c r="E19" t="n">
-        <v>96.13949442922046</v>
+        <v>96.19658912421941</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1463954880749849</v>
+        <v>0.1435290419539552</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4854587557719611</v>
+        <v>0.4853744139867775</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3015611240592241</v>
+        <v>0.295707886155419</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7169328364750099</v>
+        <v>0.7169983797809666</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935349208083267</v>
+        <v>0.6934809228846903</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.645534668204546</v>
+        <v>2.644045155322117</v>
       </c>
       <c r="E20" t="n">
-        <v>108.3066338677396</v>
+        <v>108.2046876690985</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3060471615546191</v>
+        <v>-0.3070747184070788</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845373785531247</v>
+        <v>0.7845258707480058</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3900988912969877</v>
+        <v>-0.3914143941668852</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320761104908039</v>
+        <v>0.7320733854211143</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14447786588528</v>
+        <v>1.144461935917861</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.1905272700571</v>
+        <v>581.210434989652</v>
       </c>
       <c r="E2" t="n">
-        <v>8165.91119161382</v>
+        <v>8070.162329473</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6820104231603104</v>
+        <v>0.6826406154018538</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018345233896537</v>
+        <v>0.5018356801453453</v>
       </c>
       <c r="H2" t="n">
-        <v>1.359034485219658</v>
+        <v>1.36028712666294</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.2388718792107</v>
+        <v>225.3267585261124</v>
       </c>
       <c r="E3" t="n">
-        <v>4524.701200554677</v>
+        <v>4485.015520091327</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2725213296328308</v>
+        <v>0.2733072802321006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026707121891101</v>
+        <v>0.6026735102148226</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4521894363224295</v>
+        <v>0.4534914437083528</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908242766862818</v>
+        <v>0.8908246336756641</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069822174926395</v>
+        <v>1.069825104519575</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.86846970466579</v>
+        <v>38.78054877042567</v>
       </c>
       <c r="E4" t="n">
-        <v>1930.5407653246</v>
+        <v>1945.25914205272</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8940028884654505</v>
+        <v>0.892942370442845</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117225560163277</v>
+        <v>1.117223964668058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8001991006496454</v>
+        <v>0.7992509995148106</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715398327219699</v>
+        <v>0.4715399864747906</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049781011863645</v>
+        <v>1.049777435188163</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.29168684752985</v>
+        <v>37.31474460664187</v>
       </c>
       <c r="E5" t="n">
-        <v>298.0582517250178</v>
+        <v>298.882770620402</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3346371565240859</v>
+        <v>-0.3338805854433086</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663173311248766</v>
+        <v>0.5663294272989022</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5909004336127164</v>
+        <v>-0.5895518921482605</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367844963528468</v>
+        <v>0.7367811993250252</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314570045328472</v>
+        <v>0.8314691265824097</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.02598503396964</v>
+        <v>11.05565240160689</v>
       </c>
       <c r="E6" t="n">
-        <v>196.9062500103166</v>
+        <v>198.3677411378224</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2937948163986482</v>
+        <v>-0.2900866399888797</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7193951398264802</v>
+        <v>0.7195294434324139</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.408391439049077</v>
+        <v>-0.4031615976756452</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499078060225093</v>
+        <v>0.7498077737049118</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075015778760299</v>
+        <v>1.075070568794423</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.04607803450863</v>
+        <v>10.10739411203336</v>
       </c>
       <c r="E7" t="n">
-        <v>327.8114730120459</v>
+        <v>332.2180789493447</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.545783445348989</v>
+        <v>-0.5407906014575463</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8098434439037825</v>
+        <v>0.8101201813279045</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6739369806071228</v>
+        <v>-0.6675436730524501</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6834512912323254</v>
+        <v>0.6832771749017962</v>
       </c>
       <c r="N7" t="n">
-        <v>1.102930391662816</v>
+        <v>1.103023660390871</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.968847421497768</v>
+        <v>9.987506515652033</v>
       </c>
       <c r="E8" t="n">
-        <v>370.2339503174956</v>
+        <v>369.8115425685106</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3187924666572269</v>
+        <v>-0.3153629950512642</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176818432276672</v>
+        <v>1.17684302626033</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2708935022716218</v>
+        <v>-0.2679737127332924</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385603275578052</v>
+        <v>0.7385600554725442</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731948214617871</v>
+        <v>1.731979779727043</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.529750869182746</v>
+        <v>7.545979387127653</v>
       </c>
       <c r="E9" t="n">
-        <v>412.0819910355237</v>
+        <v>393.4388142534972</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4764464828277137</v>
+        <v>0.4783852048651394</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833583505370342</v>
+        <v>0.483356843585128</v>
       </c>
       <c r="H9" t="n">
-        <v>0.985700324197066</v>
+        <v>0.9897143512376627</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6781418421891854</v>
+        <v>0.6781498964753936</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531745166846534</v>
+        <v>0.6531787324149432</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.998505247906071</v>
+        <v>6.995864632768667</v>
       </c>
       <c r="E10" t="n">
-        <v>224.2473188844104</v>
+        <v>223.6448131359284</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2254420411490914</v>
+        <v>-0.2252997537622792</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653237690944368</v>
+        <v>0.9653246175594404</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2335403399012716</v>
+        <v>-0.2333927361470259</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131613473518971</v>
+        <v>0.7131631073978875</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371829891551047</v>
+        <v>1.371831320776112</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.795951351593373</v>
+        <v>6.872839280322427</v>
       </c>
       <c r="E11" t="n">
-        <v>388.5715698086009</v>
+        <v>115.2677367477947</v>
       </c>
       <c r="F11" t="n">
-        <v>1.045222595834877</v>
+        <v>-0.2403997173048603</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272148917011979</v>
+        <v>0.6634503911837316</v>
       </c>
       <c r="H11" t="n">
-        <v>1.263544220879943</v>
+        <v>-0.3623476909493382</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3268819295856837</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="J11" t="n">
         <v>265</v>
@@ -1030,45 +1030,45 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626677992222987</v>
+        <v>0.7878332613788653</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092329535371393</v>
+        <v>1.041552655837422</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.54439104299562</v>
+        <v>6.794342804062208</v>
       </c>
       <c r="E12" t="n">
-        <v>115.5611900598949</v>
+        <v>386.6362709263305</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2409785439346752</v>
+        <v>1.046745785735527</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6634269683210862</v>
+        <v>0.8272163434996075</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3632329637495926</v>
+        <v>1.265383347368576</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4207389749702026</v>
+        <v>0.3268819295856837</v>
       </c>
       <c r="J12" t="n">
         <v>265</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7878367247149547</v>
+        <v>0.6626693450704276</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041522863511372</v>
+        <v>1.092331482726922</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.728281691126901</v>
+        <v>4.734586833958632</v>
       </c>
       <c r="E13" t="n">
-        <v>168.4946423764295</v>
+        <v>167.9096840080234</v>
       </c>
       <c r="F13" t="n">
-        <v>1.795953348496985</v>
+        <v>1.811839674211146</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8656328441004383</v>
+        <v>0.8657096119948592</v>
       </c>
       <c r="H13" t="n">
-        <v>2.074728749881634</v>
+        <v>2.092895411009835</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6021017794163225</v>
+        <v>0.6020774464967137</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038587525293465</v>
+        <v>1.038635260941519</v>
       </c>
     </row>
     <row r="14">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.698064710145841</v>
+        <v>4.693557155496197</v>
       </c>
       <c r="E14" t="n">
-        <v>106.5480080784263</v>
+        <v>107.2488145965308</v>
       </c>
       <c r="F14" t="n">
         <v>-0.3841507477623464</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601428066172761</v>
+        <v>0.7601432499189322</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298407313860656</v>
+        <v>1.298405078174661</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.298426138037959</v>
+        <v>4.29335854679691</v>
       </c>
       <c r="E15" t="n">
-        <v>379.063311613755</v>
+        <v>375.3238881131689</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02497764651847278</v>
+        <v>0.01968662811963595</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966760769297252</v>
+        <v>0.796597014784864</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03135232403956829</v>
+        <v>0.02471340935787049</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166168504564672</v>
+        <v>0.7166773593903518</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137648915078935</v>
+        <v>1.137629442547617</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.21488532852031</v>
+        <v>4.221308794202775</v>
       </c>
       <c r="E16" t="n">
-        <v>306.8755270106812</v>
+        <v>298.9133964377314</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5724208273967837</v>
+        <v>0.5752233056321956</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624812807668676</v>
+        <v>0.9624665198203557</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5947345042811649</v>
+        <v>0.5976553924593252</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129493205816364</v>
+        <v>0.5129554218585559</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9837986348710555</v>
+        <v>0.9837929809139856</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.52485359674722</v>
+        <v>3.521935970048078</v>
       </c>
       <c r="E17" t="n">
-        <v>85.06086489722115</v>
+        <v>86.01013907065833</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1678099582803586</v>
+        <v>-0.1670571321267226</v>
       </c>
       <c r="G17" t="n">
-        <v>0.756792790249364</v>
+        <v>0.7568127084176448</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2217383152197645</v>
+        <v>-0.2207377469598893</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7224960522350102</v>
+        <v>0.7224953350048551</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089561952856185</v>
+        <v>1.089587036030941</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.223099896880877</v>
+        <v>3.21326819655976</v>
       </c>
       <c r="E18" t="n">
-        <v>65.03083168419269</v>
+        <v>64.93250372764548</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4488587814240778</v>
+        <v>-0.4504922128720239</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519606391544971</v>
+        <v>0.751950540922398</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.596917921034768</v>
+        <v>-0.5990981964311335</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642070431527487</v>
+        <v>0.7642059185569771</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145105786532973</v>
+        <v>1.145086084091478</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.022759921845328</v>
+        <v>3.027395906598912</v>
       </c>
       <c r="E19" t="n">
-        <v>96.19658912421941</v>
+        <v>97.00757017791135</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1435290419539552</v>
+        <v>0.1463954880749849</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4853744139867775</v>
+        <v>0.4854587557719611</v>
       </c>
       <c r="H19" t="n">
-        <v>0.295707886155419</v>
+        <v>0.3015611240592241</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7169983797809666</v>
+        <v>0.7169131083318367</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934809228846903</v>
+        <v>0.6935173391150331</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.644045155322117</v>
+        <v>2.642273101328846</v>
       </c>
       <c r="E20" t="n">
-        <v>108.2046876690985</v>
+        <v>108.2449568816213</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3070747184070788</v>
+        <v>-0.3065609921268032</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845258707480058</v>
+        <v>0.7845313711516149</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3914143941668852</v>
+        <v>-0.3907568306373801</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320733854211143</v>
+        <v>0.7320750163551298</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144461935917861</v>
+        <v>1.144469871493767</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.210434989652</v>
+        <v>581.803061518281</v>
       </c>
       <c r="E2" t="n">
-        <v>8070.162329473</v>
+        <v>8111.990377165434</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6826406154018538</v>
+        <v>0.6849193036093359</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018356801453453</v>
+        <v>0.5018415431807284</v>
       </c>
       <c r="H2" t="n">
-        <v>1.36028712666294</v>
+        <v>1.364811887171078</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.3267585261124</v>
+        <v>225.5865800516114</v>
       </c>
       <c r="E3" t="n">
-        <v>4485.015520091327</v>
+        <v>4491.033099032537</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2733072802321006</v>
+        <v>0.2757782759456153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026735102148226</v>
+        <v>0.6026852759677156</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4534914437083528</v>
+        <v>0.4575825674566307</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908246336756641</v>
+        <v>0.8908271351953889</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069825104519575</v>
+        <v>1.069836495424239</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.78054877042567</v>
+        <v>38.88196171724254</v>
       </c>
       <c r="E4" t="n">
-        <v>1945.25914205272</v>
+        <v>1972.2014749937</v>
       </c>
       <c r="F4" t="n">
-        <v>0.892942370442845</v>
+        <v>0.8968317319125021</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117223964668058</v>
+        <v>1.117230810303509</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7992509995148106</v>
+        <v>0.8027273537764923</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715399864747906</v>
+        <v>0.4715485384762168</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049777435188163</v>
+        <v>1.049790641882934</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.31474460664187</v>
+        <v>37.32520745340842</v>
       </c>
       <c r="E5" t="n">
-        <v>298.882770620402</v>
+        <v>298.2690586623384</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3338805854433086</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367811993250252</v>
+        <v>0.7368032096909799</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314691265824097</v>
+        <v>0.831484251247037</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.05565240160689</v>
+        <v>11.06366010102116</v>
       </c>
       <c r="E6" t="n">
-        <v>198.3677411378224</v>
+        <v>197.953488449948</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2900866399888797</v>
+        <v>-0.29070503877807</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7195294434324139</v>
+        <v>0.7195050965275779</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4031615976756452</v>
+        <v>-0.4040347180041518</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7498077737049118</v>
+        <v>0.7498932362308646</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075070568794423</v>
+        <v>1.075144161840258</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.10739411203336</v>
+        <v>10.10170081707374</v>
       </c>
       <c r="E7" t="n">
-        <v>332.2180789493447</v>
+        <v>331.1723132865722</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5407906014575463</v>
+        <v>-0.5425441790890799</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8101201813279045</v>
+        <v>0.8100105956832497</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6675436730524501</v>
+        <v>-0.6697988668054892</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6832771749017962</v>
+        <v>0.6834167095358598</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103023660390871</v>
+        <v>1.103086788077385</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.987506515652033</v>
+        <v>10.01324446716738</v>
       </c>
       <c r="E8" t="n">
-        <v>369.8115425685106</v>
+        <v>370.1602505845019</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3153629950512642</v>
+        <v>-0.3146002498350767</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17684302626033</v>
+        <v>1.17685060348873</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2679737127332924</v>
+        <v>-0.2673238632860076</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385600554725442</v>
+        <v>0.7385690511861216</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731979779727043</v>
+        <v>1.731991791866194</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.545979387127653</v>
+        <v>7.518489510976842</v>
       </c>
       <c r="E9" t="n">
-        <v>393.4388142534972</v>
+        <v>382.6429389546213</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4783852048651394</v>
+        <v>0.4725711308007232</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483356843585128</v>
+        <v>0.4833690302456716</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9897143512376627</v>
+        <v>0.9776611682393876</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6781498964753936</v>
+        <v>0.6780813285093339</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531787324149432</v>
+        <v>0.6531215253959473</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.995864632768667</v>
+        <v>7.003905510458186</v>
       </c>
       <c r="E10" t="n">
-        <v>223.6448131359284</v>
+        <v>222.2653645153499</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2252997537622792</v>
+        <v>-0.224161196948749</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653246175594404</v>
+        <v>0.9653323153511419</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2333927361470259</v>
+        <v>-0.232211429560617</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131631073978875</v>
+        <v>0.7131698020412021</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371831320776112</v>
+        <v>1.371839110567653</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.872839280322427</v>
+        <v>6.882568851987775</v>
       </c>
       <c r="E11" t="n">
-        <v>115.2677367477947</v>
+        <v>117.1375930589173</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2403997173048603</v>
+        <v>-0.2402067482334098</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6634503911837316</v>
+        <v>0.663458343641523</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3623476909493382</v>
+        <v>-0.3620524943811654</v>
       </c>
       <c r="I11" t="n">
         <v>0.4207389749702026</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7878332613788653</v>
+        <v>0.7878993659965882</v>
       </c>
       <c r="N11" t="n">
-        <v>1.041552655837422</v>
+        <v>1.041640365217928</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.794342804062208</v>
+        <v>6.805107434285102</v>
       </c>
       <c r="E12" t="n">
-        <v>386.6362709263305</v>
+        <v>387.8398595793327</v>
       </c>
       <c r="F12" t="n">
-        <v>1.046745785735527</v>
+        <v>1.050707532953253</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8272163434996075</v>
+        <v>0.8272223838294045</v>
       </c>
       <c r="H12" t="n">
-        <v>1.265383347368576</v>
+        <v>1.270163324267513</v>
       </c>
       <c r="I12" t="n">
         <v>0.3268819295856837</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.6626693450704276</v>
+        <v>0.6626753178634147</v>
       </c>
       <c r="N12" t="n">
-        <v>1.092331482726922</v>
+        <v>1.092336542474057</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.734586833958632</v>
+        <v>4.786413107014031</v>
       </c>
       <c r="E13" t="n">
-        <v>167.9096840080234</v>
+        <v>175.5664276564063</v>
       </c>
       <c r="F13" t="n">
-        <v>1.811839674211146</v>
+        <v>1.867635352816752</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8657096119948592</v>
+        <v>0.8661937711424813</v>
       </c>
       <c r="H13" t="n">
-        <v>2.092895411009835</v>
+        <v>2.156140363781885</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6020774464967137</v>
+        <v>0.6018992797821273</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038635260941519</v>
+        <v>1.038896468590418</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.693557155496197</v>
+        <v>4.695730640993949</v>
       </c>
       <c r="E14" t="n">
-        <v>107.2488145965308</v>
+        <v>107.5640254058469</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3841507477623464</v>
+        <v>-0.3835251111792812</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571884254440747</v>
+        <v>0.8571918425125286</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4481520472740091</v>
+        <v>-0.4474203931469118</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601432499189322</v>
+        <v>0.7601455514456473</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298405078174661</v>
+        <v>1.298399015935472</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.29335854679691</v>
+        <v>4.305811467137314</v>
       </c>
       <c r="E15" t="n">
-        <v>375.3238881131689</v>
+        <v>331.2355592368145</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01968662811963595</v>
+        <v>0.02427174405639909</v>
       </c>
       <c r="G15" t="n">
-        <v>0.796597014784864</v>
+        <v>0.7966641081139942</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02471340935787049</v>
+        <v>0.03046672218466012</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166773593903518</v>
+        <v>0.7166732167809259</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137629442547617</v>
+        <v>1.137705390903335</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.221308794202775</v>
+        <v>4.241401415500842</v>
       </c>
       <c r="E16" t="n">
-        <v>298.9133964377314</v>
+        <v>263.371246330534</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5752233056321956</v>
+        <v>0.5906613356319648</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624665198203557</v>
+        <v>0.9624270160741564</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5976553924593252</v>
+        <v>0.6137206518176683</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129554218585559</v>
+        <v>0.5130031573540497</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9837929809139856</v>
+        <v>0.9838326553030551</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.521935970048078</v>
+        <v>3.514841844387824</v>
       </c>
       <c r="E17" t="n">
-        <v>86.01013907065833</v>
+        <v>86.00218205768422</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1670571321267226</v>
+        <v>-0.1717592334288705</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7568127084176448</v>
+        <v>0.7567013369373577</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2207377469598893</v>
+        <v>-0.2269841812676608</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7224953350048551</v>
+        <v>0.7226129323369068</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089587036030941</v>
+        <v>1.08959128517314</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.21326819655976</v>
+        <v>3.217604576254712</v>
       </c>
       <c r="E18" t="n">
-        <v>64.93250372764548</v>
+        <v>64.39390950789272</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4504922128720239</v>
+        <v>-0.4501656328592654</v>
       </c>
       <c r="G18" t="n">
-        <v>0.751950540922398</v>
+        <v>0.751951887098416</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5990981964311335</v>
+        <v>-0.5986628141812846</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642059185569771</v>
+        <v>0.764205163738657</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145086084091478</v>
+        <v>1.145073624956334</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.027395906598912</v>
+        <v>3.023439454930126</v>
       </c>
       <c r="E19" t="n">
-        <v>97.00757017791135</v>
+        <v>97.61091213099559</v>
       </c>
       <c r="F19" t="n">
         <v>0.1463954880749849</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7169131083318367</v>
+        <v>0.7169994985700678</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935173391150331</v>
+        <v>0.6935928067230444</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.642273101328846</v>
+        <v>2.648741359889771</v>
       </c>
       <c r="E20" t="n">
-        <v>108.2449568816213</v>
+        <v>108.4450311292754</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3065609921268032</v>
+        <v>-0.3034764455360498</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845313711516149</v>
+        <v>0.7845750200871737</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3907568306373801</v>
+        <v>-0.3868036042013301</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320750163551298</v>
+        <v>0.7320767568727349</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144469871493767</v>
+        <v>1.1445228957897</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.2769176508824</v>
+        <v>581.3798527211871</v>
       </c>
       <c r="E2" t="n">
-        <v>7961.900213329835</v>
+        <v>7975.769154418218</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6828088326298931</v>
+        <v>0.683420499995675</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018360229780013</v>
+        <v>0.50183739052326</v>
       </c>
       <c r="H2" t="n">
-        <v>1.360621400946789</v>
+        <v>1.361836548853166</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.4099287782111</v>
+        <v>225.3531185090955</v>
       </c>
       <c r="E3" t="n">
-        <v>4296.536608255219</v>
+        <v>4291.947295008519</v>
       </c>
       <c r="F3" t="n">
-        <v>0.273821962761476</v>
+        <v>0.2738032460347382</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026755895661955</v>
+        <v>0.6026755105244163</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4543438750498795</v>
+        <v>0.4543128785778753</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908242771667076</v>
+        <v>0.8908257672643692</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069827636635922</v>
+        <v>1.069826370479412</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.03504600654483</v>
+        <v>38.97658262472027</v>
       </c>
       <c r="E4" t="n">
-        <v>1916.32132596144</v>
+        <v>1920.377369916216</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9170206652507467</v>
+        <v>0.9049710951117163</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117310127335899</v>
+        <v>1.117253969969449</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8207395984472813</v>
+        <v>0.8099958643570203</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715437262888975</v>
+        <v>0.471551095942059</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049866005508712</v>
+        <v>1.049826784399978</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.29867033484167</v>
+        <v>37.27026282800273</v>
       </c>
       <c r="E5" t="n">
-        <v>283.7243970307086</v>
+        <v>282.937412882563</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3346371565240859</v>
+        <v>-0.3350153537144025</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663173311248766</v>
+        <v>0.5663119019514719</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5909004336127164</v>
+        <v>-0.5915739234156349</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367916546693639</v>
+        <v>0.7367998356773041</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314625980640827</v>
+        <v>0.8314615932959386</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.02568432251237</v>
+        <v>11.01112914920039</v>
       </c>
       <c r="E6" t="n">
-        <v>178.8720538579817</v>
+        <v>180.496131284935</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2941035908237466</v>
+        <v>-0.2950296920722991</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7193852240056364</v>
+        <v>0.7193566547956974</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4088262880715524</v>
+        <v>-0.4101299266579937</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499351323654556</v>
+        <v>0.7499715038564245</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075036921393084</v>
+        <v>1.075043435172753</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.15473688937</v>
+        <v>10.11702523032162</v>
       </c>
       <c r="E7" t="n">
-        <v>288.1986701884917</v>
+        <v>291.8227859227608</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5387717169480619</v>
+        <v>-0.5404396654443309</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8102628817456045</v>
+        <v>0.8101437174715376</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6649344664380397</v>
+        <v>-0.6670911022195489</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6831816774879437</v>
+        <v>0.6832864432509334</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103063011443966</v>
+        <v>1.103066909095843</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.982651165648228</v>
+        <v>9.950532428775976</v>
       </c>
       <c r="E8" t="n">
-        <v>357.9983598072541</v>
+        <v>360.1369677723338</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3161255075262525</v>
+        <v>-0.3203151606412957</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176836216980637</v>
+        <v>1.176812493545588</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2686231974890468</v>
+        <v>-0.2721887831732874</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.738561773443871</v>
+        <v>0.7385577540428239</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731972603936199</v>
+        <v>1.731923544509743</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.531793591928591</v>
+        <v>7.498719354798828</v>
       </c>
       <c r="E9" t="n">
-        <v>345.6404432216464</v>
+        <v>343.3646795426337</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4779004590148501</v>
+        <v>0.4650705848672394</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833569807626908</v>
+        <v>0.4834188053522628</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9887111969724098</v>
+        <v>0.9620448764469284</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6781468358076808</v>
+        <v>0.6779856141234711</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653175523599552</v>
+        <v>0.6531019844572494</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.008677359638309</v>
+        <v>7.005980564408829</v>
       </c>
       <c r="E10" t="n">
-        <v>207.863527510568</v>
+        <v>206.8690902623021</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2220251688387778</v>
+        <v>-0.2231645840629187</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653511093567646</v>
+        <v>0.9653403780847349</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2299942131798224</v>
+        <v>-0.2311770947628692</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713159327644392</v>
+        <v>0.7131648575036044</v>
       </c>
       <c r="N10" t="n">
-        <v>1.37186076042177</v>
+        <v>1.371852409126868</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.794649201454448</v>
+        <v>6.79320372775466</v>
       </c>
       <c r="E11" t="n">
-        <v>364.5269021329714</v>
+        <v>366.4131120831735</v>
       </c>
       <c r="F11" t="n">
-        <v>1.044613406873737</v>
+        <v>1.046136472494112</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272144465349048</v>
+        <v>0.8272157046861656</v>
       </c>
       <c r="H11" t="n">
-        <v>1.262808466715601</v>
+        <v>1.264647741293792</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626664488653485</v>
+        <v>0.662668247453301</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092323457535908</v>
+        <v>1.092325106980687</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.558050934004897</v>
+        <v>6.55132761806443</v>
       </c>
       <c r="E12" t="n">
-        <v>105.94559288541</v>
+        <v>106.407431747405</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2402067482334098</v>
+        <v>-0.2398207698074929</v>
       </c>
       <c r="G12" t="n">
-        <v>0.663458343641523</v>
+        <v>0.6634744657968814</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3620524943811654</v>
+        <v>-0.3614619434064438</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7878307482487243</v>
+        <v>0.7878349913116708</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041561106357391</v>
+        <v>1.041589187787661</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.816615786237584</v>
+        <v>4.886979221194027</v>
       </c>
       <c r="E13" t="n">
-        <v>188.8227153381944</v>
+        <v>244.3281435026387</v>
       </c>
       <c r="F13" t="n">
-        <v>1.875630636582229</v>
+        <v>1.928552014967049</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8662902768919202</v>
+        <v>0.8670983610430454</v>
       </c>
       <c r="H13" t="n">
-        <v>2.165129502909376</v>
+        <v>2.224144458821448</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6017692986226441</v>
+        <v>0.6013198623254322</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038799266013869</v>
+        <v>1.038988877535312</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.696597602973396</v>
+        <v>4.690045613372703</v>
       </c>
       <c r="E14" t="n">
-        <v>97.16866619824619</v>
+        <v>97.33870521106051</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3822733160838268</v>
+        <v>-0.3847762102624862</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8572012737771414</v>
+        <v>0.8571858740995347</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4459551423662626</v>
+        <v>-0.4488830507930264</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601443536961331</v>
+        <v>0.7601408766028532</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298425538238794</v>
+        <v>1.298392734487572</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.323360646498784</v>
+        <v>4.310829476209205</v>
       </c>
       <c r="E15" t="n">
-        <v>270.8244097614946</v>
+        <v>263.4420301961471</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03522818171878339</v>
+        <v>0.02656641407463556</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7968989553162588</v>
+        <v>0.7967046121350794</v>
       </c>
       <c r="H15" t="n">
-        <v>0.04420658539425826</v>
+        <v>0.03334537502354924</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7164752039773616</v>
+        <v>0.7166242196099794</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137738853762181</v>
+        <v>1.137694862345076</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.245665837062884</v>
+        <v>4.216029636089911</v>
       </c>
       <c r="E16" t="n">
-        <v>239.1344984115981</v>
+        <v>235.3029551935135</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5934726776058894</v>
+        <v>0.5766250573171603</v>
       </c>
       <c r="G16" t="n">
-        <v>0.962427412446229</v>
+        <v>0.9624600137347983</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6166414941335089</v>
+        <v>0.5991158584132585</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5130160972773087</v>
+        <v>0.5129537121067861</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9838686990142732</v>
+        <v>0.9837796986088272</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.515365157511799</v>
+        <v>3.51366149218845</v>
       </c>
       <c r="E17" t="n">
-        <v>80.05678699496191</v>
+        <v>80.15029685637761</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1681863014103373</v>
+        <v>-0.1621592205307761</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7567831309490562</v>
+        <v>0.7569616581117294</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2222384386388483</v>
+        <v>-0.214223823350959</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7225211377065036</v>
+        <v>0.7224028364056215</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089582620086983</v>
+        <v>1.0896582422845</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.214154558819589</v>
+        <v>3.207887198132426</v>
       </c>
       <c r="E18" t="n">
-        <v>55.51909440276691</v>
+        <v>55.12139855726328</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4507371129915595</v>
+        <v>-0.452042741627372</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519497522755971</v>
+        <v>0.7519487452029018</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5994245115814066</v>
+        <v>-0.6011616410176936</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642045245471349</v>
+        <v>0.7641919133952103</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145082012070502</v>
+        <v>1.145058461611578</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.023754518246285</v>
+        <v>3.018891856620596</v>
       </c>
       <c r="E19" t="n">
-        <v>97.11108443988356</v>
+        <v>97.22551696555348</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1463954880749849</v>
+        <v>0.1444843055259737</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4854587557719611</v>
+        <v>0.4854014670701913</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3015611240592241</v>
+        <v>0.2976593919216164</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7169196156553684</v>
+        <v>0.7170136989886678</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935231602929874</v>
+        <v>0.6935304303165361</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.647207183626107</v>
+        <v>2.655889394271015</v>
       </c>
       <c r="E20" t="n">
-        <v>106.0534629167781</v>
+        <v>111.2673094286417</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3050191876741568</v>
+        <v>-0.3034764455360498</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845509143022783</v>
+        <v>0.7845750200871737</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3887818905232153</v>
+        <v>-0.3868036042013301</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320677672367839</v>
+        <v>0.7320618006665295</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144486266068674</v>
+        <v>1.144508984004</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.3798527211871</v>
+        <v>581.2735081730279</v>
       </c>
       <c r="E2" t="n">
-        <v>7975.769154418218</v>
+        <v>8019.477202993045</v>
       </c>
       <c r="F2" t="n">
-        <v>0.683420499995675</v>
+        <v>0.6802046955106436</v>
       </c>
       <c r="G2" t="n">
-        <v>0.50183739052326</v>
+        <v>0.5018323248303904</v>
       </c>
       <c r="H2" t="n">
-        <v>1.361836548853166</v>
+        <v>1.355442170331574</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.3531185090955</v>
+        <v>225.3747956107553</v>
       </c>
       <c r="E3" t="n">
-        <v>4291.947295008519</v>
+        <v>4286.510606260245</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2738032460347382</v>
+        <v>0.2722874414388936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026755105244163</v>
+        <v>0.6026699675961326</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4543128785778753</v>
+        <v>0.4518019083064078</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908257672643692</v>
+        <v>0.8908199920159222</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069826370479412</v>
+        <v>1.06982039449865</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.97658262472027</v>
+        <v>38.83529025253894</v>
       </c>
       <c r="E4" t="n">
-        <v>1920.377369916216</v>
+        <v>1914.736504699751</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9049710951117163</v>
+        <v>0.892942370442845</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117253969969449</v>
+        <v>1.117223964668058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8099958643570203</v>
+        <v>0.7992509995148106</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.471551095942059</v>
+        <v>0.4715354663873992</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049826784399978</v>
+        <v>1.04977439111158</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.27026282800273</v>
+        <v>37.31634060272207</v>
       </c>
       <c r="E5" t="n">
-        <v>282.937412882563</v>
+        <v>283.5149832473697</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3350153537144025</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367998356773041</v>
+        <v>0.7367723300942082</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314615932959386</v>
+        <v>0.8314389466678707</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.01112914920039</v>
+        <v>11.00410390640764</v>
       </c>
       <c r="E6" t="n">
-        <v>180.496131284935</v>
+        <v>180.2502456488992</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2950296920722991</v>
+        <v>-0.2956469078091575</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7193566547956974</v>
+        <v>0.7193385906104887</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4101299266579937</v>
+        <v>-0.4109982582169653</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499715038564245</v>
+        <v>0.7499169471177488</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075043435172753</v>
+        <v>1.07494908781917</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.11702523032162</v>
+        <v>10.09197098885017</v>
       </c>
       <c r="E7" t="n">
-        <v>291.8227859227608</v>
+        <v>290.8859640833167</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5404396654443309</v>
+        <v>-0.5432450951973771</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8101437174715376</v>
+        <v>0.8099705399390968</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6670911022195489</v>
+        <v>-0.6706973505952756</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6832864432509334</v>
+        <v>0.6833132000093174</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103066909095843</v>
+        <v>1.102885434385118</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.950532428775976</v>
+        <v>9.946060456043989</v>
       </c>
       <c r="E8" t="n">
-        <v>360.1369677723338</v>
+        <v>362.8121281350593</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3203151606412957</v>
+        <v>-0.3222172145376248</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176812493545588</v>
+        <v>1.176809390180492</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2721887831732874</v>
+        <v>-0.2738057813153624</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385577540428239</v>
+        <v>0.7385566304963018</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731923544509743</v>
+        <v>1.73193382519124</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.498719354798828</v>
+        <v>7.468319656118181</v>
       </c>
       <c r="E9" t="n">
-        <v>343.3646795426337</v>
+        <v>354.3535258748457</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4650705848672394</v>
+        <v>0.4585464102903125</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4834188053522628</v>
+        <v>0.4834934085770315</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9620448764469284</v>
+        <v>0.9484026093341367</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6779856141234711</v>
+        <v>0.6779279558565583</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531019844572494</v>
+        <v>0.6531538163818519</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.005980564408829</v>
+        <v>6.987080413416766</v>
       </c>
       <c r="E10" t="n">
-        <v>206.8690902623021</v>
+        <v>205.5869835476144</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2231645840629187</v>
+        <v>-0.2277176650586974</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653403780847349</v>
+        <v>0.965313631773961</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2311770947628692</v>
+        <v>-0.2359001857667955</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131648575036044</v>
+        <v>0.713158348956101</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371852409126868</v>
+        <v>1.371815727680373</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.79320372775466</v>
+        <v>6.778993355423449</v>
       </c>
       <c r="E11" t="n">
-        <v>366.4131120831735</v>
+        <v>369.8446700134149</v>
       </c>
       <c r="F11" t="n">
-        <v>1.046136472494112</v>
+        <v>1.033656514847074</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272157046861656</v>
+        <v>0.8272196790630383</v>
       </c>
       <c r="H11" t="n">
-        <v>1.264647741293792</v>
+        <v>1.249555034785752</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.662668247453301</v>
+        <v>0.6626546516283449</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092325106980687</v>
+        <v>1.092318970155812</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.55132761806443</v>
+        <v>6.521949856459533</v>
       </c>
       <c r="E12" t="n">
-        <v>106.407431747405</v>
+        <v>105.6794393883238</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2398207698074929</v>
+        <v>-0.2475301188036181</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6634744657968814</v>
+        <v>0.6632070792374435</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3614619434064438</v>
+        <v>-0.3732320214196576</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7878349913116708</v>
+        <v>0.788020700380742</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041589187787661</v>
+        <v>1.041425355082083</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.886979221194027</v>
+        <v>4.831677632315085</v>
       </c>
       <c r="E13" t="n">
-        <v>244.3281435026387</v>
+        <v>257.7080514834947</v>
       </c>
       <c r="F13" t="n">
-        <v>1.928552014967049</v>
+        <v>1.869233921602445</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8670983610430454</v>
+        <v>0.8662125258672767</v>
       </c>
       <c r="H13" t="n">
-        <v>2.224144458821448</v>
+        <v>2.157939149784188</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6013198623254322</v>
+        <v>0.6017168446109954</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038988877535312</v>
+        <v>1.038623145696201</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.690045613372703</v>
+        <v>4.683076576752126</v>
       </c>
       <c r="E14" t="n">
-        <v>97.33870521106051</v>
+        <v>97.46861162261516</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3847762102624862</v>
+        <v>-0.386026612693965</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571858740995347</v>
+        <v>0.8571833686104934</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4488830507930264</v>
+        <v>-0.4503430967398722</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601408766028532</v>
+        <v>0.7601397950336481</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298392734487572</v>
+        <v>1.298400198397051</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.310829476209205</v>
+        <v>4.307666835121771</v>
       </c>
       <c r="E15" t="n">
-        <v>263.4420301961471</v>
+        <v>247.2325536003746</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02656641407463556</v>
+        <v>0.02374240465935862</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7967046121350794</v>
+        <v>0.7966554196630761</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03334537502354924</v>
+        <v>0.02980260232133967</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166242196099794</v>
+        <v>0.7165991940118649</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137694862345076</v>
+        <v>1.137596371115973</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.216029636089911</v>
+        <v>4.20554114685407</v>
       </c>
       <c r="E16" t="n">
-        <v>235.3029551935135</v>
+        <v>229.8768881205022</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5766250573171603</v>
+        <v>0.5682196749445945</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624600137347983</v>
+        <v>0.9625077939160409</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5991158584132585</v>
+        <v>0.5903533234081635</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129537121067861</v>
+        <v>0.5129532361953253</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9837796986088272</v>
+        <v>0.9838375555407368</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.51366149218845</v>
+        <v>3.518289271203998</v>
       </c>
       <c r="E17" t="n">
-        <v>80.15029685637761</v>
+        <v>80.97471735549956</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1621592205307761</v>
+        <v>-0.1693150508984574</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7569616581117294</v>
+        <v>0.756755352274824</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.214223823350959</v>
+        <v>-0.2237381610708038</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7224028364056215</v>
+        <v>0.7224863016917131</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0896582422845</v>
+        <v>1.089498122575576</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.207887198132426</v>
+        <v>3.210031248092272</v>
       </c>
       <c r="E18" t="n">
-        <v>55.12139855726328</v>
+        <v>55.15496208029871</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.452042741627372</v>
+        <v>-0.4522058853363685</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519487452029018</v>
+        <v>0.7519489981536441</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6011616410176936</v>
+        <v>-0.6013783999270257</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641919133952103</v>
+        <v>0.7642015777598685</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145058461611578</v>
+        <v>1.145084886626593</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.018891856620596</v>
+        <v>3.016586317713119</v>
       </c>
       <c r="E19" t="n">
-        <v>97.22551696555348</v>
+        <v>97.09099559318673</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1444843055259737</v>
+        <v>0.1406645630379924</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4854014670701913</v>
+        <v>0.4852996219144791</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2976593919216164</v>
+        <v>0.2898509635822067</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7170136989886678</v>
+        <v>0.7170382538355502</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935304303165361</v>
+        <v>0.6934156615005238</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.655889394271015</v>
+        <v>2.653334759107451</v>
       </c>
       <c r="E20" t="n">
-        <v>111.2673094286417</v>
+        <v>111.1642081852065</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3034764455360498</v>
+        <v>-0.3039907970446515</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845750200871737</v>
+        <v>0.7845664778905054</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3868036042013301</v>
+        <v>-0.3874634025430241</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320618006665295</v>
+        <v>0.732030846412257</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144508984004</v>
+        <v>1.144459681968437</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.2735081730279</v>
+        <v>580.9642365216041</v>
       </c>
       <c r="E2" t="n">
-        <v>8019.477202993045</v>
+        <v>8045.657841928279</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6802046955106436</v>
+        <v>0.6819391139667732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018323248303904</v>
+        <v>0.5018344051850616</v>
       </c>
       <c r="H2" t="n">
-        <v>1.355442170331574</v>
+        <v>1.358892708273548</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.3747956107553</v>
+        <v>225.2158980720346</v>
       </c>
       <c r="E3" t="n">
-        <v>4286.510606260245</v>
+        <v>4314.433486767353</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2722874414388936</v>
+        <v>0.2727832983931244</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026699675961326</v>
+        <v>0.602671594140254</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4518019083064078</v>
+        <v>0.4526234537107488</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908199920159222</v>
+        <v>0.8908237739634387</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06982039449865</v>
+        <v>1.069823388762274</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.83529025253894</v>
+        <v>38.85997988061091</v>
       </c>
       <c r="E4" t="n">
-        <v>1914.736504699751</v>
+        <v>1910.473665761697</v>
       </c>
       <c r="F4" t="n">
-        <v>0.892942370442845</v>
+        <v>0.8968317319125021</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117223964668058</v>
+        <v>1.117230810303509</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7992509995148106</v>
+        <v>0.8027273537764923</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715354663873992</v>
+        <v>0.4715411709080634</v>
       </c>
       <c r="N4" t="n">
-        <v>1.04977439111158</v>
+        <v>1.049789171531205</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.31634060272207</v>
+        <v>37.2913721324714</v>
       </c>
       <c r="E5" t="n">
-        <v>283.5149832473697</v>
+        <v>284.6024778282916</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3350153537144025</v>
+        <v>-0.3346371565240859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663119019514719</v>
+        <v>0.5663173311248766</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5915739234156349</v>
+        <v>-0.5909004336127164</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367723300942082</v>
+        <v>0.7367838338591245</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314389466678707</v>
+        <v>0.8314564527579233</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.00410390640764</v>
+        <v>11.03605092898645</v>
       </c>
       <c r="E6" t="n">
-        <v>180.2502456488992</v>
+        <v>181.5201114334036</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2956469078091575</v>
+        <v>-0.2937948163986482</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7193385906104887</v>
+        <v>0.7193951398264802</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4109982582169653</v>
+        <v>-0.408391439049077</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499169471177488</v>
+        <v>0.7499060725072265</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07494908781917</v>
+        <v>1.075013546927136</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.09197098885017</v>
+        <v>10.1208862407058</v>
       </c>
       <c r="E7" t="n">
-        <v>290.8859640833167</v>
+        <v>292.7394562945915</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5432450951973771</v>
+        <v>-0.5399131237391799</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8099705399390968</v>
+        <v>0.8101800333551309</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6706973505952756</v>
+        <v>-0.6664112931829272</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6833132000093174</v>
+        <v>0.683210256824034</v>
       </c>
       <c r="N7" t="n">
-        <v>1.102885434385118</v>
+        <v>1.102999919780591</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.946060456043989</v>
+        <v>9.944956390969441</v>
       </c>
       <c r="E8" t="n">
-        <v>362.8121281350593</v>
+        <v>364.6488703466663</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3222172145376248</v>
+        <v>-0.3199345746732027</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176809390180492</v>
+        <v>1.176813690226725</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2738057813153624</v>
+        <v>-0.2718651026328257</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385566304963018</v>
+        <v>0.7385592592480811</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73193382519124</v>
+        <v>1.731939138382381</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.468319656118181</v>
+        <v>7.47413052501559</v>
       </c>
       <c r="E9" t="n">
-        <v>354.3535258748457</v>
+        <v>354.5538721881562</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4585464102903125</v>
+        <v>0.4607202486580262</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4834934085770315</v>
+        <v>0.4834653087776671</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9484026093341367</v>
+        <v>0.9529541009319848</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6779279558565583</v>
+        <v>0.6779314817724206</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531538163818519</v>
+        <v>0.6531165455751045</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.987080413416766</v>
+        <v>6.984953986095958</v>
       </c>
       <c r="E10" t="n">
-        <v>205.5869835476144</v>
+        <v>206.0868477904028</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2277176650586974</v>
+        <v>-0.2261533706586072</v>
       </c>
       <c r="G10" t="n">
-        <v>0.965313631773961</v>
+        <v>0.9653199059707187</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2359001857667955</v>
+        <v>-0.2342781592504186</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713158348956101</v>
+        <v>0.7131613571154007</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371815727680373</v>
+        <v>1.371824743540086</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.778993355423449</v>
+        <v>6.776738798516392</v>
       </c>
       <c r="E11" t="n">
-        <v>369.8446700134149</v>
+        <v>369.970653830074</v>
       </c>
       <c r="F11" t="n">
-        <v>1.033656514847074</v>
+        <v>1.040046075074955</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272196790630383</v>
+        <v>0.8272135768015039</v>
       </c>
       <c r="H11" t="n">
-        <v>1.249555034785752</v>
+        <v>1.257288449128684</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626546516283449</v>
+        <v>0.6626604221469528</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092318970155812</v>
+        <v>1.092315896130775</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.521949856459533</v>
+        <v>6.51262734862963</v>
       </c>
       <c r="E12" t="n">
-        <v>105.6794393883238</v>
+        <v>105.9892114258306</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2475301188036181</v>
+        <v>-0.2469526649265824</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6632070792374435</v>
+        <v>0.6632231112303909</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3732320214196576</v>
+        <v>-0.3723523211795854</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.788020700380742</v>
+        <v>0.788043248787398</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041425355082083</v>
+        <v>1.04147601249489</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.831677632315085</v>
+        <v>4.821146820473955</v>
       </c>
       <c r="E13" t="n">
-        <v>257.7080514834947</v>
+        <v>261.6337627893596</v>
       </c>
       <c r="F13" t="n">
-        <v>1.869233921602445</v>
+        <v>1.875630636582229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8662125258672767</v>
+        <v>0.8662902768919202</v>
       </c>
       <c r="H13" t="n">
-        <v>2.157939149784188</v>
+        <v>2.165129502909376</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6017168446109954</v>
+        <v>0.6017353370654198</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038623145696201</v>
+        <v>1.038743988806076</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.683076576752126</v>
+        <v>4.688351702916305</v>
       </c>
       <c r="E14" t="n">
-        <v>97.46861162261516</v>
+        <v>97.91958314367119</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.386026612693965</v>
+        <v>-0.3841507477623464</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571833686104934</v>
+        <v>0.8571884254440747</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4503430967398722</v>
+        <v>-0.4481520472740091</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601397950336481</v>
+        <v>0.7601427372228657</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298400198397051</v>
+        <v>1.29840750116073</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.307666835121771</v>
+        <v>4.309961486166221</v>
       </c>
       <c r="E15" t="n">
-        <v>247.2325536003746</v>
+        <v>247.3918144605227</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02374240465935862</v>
+        <v>0.02497764651847278</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966554196630761</v>
+        <v>0.7966760769297252</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02980260232133967</v>
+        <v>0.03135232403956829</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7165991940118649</v>
+        <v>0.7166155416235874</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137596371115973</v>
+        <v>1.137647105237863</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.20554114685407</v>
+        <v>4.225865491408979</v>
       </c>
       <c r="E16" t="n">
-        <v>229.8768881205022</v>
+        <v>229.7330955514416</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5682196749445945</v>
+        <v>0.5822354779688275</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9625077939160409</v>
+        <v>0.9624398189073736</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5903533234081635</v>
+        <v>0.6049578025874078</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129532361953253</v>
+        <v>0.5129899996439994</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9838375555407368</v>
+        <v>0.9838345024921006</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.518289271203998</v>
+        <v>3.519972234793209</v>
       </c>
       <c r="E17" t="n">
-        <v>80.97471735549956</v>
+        <v>80.78298026890047</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1693150508984574</v>
+        <v>-0.1661158372322786</v>
       </c>
       <c r="G17" t="n">
-        <v>0.756755352274824</v>
+        <v>0.7568387302353949</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2237381610708038</v>
+        <v>-0.2194864382543064</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7224863016917131</v>
+        <v>0.7224580820855997</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089498122575576</v>
+        <v>1.089571085291225</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.210031248092272</v>
+        <v>3.21293116520547</v>
       </c>
       <c r="E18" t="n">
-        <v>55.15496208029871</v>
+        <v>55.53194814436372</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4522058853363685</v>
+        <v>-0.4498389996938285</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519489981536441</v>
+        <v>0.751953570012122</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6013783999270257</v>
+        <v>-0.5982270949077039</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642015777598685</v>
+        <v>0.7642074780946612</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145084886626593</v>
+        <v>1.145095942896398</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.016586317713119</v>
+        <v>3.014788823619455</v>
       </c>
       <c r="E19" t="n">
-        <v>97.09099559318673</v>
+        <v>97.82242580611727</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1406645630379924</v>
+        <v>0.1425739969602229</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4852996219144791</v>
+        <v>0.4853484219871871</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2898509635822067</v>
+        <v>0.2937559709712763</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7170382538355502</v>
+        <v>0.7170294908762125</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934156615005238</v>
+        <v>0.6934740390840891</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.653334759107451</v>
+        <v>2.650301655672647</v>
       </c>
       <c r="E20" t="n">
-        <v>111.1642081852065</v>
+        <v>111.1541549013615</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3039907970446515</v>
+        <v>-0.3034764455360498</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845664778905054</v>
+        <v>0.7845750200871737</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3874634025430241</v>
+        <v>-0.3868036042013301</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732030846412257</v>
+        <v>0.7320453805636538</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144459681968437</v>
+        <v>1.144490121096121</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.9642365216041</v>
+        <v>581.0369773112604</v>
       </c>
       <c r="E2" t="n">
-        <v>8045.657841928279</v>
+        <v>8017.507378493138</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6819391139667732</v>
+        <v>0.6817569692433625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018344051850616</v>
+        <v>0.5018341149665085</v>
       </c>
       <c r="H2" t="n">
-        <v>1.358892708273548</v>
+        <v>1.358530536109251</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.2158980720346</v>
+        <v>225.278780085962</v>
       </c>
       <c r="E3" t="n">
-        <v>4314.433486767353</v>
+        <v>4293.714198129791</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2727832983931244</v>
+        <v>0.2729797846583681</v>
       </c>
       <c r="G3" t="n">
-        <v>0.602671594140254</v>
+        <v>0.6026722888913626</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4526234537107488</v>
+        <v>0.4529489569870954</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908237739634387</v>
+        <v>0.8908229785523335</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069823388762274</v>
+        <v>1.06982428549519</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.85997988061091</v>
+        <v>38.78613661937398</v>
       </c>
       <c r="E4" t="n">
-        <v>1910.473665761697</v>
+        <v>1901.96144755969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8968317319125021</v>
+        <v>0.892942370442845</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117230810303509</v>
+        <v>1.117223964668058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8027273537764923</v>
+        <v>0.7992509995148106</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715411709080634</v>
+        <v>0.471538674148192</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049789171531205</v>
+        <v>1.04977778774829</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.2913721324714</v>
+        <v>37.30121173750553</v>
       </c>
       <c r="E5" t="n">
-        <v>284.6024778282916</v>
+        <v>282.6250947922146</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3346371565240859</v>
+        <v>-0.3338805854433086</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663173311248766</v>
+        <v>0.5663294272989022</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5909004336127164</v>
+        <v>-0.5895518921482605</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367838338591245</v>
+        <v>0.7367716207013422</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314564527579233</v>
+        <v>0.8314609102048034</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.03605092898645</v>
+        <v>11.01038450354572</v>
       </c>
       <c r="E6" t="n">
-        <v>181.5201114334036</v>
+        <v>180.6718192768315</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2937948163986482</v>
+        <v>-0.2956469078091575</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7193951398264802</v>
+        <v>0.7193385906104887</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.408391439049077</v>
+        <v>-0.4109982582169653</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499060725072265</v>
+        <v>0.7499509659408715</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075013546927136</v>
+        <v>1.074994016504606</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.1208862407058</v>
+        <v>10.12966298857575</v>
       </c>
       <c r="E7" t="n">
-        <v>292.7394562945915</v>
+        <v>293.3459883544952</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5399131237391799</v>
+        <v>-0.5394742128277675</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8101800333551309</v>
+        <v>0.8102112238498623</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6664112931829272</v>
+        <v>-0.6658439144601825</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.683210256824034</v>
+        <v>0.6831806635698398</v>
       </c>
       <c r="N7" t="n">
-        <v>1.102999919780591</v>
+        <v>1.102995242916918</v>
       </c>
     </row>
     <row r="8">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.944956390969441</v>
+        <v>9.944263473832679</v>
       </c>
       <c r="E8" t="n">
-        <v>364.6488703466663</v>
+        <v>362.2241264101905</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3199345746732027</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385592592480811</v>
+        <v>0.7385591881830516</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731939138382381</v>
+        <v>1.731939973340704</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.47413052501559</v>
+        <v>7.469772294316507</v>
       </c>
       <c r="E9" t="n">
-        <v>354.5538721881562</v>
+        <v>350.6876476698498</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4607202486580262</v>
+        <v>0.4609618409992995</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4834653087776671</v>
+        <v>0.483462386067533</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9529541009319848</v>
+        <v>0.9534595746915242</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6779314817724206</v>
+        <v>0.6779407334384245</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531165455751045</v>
+        <v>0.6531218879417716</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.984953986095958</v>
+        <v>6.981277584292516</v>
       </c>
       <c r="E10" t="n">
-        <v>206.0868477904028</v>
+        <v>205.4112716201184</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2261533706586072</v>
+        <v>-0.2274333124051535</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653199059707187</v>
+        <v>0.9653145450113569</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2342781592504186</v>
+        <v>-0.2356053926468888</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131613571154007</v>
+        <v>0.7131604337018697</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371824743540086</v>
+        <v>1.371816142122913</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.776738798516392</v>
+        <v>6.772144546682927</v>
       </c>
       <c r="E11" t="n">
-        <v>369.970653830074</v>
+        <v>371.550975734807</v>
       </c>
       <c r="F11" t="n">
-        <v>1.040046075074955</v>
+        <v>1.033656514847074</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272135768015039</v>
+        <v>0.8272196790630383</v>
       </c>
       <c r="H11" t="n">
-        <v>1.257288449128684</v>
+        <v>1.249555034785752</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626604221469528</v>
+        <v>0.662646194492767</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092315896130775</v>
+        <v>1.092301132969474</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.51262734862963</v>
+        <v>6.617654993745368</v>
       </c>
       <c r="E12" t="n">
-        <v>105.9892114258306</v>
+        <v>106.187140241436</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2469526649265824</v>
+        <v>-0.2482998684795411</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6632231112303909</v>
+        <v>0.663186718205116</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3723523211795854</v>
+        <v>-0.3744041635085111</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.788043248787398</v>
+        <v>0.788075298296893</v>
       </c>
       <c r="N12" t="n">
-        <v>1.04147601249489</v>
+        <v>1.041461820129376</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.821146820473955</v>
+        <v>4.797222408888715</v>
       </c>
       <c r="E13" t="n">
-        <v>261.6337627893596</v>
+        <v>264.8413765658671</v>
       </c>
       <c r="F13" t="n">
-        <v>1.875630636582229</v>
+        <v>1.850067220767729</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8662902768919202</v>
+        <v>0.8660055072866962</v>
       </c>
       <c r="H13" t="n">
-        <v>2.165129502909376</v>
+        <v>2.136322696796954</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6017353370654198</v>
+        <v>0.601898460184633</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038743988806076</v>
+        <v>1.038684628648775</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.688351702916305</v>
+        <v>4.686559005247719</v>
       </c>
       <c r="E14" t="n">
-        <v>97.91958314367119</v>
+        <v>97.59902037608396</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3841507477623464</v>
+        <v>-0.3854014985997186</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571884254440747</v>
+        <v>0.8571841884866382</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4481520472740091</v>
+        <v>-0.4496134013859336</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601427372228657</v>
+        <v>0.7601401384284179</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29840750116073</v>
+        <v>1.298397395199746</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.309961486166221</v>
+        <v>4.304482113186347</v>
       </c>
       <c r="E15" t="n">
-        <v>247.3918144605227</v>
+        <v>244.4802647728864</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02497764651847278</v>
+        <v>0.02180213513318563</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966760769297252</v>
+        <v>0.7966256753254912</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03135232403956829</v>
+        <v>0.02736810500650453</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166155416235874</v>
+        <v>0.7166472777133975</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137647105237863</v>
+        <v>1.137626168792273</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.225865491408979</v>
+        <v>4.219085510399428</v>
       </c>
       <c r="E16" t="n">
-        <v>229.7330955514416</v>
+        <v>227.3171917215808</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5822354779688275</v>
+        <v>0.5766250573171603</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624398189073736</v>
+        <v>0.9624600137347983</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6049578025874078</v>
+        <v>0.5991158584132585</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129899996439994</v>
+        <v>0.5129709394506199</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9838345024921006</v>
+        <v>0.9838191599671248</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.519972234793209</v>
+        <v>3.516393839294078</v>
       </c>
       <c r="E17" t="n">
-        <v>80.78298026890047</v>
+        <v>80.65192155359253</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1661158372322786</v>
+        <v>-0.1674335685159767</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7568387302353949</v>
+        <v>0.7568026494081638</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2194864382543064</v>
+        <v>-0.2212380845216562</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7224580820855997</v>
+        <v>0.7224824091506851</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089571085291225</v>
+        <v>1.089556459174806</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.21293116520547</v>
+        <v>3.218467324741882</v>
       </c>
       <c r="E18" t="n">
-        <v>55.53194814436372</v>
+        <v>55.06293085985021</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4498389996938285</v>
+        <v>-0.4487770749928481</v>
       </c>
       <c r="G18" t="n">
-        <v>0.751953570012122</v>
+        <v>0.7519613650459236</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5982270949077039</v>
+        <v>-0.596808687059927</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642074780946612</v>
+        <v>0.7642059906577289</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145095942896398</v>
+        <v>1.145106246811477</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.014788823619455</v>
+        <v>3.020143663001203</v>
       </c>
       <c r="E19" t="n">
-        <v>97.82242580611727</v>
+        <v>97.34815397985832</v>
       </c>
       <c r="F19" t="n">
         <v>0.1425739969602229</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7170294908762125</v>
+        <v>0.7170234105379135</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934740390840891</v>
+        <v>0.6934685595371944</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.650301655672647</v>
+        <v>2.647474623968835</v>
       </c>
       <c r="E20" t="n">
-        <v>111.1541549013615</v>
+        <v>110.778793927204</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3034764455360498</v>
+        <v>-0.3050191876741568</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845750200871737</v>
+        <v>0.7845509143022783</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3868036042013301</v>
+        <v>-0.3887818905232153</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320453805636538</v>
+        <v>0.7320583490224113</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144490121096121</v>
+        <v>1.144475893366634</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.0369773112604</v>
+        <v>581.1670725417108</v>
       </c>
       <c r="E2" t="n">
-        <v>8017.507378493138</v>
+        <v>7902.556180492243</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6817569692433625</v>
+        <v>0.6823770585028441</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018341149665085</v>
+        <v>0.5018351718640497</v>
       </c>
       <c r="H2" t="n">
-        <v>1.358530536109251</v>
+        <v>1.359763318238891</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.278780085962</v>
+        <v>225.1012131846209</v>
       </c>
       <c r="E3" t="n">
-        <v>4293.714198129791</v>
+        <v>4288.48366983811</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2729797846583681</v>
+        <v>0.2716606791675473</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026722888913626</v>
+        <v>0.6026681714918881</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4529489569870954</v>
+        <v>0.4507632757427009</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908229785523335</v>
+        <v>0.8908251710305661</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06982428549519</v>
+        <v>1.069817356463372</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.78613661937398</v>
+        <v>38.88982636281212</v>
       </c>
       <c r="E4" t="n">
-        <v>1901.96144755969</v>
+        <v>1869.924198407988</v>
       </c>
       <c r="F4" t="n">
-        <v>0.892942370442845</v>
+        <v>0.8986003463043306</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117223964668058</v>
+        <v>1.117234826936516</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7992509995148106</v>
+        <v>0.8043074961853037</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.471538674148192</v>
+        <v>0.4715434487364553</v>
       </c>
       <c r="N4" t="n">
-        <v>1.04977778774829</v>
+        <v>1.049796413003993</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.30121173750553</v>
+        <v>37.30076942087705</v>
       </c>
       <c r="E5" t="n">
-        <v>282.6250947922146</v>
+        <v>283.0884420772275</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3338805854433086</v>
+        <v>-0.3346371565240859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663294272989022</v>
+        <v>0.5663173311248766</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5895518921482605</v>
+        <v>-0.5909004336127164</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367716207013422</v>
+        <v>0.7367878426031881</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314609102048034</v>
+        <v>0.8314597063382598</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.01038450354572</v>
+        <v>11.02364956476757</v>
       </c>
       <c r="E6" t="n">
-        <v>180.6718192768315</v>
+        <v>179.9931861657879</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2956469078091575</v>
+        <v>-0.2941035908237466</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7193385906104887</v>
+        <v>0.7193852240056364</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4109982582169653</v>
+        <v>-0.4088262880715524</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499509659408715</v>
+        <v>0.7499250663229017</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074994016504606</v>
+        <v>1.075024314896549</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.12966298857575</v>
+        <v>10.12794471431926</v>
       </c>
       <c r="E7" t="n">
-        <v>293.3459883544952</v>
+        <v>291.3907089323219</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5394742128277675</v>
+        <v>-0.540264169897489</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8102112238498623</v>
+        <v>0.8101556878829619</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6658439144601825</v>
+        <v>-0.6668646261180575</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6831806635698398</v>
+        <v>0.6832431190923055</v>
       </c>
       <c r="N7" t="n">
-        <v>1.102995242916918</v>
+        <v>1.103018142557538</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.944263473832679</v>
+        <v>9.958090680913696</v>
       </c>
       <c r="E8" t="n">
-        <v>362.2241264101905</v>
+        <v>362.5559641482149</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3199345746732027</v>
+        <v>-0.3187924666572269</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176813690226725</v>
+        <v>1.176818432276672</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2718651026328257</v>
+        <v>-0.2708935022716218</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385591881830516</v>
+        <v>0.7385608227165149</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731939973340704</v>
+        <v>1.731947137746009</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.469772294316507</v>
+        <v>7.455980210043395</v>
       </c>
       <c r="E9" t="n">
-        <v>350.6876476698498</v>
+        <v>344.6321862988048</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4609618409992995</v>
+        <v>0.4558907017477618</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483462386067533</v>
+        <v>0.4835321409376281</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9534595746915242</v>
+        <v>0.9428343292003999</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6779407334384245</v>
+        <v>0.6778062198438398</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531218879417716</v>
+        <v>0.6530851383025812</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.981277584292516</v>
+        <v>6.984596132044562</v>
       </c>
       <c r="E10" t="n">
-        <v>205.4112716201184</v>
+        <v>204.3355781797353</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2274333124051535</v>
+        <v>-0.2268645210726652</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653145450113569</v>
+        <v>0.9653166748545496</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2356053926468888</v>
+        <v>-0.2350156451061496</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131604337018697</v>
+        <v>0.7131616699340662</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371816142122913</v>
+        <v>1.371818657702552</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.772144546682927</v>
+        <v>6.768707260931334</v>
       </c>
       <c r="E11" t="n">
-        <v>371.550975734807</v>
+        <v>368.1436609864452</v>
       </c>
       <c r="F11" t="n">
-        <v>1.033656514847074</v>
+        <v>1.033352387085667</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272196790630383</v>
+        <v>0.8272201826574204</v>
       </c>
       <c r="H11" t="n">
-        <v>1.249555034785752</v>
+        <v>1.249186623766907</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.662646194492767</v>
+        <v>0.6626413974332728</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092301132969474</v>
+        <v>1.092291590055424</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.617654993745368</v>
+        <v>6.606053137075683</v>
       </c>
       <c r="E12" t="n">
-        <v>106.187140241436</v>
+        <v>105.2028739958746</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2482998684795411</v>
+        <v>-0.2486846623636505</v>
       </c>
       <c r="G12" t="n">
-        <v>0.663186718205116</v>
+        <v>0.663176972701223</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3744041635085111</v>
+        <v>-0.37498989349814</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.788075298296893</v>
+        <v>0.7880968403746058</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041461820129376</v>
+        <v>1.041472790465589</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.797222408888715</v>
+        <v>4.802482342962301</v>
       </c>
       <c r="E13" t="n">
-        <v>264.8413765658671</v>
+        <v>267.2503832655229</v>
       </c>
       <c r="F13" t="n">
-        <v>1.850067220767729</v>
+        <v>1.862841111345555</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8660055072866962</v>
+        <v>0.8661391465283728</v>
       </c>
       <c r="H13" t="n">
-        <v>2.136322696796954</v>
+        <v>2.150741158406391</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.601898460184633</v>
+        <v>0.6018409063165412</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038684628648775</v>
+        <v>1.038743392589646</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.686559005247719</v>
+        <v>4.684091304721367</v>
       </c>
       <c r="E14" t="n">
-        <v>97.59902037608396</v>
+        <v>97.34544611935006</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3854014985997186</v>
+        <v>-0.386026612693965</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571841884866382</v>
+        <v>0.8571833686104934</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4496134013859336</v>
+        <v>-0.4503430967398722</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601401384284179</v>
+        <v>0.7601364642084683</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298397395199746</v>
+        <v>1.29838714288125</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.304482113186347</v>
+        <v>4.300279335319895</v>
       </c>
       <c r="E15" t="n">
-        <v>244.4802647728864</v>
+        <v>238.8696170673223</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02180213513318563</v>
+        <v>0.02250757100397216</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966256753254912</v>
+        <v>0.7966361071957424</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02736810500650453</v>
+        <v>0.0282532649482856</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166472777133975</v>
+        <v>0.7166498889508467</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137626168792273</v>
+        <v>1.137642815340027</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.219085510399428</v>
+        <v>4.19495490283794</v>
       </c>
       <c r="E16" t="n">
-        <v>227.3171917215808</v>
+        <v>219.4098571409742</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5766250573171603</v>
+        <v>0.5668199753190271</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624600137347983</v>
+        <v>0.9625177973637743</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5991158584132585</v>
+        <v>0.5888929813780918</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129709394506199</v>
+        <v>0.5129137940686769</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9838191599671248</v>
+        <v>0.9837665492250963</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.516393839294078</v>
+        <v>3.525709715646309</v>
       </c>
       <c r="E17" t="n">
-        <v>80.65192155359253</v>
+        <v>80.46616622045957</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1674335685159767</v>
+        <v>-0.1653625916476025</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7568026494081638</v>
+        <v>0.756860446895126</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2212380845216562</v>
+        <v>-0.2184849166394817</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7224824091506851</v>
+        <v>0.7224521076847211</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089556459174806</v>
+        <v>1.089591674197587</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.218467324741882</v>
+        <v>3.216437491586324</v>
       </c>
       <c r="E18" t="n">
-        <v>55.06293085985021</v>
+        <v>54.66753875374237</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4487770749928481</v>
+        <v>-0.4495939899468893</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519613650459236</v>
+        <v>0.7519550531801662</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.596808687059927</v>
+        <v>-0.5979000846466389</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642059906577289</v>
+        <v>0.7642082750611439</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145106246811477</v>
+        <v>1.145097646264622</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.020143663001203</v>
+        <v>3.030673892642888</v>
       </c>
       <c r="E19" t="n">
-        <v>97.34815397985832</v>
+        <v>98.08285721630969</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1425739969602229</v>
+        <v>0.1502204724882341</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4853484219871871</v>
+        <v>0.4855860579126721</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2937559709712763</v>
+        <v>0.3093591136738316</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7170234105379135</v>
+        <v>0.7167367490179032</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934685595371944</v>
+        <v>0.6935292542847784</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.647474623968835</v>
+        <v>2.647509612197937</v>
       </c>
       <c r="E20" t="n">
-        <v>110.778793927204</v>
+        <v>113.0434015126727</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3050191876741568</v>
+        <v>-0.3045050444356187</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845509143022783</v>
+        <v>0.7845584426236817</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3887818905232153</v>
+        <v>-0.388122831764206</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320583490224113</v>
+        <v>0.732059941420989</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144475893366634</v>
+        <v>1.14448695458123</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.1670725417108</v>
+        <v>581.4967855496064</v>
       </c>
       <c r="E2" t="n">
-        <v>7902.556180492243</v>
+        <v>7843.250861730003</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6823770585028441</v>
+        <v>0.6841524101667367</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018351718640497</v>
+        <v>0.5018392761646596</v>
       </c>
       <c r="H2" t="n">
-        <v>1.359763318238891</v>
+        <v>1.363289887143584</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.1012131846209</v>
+        <v>225.5649174385043</v>
       </c>
       <c r="E3" t="n">
-        <v>4288.48366983811</v>
+        <v>4317.632292809109</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2716606791675473</v>
+        <v>0.2756940158489758</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026681714918881</v>
+        <v>0.6026848006235846</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4507632757427009</v>
+        <v>0.4574431204565326</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908251710305661</v>
+        <v>0.8908247948370147</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069817356463372</v>
+        <v>1.069837673866588</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.88982636281212</v>
+        <v>38.94944385351001</v>
       </c>
       <c r="E4" t="n">
-        <v>1869.924198407988</v>
+        <v>1846.406088736985</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8986003463043306</v>
+        <v>0.9032008562348812</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117234826936516</v>
+        <v>1.117247917194411</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8043074961853037</v>
+        <v>0.8084157887740474</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715434487364553</v>
+        <v>0.4715538487915281</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049796413003993</v>
+        <v>1.049823280939213</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.30076942087705</v>
+        <v>37.29794620676635</v>
       </c>
       <c r="E5" t="n">
-        <v>283.0884420772275</v>
+        <v>287.5204834642458</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3346371565240859</v>
+        <v>-0.3338805854433086</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663173311248766</v>
+        <v>0.5663294272989022</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5909004336127164</v>
+        <v>-0.5895518921482605</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367878426031881</v>
+        <v>0.7367962347859301</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314597063382598</v>
+        <v>0.8314801361729049</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.02364956476757</v>
+        <v>11.04188195016334</v>
       </c>
       <c r="E6" t="n">
-        <v>179.9931861657879</v>
+        <v>180.2377139134628</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2941035908237466</v>
+        <v>-0.2922503895353402</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7193852240056364</v>
+        <v>0.7194476641931766</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4088262880715524</v>
+        <v>-0.406214939710846</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499250663229017</v>
+        <v>0.7499176218605886</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075024314896549</v>
+        <v>1.07509815793668</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.12794471431926</v>
+        <v>10.12626959507426</v>
       </c>
       <c r="E7" t="n">
-        <v>291.3907089323219</v>
+        <v>286.2398798566263</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.540264169897489</v>
+        <v>-0.5408783239834409</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8101556878829619</v>
+        <v>0.8101143816044588</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6668646261180575</v>
+        <v>-0.6676567362157096</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6832431190923055</v>
+        <v>0.683329511301023</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103018142557538</v>
+        <v>1.103092346040429</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.958090680913696</v>
+        <v>10.00268928849212</v>
       </c>
       <c r="E8" t="n">
-        <v>362.5559641482149</v>
+        <v>363.5461089393099</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3187924666572269</v>
+        <v>-0.3146002498350767</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176818432276672</v>
+        <v>1.17685060348873</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2708935022716218</v>
+        <v>-0.2673238632860076</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385608227165149</v>
+        <v>0.73856593148683</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731947137746009</v>
+        <v>1.731992300063223</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.455980210043395</v>
+        <v>7.474953245093864</v>
       </c>
       <c r="E9" t="n">
-        <v>344.6321862988048</v>
+        <v>271.8163664091087</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4558907017477618</v>
+        <v>0.4619283198159134</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4835321409376281</v>
+        <v>0.483451094240932</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9428343292003999</v>
+        <v>0.9554809686410752</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6778062198438398</v>
+        <v>0.6779055548108391</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6530851383025812</v>
+        <v>0.6530660269758813</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.984596132044562</v>
+        <v>7.001592730999998</v>
       </c>
       <c r="E10" t="n">
-        <v>204.3355781797353</v>
+        <v>202.7305018773293</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2268645210726652</v>
+        <v>-0.2220251688387778</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653166748545496</v>
+        <v>0.9653511093567646</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2350156451061496</v>
+        <v>-0.2299942131798224</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131616699340662</v>
+        <v>0.7131671791075783</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371818657702552</v>
+        <v>1.371866970576539</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.768707260931334</v>
+        <v>6.775613191625101</v>
       </c>
       <c r="E11" t="n">
-        <v>368.1436609864452</v>
+        <v>364.3398312114437</v>
       </c>
       <c r="F11" t="n">
-        <v>1.033352387085667</v>
+        <v>1.039132944599916</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272201826574204</v>
+        <v>0.8272139257054762</v>
       </c>
       <c r="H11" t="n">
-        <v>1.249186623766907</v>
+        <v>1.256184056275054</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626413974332728</v>
+        <v>0.6626496637907309</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092291590055424</v>
+        <v>1.092288020860066</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.606053137075683</v>
+        <v>6.514726705846299</v>
       </c>
       <c r="E12" t="n">
-        <v>105.2028739958746</v>
+        <v>105.1405055998333</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2486846623636505</v>
+        <v>-0.2456048007343921</v>
       </c>
       <c r="G12" t="n">
-        <v>0.663176972701223</v>
+        <v>0.6632630563204768</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.37498989349814</v>
+        <v>-0.3702977248528075</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7880968403746058</v>
+        <v>0.7880561368598558</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041472790465589</v>
+        <v>1.041545663544827</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.802482342962301</v>
+        <v>4.825779034985377</v>
       </c>
       <c r="E13" t="n">
-        <v>267.2503832655229</v>
+        <v>270.5216981177854</v>
       </c>
       <c r="F13" t="n">
-        <v>1.862841111345555</v>
+        <v>1.886834271724736</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8661391465283728</v>
+        <v>0.8664368569766452</v>
       </c>
       <c r="H13" t="n">
-        <v>2.150741158406391</v>
+        <v>2.177693915640521</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6018409063165412</v>
+        <v>0.601740567114594</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038743392589646</v>
+        <v>1.038918694588275</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.684091304721367</v>
+        <v>4.692525072398977</v>
       </c>
       <c r="E14" t="n">
-        <v>97.34544611935006</v>
+        <v>97.59484216200835</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.386026612693965</v>
+        <v>-0.3835251111792812</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571833686104934</v>
+        <v>0.8571918425125286</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4503430967398722</v>
+        <v>-0.4474203931469118</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601364642084683</v>
+        <v>0.760145539831214</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29838714288125</v>
+        <v>1.298404861503515</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.300279335319895</v>
+        <v>4.300188072331889</v>
       </c>
       <c r="E15" t="n">
-        <v>238.8696170673223</v>
+        <v>226.9199392652764</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02250757100397216</v>
+        <v>0.02286033895337147</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966361071957424</v>
+        <v>0.7966414878133019</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0282532649482856</v>
+        <v>0.02869589307496491</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166498889508467</v>
+        <v>0.7166733616806845</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137642815340027</v>
+        <v>1.137678456514694</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.19495490283794</v>
+        <v>4.229110855721067</v>
       </c>
       <c r="E16" t="n">
-        <v>219.4098571409742</v>
+        <v>214.586979886361</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5668199753190271</v>
+        <v>0.5864468742311217</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9625177973637743</v>
+        <v>0.9624307940193959</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5888929813780918</v>
+        <v>0.6093392666520425</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129137940686769</v>
+        <v>0.5129910757712959</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9837665492250963</v>
+        <v>0.9838177915302055</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.525709715646309</v>
+        <v>3.538927740048555</v>
       </c>
       <c r="E17" t="n">
-        <v>80.46616622045957</v>
+        <v>77.00715189481288</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1653625916476025</v>
+        <v>-0.1591412144338558</v>
       </c>
       <c r="G17" t="n">
-        <v>0.756860446895126</v>
+        <v>0.7570700976146764</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2184849166394817</v>
+        <v>-0.2102067099668403</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7224521076847211</v>
+        <v>0.7223432773503888</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089591674197587</v>
+        <v>1.089720397483459</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.216437491586324</v>
+        <v>3.221041951079674</v>
       </c>
       <c r="E18" t="n">
-        <v>54.66753875374237</v>
+        <v>54.97926723154313</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4495939899468893</v>
+        <v>-0.4486953652433614</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519550531801662</v>
+        <v>0.7519621119826621</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5979000846466389</v>
+        <v>-0.5966994321832361</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642082750611439</v>
+        <v>0.7642123882459377</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145097646264622</v>
+        <v>1.145105193560372</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.030673892642888</v>
+        <v>3.037952639422618</v>
       </c>
       <c r="E19" t="n">
-        <v>98.08285721630969</v>
+        <v>99.41654803558667</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1502204724882341</v>
+        <v>0.1530915001125934</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4855860579126721</v>
+        <v>0.4856926620423441</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3093591136738316</v>
+        <v>0.3152024151833829</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7167367490179032</v>
+        <v>0.7166822163239569</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935292542847784</v>
+        <v>0.6936230582529739</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.647509612197937</v>
+        <v>2.650894873577625</v>
       </c>
       <c r="E20" t="n">
-        <v>113.0434015126727</v>
+        <v>113.1512178163698</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3045050444356187</v>
+        <v>-0.3029619899445773</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845584426236817</v>
+        <v>0.7845840691971289</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.388122831764206</v>
+        <v>-0.3861434380825509</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732059941420989</v>
+        <v>0.7320652693478659</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14448695458123</v>
+        <v>1.144523307008724</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.4967855496064</v>
+        <v>582.7544522136654</v>
       </c>
       <c r="E2" t="n">
-        <v>7843.250861730003</v>
+        <v>8003.994589995848</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6841524101667367</v>
+        <v>0.6884355200096792</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018392761646596</v>
+        <v>0.5018557503066514</v>
       </c>
       <c r="H2" t="n">
-        <v>1.363289887143584</v>
+        <v>1.371779678899806</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.5649174385043</v>
+        <v>226.4978850122549</v>
       </c>
       <c r="E3" t="n">
-        <v>4317.632292809109</v>
+        <v>4468.134368127142</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2756940158489758</v>
+        <v>0.2818865051403274</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6026848006235846</v>
+        <v>0.6027336518849628</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4574431204565326</v>
+        <v>0.4676800511449261</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908247948370147</v>
+        <v>0.8908265200897388</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069837673866588</v>
+        <v>1.069891340931289</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.94944385351001</v>
+        <v>39.09496347763527</v>
       </c>
       <c r="E4" t="n">
-        <v>1846.406088736985</v>
+        <v>1853.698893099261</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9032008562348812</v>
+        <v>0.910638888025272</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117247917194411</v>
+        <v>1.117277139466659</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8084157887740474</v>
+        <v>0.8150519292464646</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715538487915281</v>
+        <v>0.471586499137125</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049823280939213</v>
+        <v>1.049888965992864</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.29794620676635</v>
+        <v>37.42219968385646</v>
       </c>
       <c r="E5" t="n">
-        <v>287.5204834642458</v>
+        <v>293.7315632147324</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3338805854433086</v>
+        <v>-0.3316094596880412</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663294272989022</v>
+        <v>0.5663756174058356</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5895518921482605</v>
+        <v>-0.5854938833823896</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367962347859301</v>
+        <v>0.7368195603170182</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314801361729049</v>
+        <v>0.8315469796575057</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.04188195016334</v>
+        <v>11.07180572898323</v>
       </c>
       <c r="E6" t="n">
-        <v>180.2377139134628</v>
+        <v>180.7125948603268</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2922503895353402</v>
+        <v>-0.2910141827973038</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7194476641931766</v>
+        <v>0.7194932174782499</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.406214939710846</v>
+        <v>-0.4044710578610856</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499176218605886</v>
+        <v>0.7499918427640597</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07509815793668</v>
+        <v>1.075237344003793</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.12626959507426</v>
+        <v>10.14721019673282</v>
       </c>
       <c r="E7" t="n">
-        <v>286.2398798566263</v>
+        <v>289.5383887362599</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5408783239834409</v>
+        <v>-0.5400886559947164</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8101143816044588</v>
+        <v>0.8101677931795085</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6676567362157096</v>
+        <v>-0.6666380230632659</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.683329511301023</v>
+        <v>0.6834304878206696</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103092346040429</v>
+        <v>1.103291871759845</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.00268928849212</v>
+        <v>10.08909081938826</v>
       </c>
       <c r="E8" t="n">
-        <v>363.5461089393099</v>
+        <v>381.2325441538234</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3146002498350767</v>
+        <v>-0.3084899234446885</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17685060348873</v>
+        <v>1.17693886537381</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2673238632860076</v>
+        <v>-0.2621121049874655</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.73856593148683</v>
+        <v>0.7385855332746674</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731992300063223</v>
+        <v>1.732111306849911</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.474953245093864</v>
+        <v>7.485704389441723</v>
       </c>
       <c r="E9" t="n">
-        <v>271.8163664091087</v>
+        <v>268.6430353706726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4619283198159134</v>
+        <v>0.4631366645412711</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483451094240932</v>
+        <v>0.4834378772907187</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9554809686410752</v>
+        <v>0.9580065739506809</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6779055548108391</v>
+        <v>0.6778308852670237</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6530660269758813</v>
+        <v>0.6529548065063501</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.001592730999998</v>
+        <v>7.055250689731877</v>
       </c>
       <c r="E10" t="n">
-        <v>202.7305018773293</v>
+        <v>208.6510911796404</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2220251688387778</v>
+        <v>-0.2176056174568938</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653511093567646</v>
+        <v>0.9654079728962262</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2299942131798224</v>
+        <v>-0.2254027556910229</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131671791075783</v>
+        <v>0.7131905590399955</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371866970576539</v>
+        <v>1.371947718982633</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.775613191625101</v>
+        <v>6.809238763649872</v>
       </c>
       <c r="E11" t="n">
-        <v>364.3398312114437</v>
+        <v>365.7521404107065</v>
       </c>
       <c r="F11" t="n">
-        <v>1.039132944599916</v>
+        <v>1.048574023635426</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272139257054762</v>
+        <v>0.8272187246904937</v>
       </c>
       <c r="H11" t="n">
-        <v>1.256184056275054</v>
+        <v>1.267589807070376</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626496637907309</v>
+        <v>0.6626655027919898</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092288020860066</v>
+        <v>1.092284609234872</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.514726705846299</v>
+        <v>6.543495773248661</v>
       </c>
       <c r="E12" t="n">
-        <v>105.1405055998333</v>
+        <v>106.157787199591</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2456048007343921</v>
+        <v>-0.2413643611853407</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6632630563204768</v>
+        <v>0.6634117151971058</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3702977248528075</v>
+        <v>-0.3638228805073619</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7880561368598558</v>
+        <v>0.7880417483246298</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041545663544827</v>
+        <v>1.041725889528061</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.825779034985377</v>
+        <v>4.86743360074379</v>
       </c>
       <c r="E13" t="n">
-        <v>270.5216981177854</v>
+        <v>284.116587189754</v>
       </c>
       <c r="F13" t="n">
-        <v>1.886834271724736</v>
+        <v>1.909277296743646</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8664368569766452</v>
+        <v>0.8667701433096108</v>
       </c>
       <c r="H13" t="n">
-        <v>2.177693915640521</v>
+        <v>2.202749265743515</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.601740567114594</v>
+        <v>0.6017598478504416</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038918694588275</v>
+        <v>1.039317511537107</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.692525072398977</v>
+        <v>4.710207132702939</v>
       </c>
       <c r="E14" t="n">
-        <v>97.59484216200835</v>
+        <v>99.39742673171394</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3835251111792812</v>
+        <v>-0.3810208256140726</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571918425125286</v>
+        <v>0.8572141677790761</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4474203931469118</v>
+        <v>-0.4444873170974823</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.760145539831214</v>
+        <v>0.7601593333700285</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298404861503515</v>
+        <v>1.298419615469433</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.300188072331889</v>
+        <v>4.326039828770958</v>
       </c>
       <c r="E15" t="n">
-        <v>226.9199392652764</v>
+        <v>232.2778170586694</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02286033895337147</v>
+        <v>0.02833250176928681</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7966414878133019</v>
+        <v>0.7967389246881408</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02869589307496491</v>
+        <v>0.03556058439140112</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166733616806845</v>
+        <v>0.7166975516015746</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137678456514694</v>
+        <v>1.137818658530361</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.229110855721067</v>
+        <v>4.258580604244105</v>
       </c>
       <c r="E16" t="n">
-        <v>214.586979886361</v>
+        <v>214.5130743897528</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5864468742311217</v>
+        <v>0.5892561748210845</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624307940193959</v>
+        <v>0.9624276923900187</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6093392666520425</v>
+        <v>0.6122602035252863</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129910757712959</v>
+        <v>0.5129788484105655</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9838177915302055</v>
+        <v>0.9837588769661374</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.538927740048555</v>
+        <v>3.568103454252245</v>
       </c>
       <c r="E17" t="n">
-        <v>77.00715189481288</v>
+        <v>78.08012737744129</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1591412144338558</v>
+        <v>-0.1542306208162745</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7570700976146764</v>
+        <v>0.7572735597123128</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2102067099668403</v>
+        <v>-0.2036656619503083</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7223432773503888</v>
+        <v>0.7223495709382456</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089720397483459</v>
+        <v>1.089986974557571</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.221041951079674</v>
+        <v>3.229418976648006</v>
       </c>
       <c r="E18" t="n">
-        <v>54.97926723154313</v>
+        <v>55.12691939702714</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4486953652433614</v>
+        <v>-0.4483684930672933</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519621119826621</v>
+        <v>0.7519653101814544</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5966994321832361</v>
+        <v>-0.5962622038496682</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642123882459377</v>
+        <v>0.7642165125545283</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145105193560372</v>
+        <v>1.145078653692251</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.037952639422618</v>
+        <v>3.03310666143638</v>
       </c>
       <c r="E19" t="n">
-        <v>99.41654803558667</v>
+        <v>99.24277018807952</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1530915001125934</v>
+        <v>0.1511772638030207</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4856926620423441</v>
+        <v>0.4856205332287487</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3152024151833829</v>
+        <v>0.3113073963283375</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7166822163239569</v>
+        <v>0.7169587612888031</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6936230582529739</v>
+        <v>0.6937648831309552</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.650894873577625</v>
+        <v>2.663794345678751</v>
       </c>
       <c r="E20" t="n">
-        <v>113.1512178163698</v>
+        <v>114.2796471721575</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3029619899445773</v>
+        <v>-0.2998730725984257</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845840691971289</v>
+        <v>0.7846490079849733</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3861434380825509</v>
+        <v>-0.3821747935022796</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320652693478659</v>
+        <v>0.7320912953031552</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144523307008724</v>
+        <v>1.144621155108923</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>582.7544522136654</v>
+        <v>585.4508999108632</v>
       </c>
       <c r="E2" t="n">
-        <v>8003.994589995848</v>
+        <v>8399.708223905614</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6884355200096792</v>
+        <v>0.7002834505592368</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018557503066514</v>
+        <v>0.501949578501525</v>
       </c>
       <c r="H2" t="n">
-        <v>1.371779678899806</v>
+        <v>1.395127081588154</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.4978850122549</v>
+        <v>227.7398793454754</v>
       </c>
       <c r="E3" t="n">
-        <v>4468.134368127142</v>
+        <v>4658.695098916818</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2818865051403274</v>
+        <v>0.2922756568949061</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6027336518849628</v>
+        <v>0.6028787530804023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4676800511449261</v>
+        <v>0.4848000620382239</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908265200897388</v>
+        <v>0.8908754259299894</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069891340931289</v>
+        <v>1.070007604225954</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.09496347763527</v>
+        <v>39.17916567553819</v>
       </c>
       <c r="E4" t="n">
-        <v>1853.698893099261</v>
+        <v>1775.212103869934</v>
       </c>
       <c r="F4" t="n">
-        <v>0.910638888025272</v>
+        <v>0.9152473645953407</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117277139466659</v>
+        <v>1.117300228872219</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8150519292464646</v>
+        <v>0.8191597396513322</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.471586499137125</v>
+        <v>0.4716505009634219</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049888965992864</v>
+        <v>1.049856868586905</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.42219968385646</v>
+        <v>37.47180536686911</v>
       </c>
       <c r="E5" t="n">
-        <v>293.7315632147324</v>
+        <v>294.3823430877821</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3316094596880412</v>
+        <v>-0.3304731030185331</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663756174058356</v>
+        <v>0.5664042812569227</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5854938833823896</v>
+        <v>-0.5834579892037035</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7368195603170182</v>
+        <v>0.7369197768442601</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8315469796575057</v>
+        <v>0.8315467019487034</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.07180572898323</v>
+        <v>11.11952730690186</v>
       </c>
       <c r="E6" t="n">
-        <v>180.7125948603268</v>
+        <v>179.4701365724265</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2910141827973038</v>
+        <v>-0.285443947716455</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7194932174782499</v>
+        <v>0.7197370614328482</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4044710578610856</v>
+        <v>-0.3965947607980543</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499918427640597</v>
+        <v>0.7501737292512299</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075237344003793</v>
+        <v>1.075661497848555</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.14721019673282</v>
+        <v>10.19342394651462</v>
       </c>
       <c r="E7" t="n">
-        <v>289.5383887362599</v>
+        <v>293.298329620725</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5400886559947164</v>
+        <v>-0.5363986294126697</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8101677931795085</v>
+        <v>0.8104531515697017</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6666380230632659</v>
+        <v>-0.6618502604052587</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6834304878206696</v>
+        <v>0.6836852025239736</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103291871759845</v>
+        <v>1.103885431523359</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.08909081938826</v>
+        <v>10.12660246245216</v>
       </c>
       <c r="E8" t="n">
-        <v>381.2325441538234</v>
+        <v>379.1620101068255</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3084899234446885</v>
+        <v>-0.3027480241551204</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17693886537381</v>
+        <v>1.177066236842618</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2621121049874655</v>
+        <v>-0.257205596999551</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385855332746674</v>
+        <v>0.7386751683090027</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732111306849911</v>
+        <v>1.732185139404242</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.485704389441723</v>
+        <v>7.514031062313351</v>
       </c>
       <c r="E9" t="n">
-        <v>268.6430353706726</v>
+        <v>267.4328046289812</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4631366645412711</v>
+        <v>0.4718448130415844</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4834378772907187</v>
+        <v>0.4833721705446919</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9580065739506809</v>
+        <v>0.9761522110589905</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6778308852670237</v>
+        <v>0.6778027435954596</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6529548065063501</v>
+        <v>0.6527169209922729</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.055250689731877</v>
+        <v>7.097491945687596</v>
       </c>
       <c r="E10" t="n">
-        <v>208.6510911796404</v>
+        <v>210.782166020025</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2176056174568938</v>
+        <v>-0.2091753019833875</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9654079728962262</v>
+        <v>0.9655832924196207</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2254027556910229</v>
+        <v>-0.2166310287528097</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7131905590399955</v>
+        <v>0.7133039692051877</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371947718982633</v>
+        <v>1.37215852862607</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.809238763649872</v>
+        <v>6.827101105007863</v>
       </c>
       <c r="E11" t="n">
-        <v>365.7521404107065</v>
+        <v>366.6528730011179</v>
       </c>
       <c r="F11" t="n">
-        <v>1.048574023635426</v>
+        <v>1.060773694087836</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272187246904937</v>
+        <v>0.8272524141341449</v>
       </c>
       <c r="H11" t="n">
-        <v>1.267589807070376</v>
+        <v>1.282285401606364</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626655027919898</v>
+        <v>0.6626899757392506</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092284609234872</v>
+        <v>1.092165240758594</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.543495773248661</v>
+        <v>6.568253355630008</v>
       </c>
       <c r="E12" t="n">
-        <v>106.157787199591</v>
+        <v>106.688513148708</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2413643611853407</v>
+        <v>-0.237310601641775</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6634117151971058</v>
+        <v>0.6635863186901747</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3638228805073619</v>
+        <v>-0.3576182856062983</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7880417483246298</v>
+        <v>0.7882468826912529</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041725889528061</v>
+        <v>1.04207647442522</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.86743360074379</v>
+        <v>4.867309993923398</v>
       </c>
       <c r="E13" t="n">
-        <v>284.116587189754</v>
+        <v>288.1530757669352</v>
       </c>
       <c r="F13" t="n">
-        <v>1.909277296743646</v>
+        <v>1.917304191205106</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8667701433096108</v>
+        <v>0.8669021308755152</v>
       </c>
       <c r="H13" t="n">
-        <v>2.202749265743515</v>
+        <v>2.211673178457587</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6017598478504416</v>
+        <v>0.602244486593293</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039317511537107</v>
+        <v>1.040118472246451</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.710207132702939</v>
+        <v>4.727362434518905</v>
       </c>
       <c r="E14" t="n">
-        <v>99.39742673171394</v>
+        <v>100.274130848325</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3810208256140726</v>
+        <v>-0.3778865613499561</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8572141677790761</v>
+        <v>0.857261551131053</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4444873170974823</v>
+        <v>-0.440806613630788</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601593333700285</v>
+        <v>0.7601850066721901</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298419615469433</v>
+        <v>1.298292509601922</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.326039828770958</v>
+        <v>4.32235322566094</v>
       </c>
       <c r="E15" t="n">
-        <v>232.2778170586694</v>
+        <v>236.8246578440896</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02833250176928681</v>
+        <v>0.0302761584592246</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7967389246881408</v>
+        <v>0.7967798373681424</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03556058439140112</v>
+        <v>0.03799814834575924</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166975516015746</v>
+        <v>0.7168578770722314</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137818658530361</v>
+        <v>1.137918881045438</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.258580604244105</v>
+        <v>4.313668166429906</v>
       </c>
       <c r="E16" t="n">
-        <v>214.5130743897528</v>
+        <v>218.3586264977698</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5892561748210845</v>
+        <v>0.620248082149657</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624276923900187</v>
+        <v>0.9625474792324079</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6122602035252863</v>
+        <v>0.6443818050869339</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5129788484105655</v>
+        <v>0.5131747007212334</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9837588769661374</v>
+        <v>0.9840729741415012</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.568103454252245</v>
+        <v>3.565820708254259</v>
       </c>
       <c r="E17" t="n">
-        <v>78.08012737744129</v>
+        <v>79.05056241534524</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1542306208162745</v>
+        <v>-0.1525289760598252</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7572735597123128</v>
+        <v>0.7573518447769381</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2036656619503083</v>
+        <v>-0.2013977745109334</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7223495709382456</v>
+        <v>0.7227078601672378</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089986974557571</v>
+        <v>1.090436479230529</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.229418976648006</v>
+        <v>3.233269708967912</v>
       </c>
       <c r="E18" t="n">
-        <v>55.12691939702714</v>
+        <v>55.37661098272531</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4483684930672933</v>
+        <v>-0.4460789025488614</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519653101814544</v>
+        <v>0.7519971254257735</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5962622038496682</v>
+        <v>-0.5931922975055202</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642165125545283</v>
+        <v>0.7642223552281561</v>
       </c>
       <c r="N18" t="n">
-        <v>1.145078653692251</v>
+        <v>1.144921798785695</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.03310666143638</v>
+        <v>3.023198106773275</v>
       </c>
       <c r="E19" t="n">
-        <v>99.24277018807952</v>
+        <v>97.62295323899806</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1511772638030207</v>
+        <v>0.1406645630379924</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4856205332287487</v>
+        <v>0.4852996219144791</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3113073963283375</v>
+        <v>0.2898509635822067</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7169587612888031</v>
+        <v>0.7175259959013942</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6937648831309552</v>
+        <v>0.6937252454007168</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.663794345678751</v>
+        <v>2.671431728730739</v>
       </c>
       <c r="E20" t="n">
-        <v>114.2796471721575</v>
+        <v>114.8471269235526</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2998730725984257</v>
+        <v>-0.2967804169958741</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7846490079849733</v>
+        <v>0.7847321903864022</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3821747935022796</v>
+        <v>-0.3781932494061948</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320912953031552</v>
+        <v>0.7322139971450775</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144621155108923</v>
+        <v>1.144720343279447</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>585.4508999108632</v>
+        <v>586.7638490631167</v>
       </c>
       <c r="E2" t="n">
-        <v>8399.708223905614</v>
+        <v>9109.513099770153</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7002834505592368</v>
+        <v>0.7063789420628632</v>
       </c>
       <c r="G2" t="n">
-        <v>0.501949578501525</v>
+        <v>0.5020253589405991</v>
       </c>
       <c r="H2" t="n">
-        <v>1.395127081588154</v>
+        <v>1.407058287958804</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.7398793454754</v>
+        <v>227.7126745687301</v>
       </c>
       <c r="E3" t="n">
-        <v>4658.695098916818</v>
+        <v>4907.024685732455</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2922756568949061</v>
+        <v>0.293111915550095</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6028787530804023</v>
+        <v>0.6028938595867059</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4848000620382239</v>
+        <v>0.4861749889956222</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908754259299894</v>
+        <v>0.8909074088851647</v>
       </c>
       <c r="N3" t="n">
-        <v>1.070007604225954</v>
+        <v>1.069911303705122</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.17916567553819</v>
+        <v>39.20063199919401</v>
       </c>
       <c r="E4" t="n">
-        <v>1775.212103869934</v>
+        <v>1723.488702205616</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9152473645953407</v>
+        <v>0.9202137391107457</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117300228872219</v>
+        <v>1.11732936959544</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8191597396513322</v>
+        <v>0.8235832370932258</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716505009634219</v>
+        <v>0.4716961941905232</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049856868586905</v>
+        <v>1.049827467695364</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.47180536686911</v>
+        <v>37.40596697814901</v>
       </c>
       <c r="E5" t="n">
-        <v>294.3823430877821</v>
+        <v>297.7732469315052</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3304731030185331</v>
+        <v>-0.3319881276959685</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5664042812569227</v>
+        <v>0.5663668877337831</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5834579892037035</v>
+        <v>-0.5861714992279303</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7369197768442601</v>
+        <v>0.7368908985379748</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8315467019487034</v>
+        <v>0.8313337112790861</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.11952730690186</v>
+        <v>11.11611141475382</v>
       </c>
       <c r="E6" t="n">
-        <v>179.4701365724265</v>
+        <v>181.7421683076794</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.285443947716455</v>
+        <v>-0.285753718377775</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7197370614328482</v>
+        <v>0.7197218472117261</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3965947607980543</v>
+        <v>-0.3970335477307147</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7501737292512299</v>
+        <v>0.7503105569886511</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075661497848555</v>
+        <v>1.075672554067586</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.19342394651462</v>
+        <v>10.17103908114133</v>
       </c>
       <c r="E7" t="n">
-        <v>293.298329620725</v>
+        <v>294.5277948595956</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5363986294126697</v>
+        <v>-0.5377174233198245</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8104531515697017</v>
+        <v>0.8103444134009277</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6618502604052587</v>
+        <v>-0.6635665211327647</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6836852025239736</v>
+        <v>0.6838657416295245</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103885431523359</v>
+        <v>1.10386213241339</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.12660246245216</v>
+        <v>10.12752345918806</v>
       </c>
       <c r="E8" t="n">
-        <v>379.1620101068255</v>
+        <v>384.5234615791809</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3027480241551204</v>
+        <v>-0.3023647686763025</v>
       </c>
       <c r="G8" t="n">
-        <v>1.177066236842618</v>
+        <v>1.17707626346606</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.257205596999551</v>
+        <v>-0.2568778065288214</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7386751683090027</v>
+        <v>0.7386961712182561</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732185139404242</v>
+        <v>1.731987664705103</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.514031062313351</v>
+        <v>7.505102825580612</v>
       </c>
       <c r="E9" t="n">
-        <v>267.4328046289812</v>
+        <v>262.0081552332526</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4718448130415844</v>
+        <v>0.4691824881081554</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833721705446919</v>
+        <v>0.4833867589853317</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9761522110589905</v>
+        <v>0.9706151014417685</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6778027435954596</v>
+        <v>0.6775435432557153</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6527169209922729</v>
+        <v>0.6523885130762301</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.097491945687596</v>
+        <v>7.12092486514227</v>
       </c>
       <c r="E10" t="n">
-        <v>210.782166020025</v>
+        <v>213.5311883904425</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2091753019833875</v>
+        <v>-0.2043059309726301</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9655832924196207</v>
+        <v>0.9657242626325556</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2166310287528097</v>
+        <v>-0.2115572103528744</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7133039692051877</v>
+        <v>0.7133901962450638</v>
       </c>
       <c r="N10" t="n">
-        <v>1.37215852862607</v>
+        <v>1.372317571151969</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.827101105007863</v>
+        <v>6.837615103010151</v>
       </c>
       <c r="E11" t="n">
-        <v>366.6528730011179</v>
+        <v>379.2798058681865</v>
       </c>
       <c r="F11" t="n">
-        <v>1.060773694087836</v>
+        <v>1.063216008144528</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272524141341449</v>
+        <v>0.8272628696953073</v>
       </c>
       <c r="H11" t="n">
-        <v>1.282285401606364</v>
+        <v>1.285221478072774</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626899757392506</v>
+        <v>0.6626748808296338</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092165240758594</v>
+        <v>1.091989306570037</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.568253355630008</v>
+        <v>6.593853779965643</v>
       </c>
       <c r="E12" t="n">
-        <v>106.688513148708</v>
+        <v>109.9711098397918</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.237310601641775</v>
+        <v>-0.2330574655455293</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6635863186901747</v>
+        <v>0.66380346781157</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3576182856062983</v>
+        <v>-0.3510940765553306</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7882468826912529</v>
+        <v>0.7883245212427712</v>
       </c>
       <c r="N12" t="n">
-        <v>1.04207647442522</v>
+        <v>1.042362784354415</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.867309993923398</v>
+        <v>4.884072300521472</v>
       </c>
       <c r="E13" t="n">
-        <v>288.1530757669352</v>
+        <v>293.9862892073856</v>
       </c>
       <c r="F13" t="n">
-        <v>1.917304191205106</v>
+        <v>1.931767855982409</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8669021308755152</v>
+        <v>0.8671568787549259</v>
       </c>
       <c r="H13" t="n">
-        <v>2.211673178457587</v>
+        <v>2.227702856668869</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.602244486593293</v>
+        <v>0.6024565664723467</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040118472246451</v>
+        <v>1.040633399217158</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.727362434518905</v>
+        <v>4.736980837380441</v>
       </c>
       <c r="E14" t="n">
-        <v>100.274130848325</v>
+        <v>103.0086142183303</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3778865613499561</v>
+        <v>-0.3760039226979185</v>
       </c>
       <c r="G14" t="n">
-        <v>0.857261551131053</v>
+        <v>0.8573003674058209</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.440806613630788</v>
+        <v>-0.4385906468647636</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601850066721901</v>
+        <v>0.7602020721701309</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298292509601922</v>
+        <v>1.298184452573108</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.32235322566094</v>
+        <v>4.325831109148832</v>
       </c>
       <c r="E15" t="n">
-        <v>236.8246578440896</v>
+        <v>219.905579539402</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0302761584592246</v>
+        <v>0.6315584224471067</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7967798373681424</v>
+        <v>0.9626609801005773</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03799814834575924</v>
+        <v>0.6560548682269457</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J15" t="n">
         <v>265</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7168578770722314</v>
+        <v>0.5133062574349485</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137918881045438</v>
+        <v>0.9842927176365097</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.313668166429906</v>
+        <v>4.321852755148798</v>
       </c>
       <c r="E16" t="n">
-        <v>218.3586264977698</v>
+        <v>236.9116370468482</v>
       </c>
       <c r="F16" t="n">
-        <v>0.620248082149657</v>
+        <v>0.02797921769882605</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9625474792324079</v>
+        <v>0.7967318426758291</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6443818050869339</v>
+        <v>0.0351174839515108</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J16" t="n">
         <v>265</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5131747007212334</v>
+        <v>0.7168856565550873</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9840729741415012</v>
+        <v>1.137722666720085</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.565820708254259</v>
+        <v>3.576060662072615</v>
       </c>
       <c r="E17" t="n">
-        <v>79.05056241534524</v>
+        <v>81.55668640347463</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1525289760598252</v>
+        <v>-0.149312203428501</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7573518447769381</v>
+        <v>0.7575107332356709</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2013977745109334</v>
+        <v>-0.197109026813021</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7227078601672378</v>
+        <v>0.7228484981247867</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090436479230529</v>
+        <v>1.090712821735366</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.233269708967912</v>
+        <v>3.232825093353267</v>
       </c>
       <c r="E18" t="n">
-        <v>55.37661098272531</v>
+        <v>55.79243280882331</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4460789025488614</v>
+        <v>-0.4461607183653843</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519971254257735</v>
+        <v>0.751995705081805</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5931922975055202</v>
+        <v>-0.5933022161567388</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642223552281561</v>
+        <v>0.7641732549118829</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144921798785695</v>
+        <v>1.144673262810443</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.023198106773275</v>
+        <v>3.01147179582652</v>
       </c>
       <c r="E19" t="n">
-        <v>97.62295323899806</v>
+        <v>99.35622655119573</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1406645630379924</v>
+        <v>0.1387560044208436</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4852996219144791</v>
+        <v>0.4852550681327761</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2898509635822067</v>
+        <v>0.2859444723674209</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7175259959013942</v>
+        <v>0.7175998477803975</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6937252454007168</v>
+        <v>0.6936282337640814</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.671431728730739</v>
+        <v>2.674545409499206</v>
       </c>
       <c r="E20" t="n">
-        <v>114.8471269235526</v>
+        <v>117.0101923142835</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2967804169958741</v>
+        <v>-0.2947165734611736</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7847321903864022</v>
+        <v>0.7847977778492154</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3781932494061948</v>
+        <v>-0.3755318653792086</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7322139971450775</v>
+        <v>0.7322804975749895</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144720343279447</v>
+        <v>1.144747166700733</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>586.7638490631167</v>
+        <v>585.4330960296212</v>
       </c>
       <c r="E2" t="n">
-        <v>9109.513099770153</v>
+        <v>9465.390790182735</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7063789420628632</v>
+        <v>0.6983658952308263</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5020253589405991</v>
+        <v>0.5019295965768076</v>
       </c>
       <c r="H2" t="n">
-        <v>1.407058287958804</v>
+        <v>1.391362254773831</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.7126745687301</v>
+        <v>227.3825117214125</v>
       </c>
       <c r="E3" t="n">
-        <v>4907.024685732455</v>
+        <v>5019.08103639304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.293111915550095</v>
+        <v>0.2884720829506524</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6028938595867059</v>
+        <v>0.6028164760468732</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4861749889956222</v>
+        <v>0.478540475274305</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909074088851647</v>
+        <v>0.8908687167543606</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069911303705122</v>
+        <v>1.069931608171435</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.20063199919401</v>
+        <v>38.79494236576664</v>
       </c>
       <c r="E4" t="n">
-        <v>1723.488702205616</v>
+        <v>1738.151948525132</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9202137391107457</v>
+        <v>0.8918820151770626</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11732936959544</v>
+        <v>1.117222572796469</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8235832370932258</v>
+        <v>0.7983028958541654</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716961941905232</v>
+        <v>0.4714933649247713</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049827467695364</v>
+        <v>1.049475930111067</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.40596697814901</v>
+        <v>37.35745631881072</v>
       </c>
       <c r="E5" t="n">
-        <v>297.7732469315052</v>
+        <v>302.071881703371</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3319881276959685</v>
+        <v>-0.3335022115831014</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663668877337831</v>
+        <v>0.5663360942730848</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5861714992279303</v>
+        <v>-0.5888768435484674</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7368908985379748</v>
+        <v>0.7368625482741772</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8313337112790861</v>
+        <v>0.831415123658385</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.11611141475382</v>
+        <v>11.08608213722319</v>
       </c>
       <c r="E6" t="n">
-        <v>181.7421683076794</v>
+        <v>180.9847717248187</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.285753718377775</v>
+        <v>-0.2891587650373231</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7197218472117261</v>
+        <v>0.7195674356544943</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3970335477307147</v>
+        <v>-0.4018508213539624</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7503105569886511</v>
+        <v>0.7501783208267911</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075672554067586</v>
+        <v>1.075457383430716</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.17103908114133</v>
+        <v>10.11323272021589</v>
       </c>
       <c r="E7" t="n">
-        <v>294.5277948595956</v>
+        <v>300.6395133436635</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5377174233198245</v>
+        <v>-0.5414922530732997</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8103444134009277</v>
+        <v>0.8100747279206941</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6635665211327647</v>
+        <v>-0.6684472856759847</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6838657416295245</v>
+        <v>0.6837107561483545</v>
       </c>
       <c r="N7" t="n">
-        <v>1.10386213241339</v>
+        <v>1.103455162916611</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.12752345918806</v>
+        <v>10.06955279496689</v>
       </c>
       <c r="E8" t="n">
-        <v>384.5234615791809</v>
+        <v>386.6663586684521</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3023647686763025</v>
+        <v>-0.3088722538846564</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17707626346606</v>
+        <v>1.17693190932304</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2568778065288214</v>
+        <v>-0.2624385076468161</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7386961712182561</v>
+        <v>0.7386211253038414</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731987664705103</v>
+        <v>1.731929691333028</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.505102825580612</v>
+        <v>7.480887271472518</v>
       </c>
       <c r="E9" t="n">
-        <v>262.0081552332526</v>
+        <v>260.3215196587723</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4691824881081554</v>
+        <v>0.4626532938295718</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4833867589853317</v>
+        <v>0.4834430443550466</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9706151014417685</v>
+        <v>0.9569964843465477</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6775435432557153</v>
+        <v>0.6775300779214614</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6523885130762301</v>
+        <v>0.6525759902312125</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.12092486514227</v>
+        <v>7.085147887969065</v>
       </c>
       <c r="E10" t="n">
-        <v>213.5311883904425</v>
+        <v>215.0595558865259</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2043059309726301</v>
+        <v>-0.2114639345317525</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9657242626325556</v>
+        <v>0.9655270565883256</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2115572103528744</v>
+        <v>-0.2190139914659222</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7133901962450638</v>
+        <v>0.713277051781847</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372317571151969</v>
+        <v>1.372081457311591</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.837615103010151</v>
+        <v>6.829341377028233</v>
       </c>
       <c r="E11" t="n">
-        <v>379.2798058681865</v>
+        <v>384.9993053820516</v>
       </c>
       <c r="F11" t="n">
-        <v>1.063216008144528</v>
+        <v>1.060773694087836</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272628696953073</v>
+        <v>0.8272524141341449</v>
       </c>
       <c r="H11" t="n">
-        <v>1.285221478072774</v>
+        <v>1.282285401606364</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626748808296338</v>
+        <v>0.6626976792534135</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091989306570037</v>
+        <v>1.092221416593812</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.593853779965643</v>
+        <v>6.591317520919583</v>
       </c>
       <c r="E12" t="n">
-        <v>109.9711098397918</v>
+        <v>111.3747628199867</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2330574655455293</v>
+        <v>-0.2342180542677315</v>
       </c>
       <c r="G12" t="n">
-        <v>0.66380346781157</v>
+        <v>0.6637407733637992</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3510940765553306</v>
+        <v>-0.3528757967974879</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7883245212427712</v>
+        <v>0.7881196852013633</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042362784354415</v>
+        <v>1.042192317262046</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.884072300521472</v>
+        <v>4.866810080551587</v>
       </c>
       <c r="E13" t="n">
-        <v>293.9862892073856</v>
+        <v>298.3553100918571</v>
       </c>
       <c r="F13" t="n">
-        <v>1.931767855982409</v>
+        <v>1.912487327388501</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8671568787549259</v>
+        <v>0.8668221203972292</v>
       </c>
       <c r="H13" t="n">
-        <v>2.227702856668869</v>
+        <v>2.206320399982509</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6024565664723467</v>
+        <v>0.6021838319662253</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040633399217158</v>
+        <v>1.039959129036965</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.736980837380441</v>
+        <v>4.7167989705284</v>
       </c>
       <c r="E14" t="n">
-        <v>103.0086142183303</v>
+        <v>104.1603016363839</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3760039226979185</v>
+        <v>-0.3797676404064466</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8573003674058209</v>
+        <v>0.8572305243620787</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4385906468647636</v>
+        <v>-0.4430169360675258</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602020721701309</v>
+        <v>0.7601572796798557</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298184452573108</v>
+        <v>1.298249849982494</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.325831109148832</v>
+        <v>4.298038847195821</v>
       </c>
       <c r="E15" t="n">
-        <v>219.905579539402</v>
+        <v>218.9455621834759</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6315584224471067</v>
+        <v>0.6230736458341817</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9626609801005773</v>
+        <v>0.9625723582299568</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6560548682269457</v>
+        <v>0.6473005800622944</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5133062574349485</v>
+        <v>0.5131821606633191</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9842927176365097</v>
+        <v>0.9841518929351383</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.321852755148798</v>
+        <v>4.28266012119688</v>
       </c>
       <c r="E16" t="n">
-        <v>236.9116370468482</v>
+        <v>239.8706116206648</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02797921769882605</v>
+        <v>0.01475512060342288</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7967318426758291</v>
+        <v>0.7965455133205728</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0351174839515108</v>
+        <v>0.01852388891365787</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7168856565550873</v>
+        <v>0.7167243860476726</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137722666720085</v>
+        <v>1.137417673489102</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.576060662072615</v>
+        <v>3.555873200206476</v>
       </c>
       <c r="E17" t="n">
-        <v>81.55668640347463</v>
+        <v>81.55677440761164</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.149312203428501</v>
+        <v>-0.1561202376823965</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7575107332356709</v>
+        <v>0.757191313957899</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.197109026813021</v>
+        <v>-0.2061833446904503</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7228484981247867</v>
+        <v>0.7227052711673302</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090712821735366</v>
+        <v>1.090244842327706</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.232825093353267</v>
+        <v>3.227504487655262</v>
       </c>
       <c r="E18" t="n">
-        <v>55.79243280882331</v>
+        <v>55.51937331443419</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4461607183653843</v>
+        <v>-0.4482867667298573</v>
       </c>
       <c r="G18" t="n">
-        <v>0.751995705081805</v>
+        <v>0.7519661623437764</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5933022161567388</v>
+        <v>-0.5961528446075397</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641732549118829</v>
+        <v>0.7641731955244749</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144673262810443</v>
+        <v>1.144846586301246</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.01147179582652</v>
+        <v>3.011794557950215</v>
       </c>
       <c r="E19" t="n">
-        <v>99.35622655119573</v>
+        <v>99.44534125416172</v>
       </c>
       <c r="F19" t="n">
         <v>0.1387560044208436</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7175998477803975</v>
+        <v>0.7174995119088015</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6936282337640814</v>
+        <v>0.693663567382922</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.674545409499206</v>
+        <v>2.665269865655668</v>
       </c>
       <c r="E20" t="n">
-        <v>117.0101923142835</v>
+        <v>118.6439302462653</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2947165734611736</v>
+        <v>-0.2983272116132374</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7847977778492154</v>
+        <v>0.7846883190667817</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3755318653792086</v>
+        <v>-0.3801856155677627</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7322804975749895</v>
+        <v>0.7321895765977342</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144747166700733</v>
+        <v>1.14466373773752</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>585.4330960296212</v>
+        <v>584.3293887397488</v>
       </c>
       <c r="E2" t="n">
-        <v>9465.390790182735</v>
+        <v>9535.881226972724</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6983658952308263</v>
+        <v>0.6936301261909572</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5019295965768076</v>
+        <v>0.5018881760754469</v>
       </c>
       <c r="H2" t="n">
-        <v>1.391362254773831</v>
+        <v>1.382041178205972</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.3825117214125</v>
+        <v>226.8098747367606</v>
       </c>
       <c r="E3" t="n">
-        <v>5019.08103639304</v>
+        <v>5037.271348854534</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2884720829506524</v>
+        <v>0.283574233274388</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6028164760468732</v>
+        <v>0.602751850696612</v>
       </c>
       <c r="H3" t="n">
-        <v>0.478540475274305</v>
+        <v>0.4704659686181897</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908687167543606</v>
+        <v>0.8908496211436537</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069931608171435</v>
+        <v>1.069882263486505</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.79494236576664</v>
+        <v>38.74878415032926</v>
       </c>
       <c r="E4" t="n">
-        <v>1738.151948525132</v>
+        <v>1702.607976489818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8918820151770626</v>
+        <v>0.8915285995971107</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117222572796469</v>
+        <v>1.117222154089103</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7983028958541654</v>
+        <v>0.7979868608352062</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4714933649247713</v>
+        <v>0.471517468251654</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049475930111067</v>
+        <v>1.049615804241546</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.35745631881072</v>
+        <v>37.29442443731321</v>
       </c>
       <c r="E5" t="n">
-        <v>302.071881703371</v>
+        <v>304.0282889349202</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3335022115831014</v>
+        <v>-0.3346371565240859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663360942730848</v>
+        <v>0.5663173311248766</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5888768435484674</v>
+        <v>-0.5909004336127164</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7368625482741772</v>
+        <v>0.7368418200762594</v>
       </c>
       <c r="N5" t="n">
-        <v>0.831415123658385</v>
+        <v>0.8314328029597864</v>
       </c>
     </row>
     <row r="6">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.08608213722319</v>
+        <v>11.09060463577539</v>
       </c>
       <c r="E6" t="n">
-        <v>180.9847717248187</v>
+        <v>179.2273409750812</v>
       </c>
       <c r="F6" t="n">
         <v>-0.2891587650373231</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7501783208267911</v>
+        <v>0.7500764668417257</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075457383430716</v>
+        <v>1.075400110061466</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.11323272021589</v>
+        <v>10.03779161654295</v>
       </c>
       <c r="E7" t="n">
-        <v>300.6395133436635</v>
+        <v>306.2055123777851</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5414922530732997</v>
+        <v>-0.5459583610547024</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8100747279206941</v>
+        <v>0.80983572508492</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6684472856759847</v>
+        <v>-0.6741593932491097</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6837107561483545</v>
+        <v>0.6836534081371687</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103455162916611</v>
+        <v>1.10312810677236</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.06955279496689</v>
+        <v>10.02891658134405</v>
       </c>
       <c r="E8" t="n">
-        <v>386.6663586684521</v>
+        <v>385.0998127264202</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3088722538846564</v>
+        <v>-0.3130740616474305</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17693190932304</v>
+        <v>1.176868061730813</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2624385076468161</v>
+        <v>-0.2660230758467471</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7386211253038414</v>
+        <v>0.7385869638934196</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731929691333028</v>
+        <v>1.731898558387692</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.480887271472518</v>
+        <v>7.468270797734267</v>
       </c>
       <c r="E9" t="n">
-        <v>260.3215196587723</v>
+        <v>257.8133306234775</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4626532938295718</v>
+        <v>0.4585464102903125</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4834430443550466</v>
+        <v>0.4834934085770315</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9569964843465477</v>
+        <v>0.9484026093341367</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6775300779214614</v>
+        <v>0.6775318953829481</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6525759902312125</v>
+        <v>0.6526995875454019</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.085147887969065</v>
+        <v>7.059869834256479</v>
       </c>
       <c r="E10" t="n">
-        <v>215.0595558865259</v>
+        <v>215.3446778900959</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2114639345317525</v>
+        <v>-0.2166067055472244</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9655270565883256</v>
+        <v>0.9654241745795313</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2190139914659222</v>
+        <v>-0.2243642859280612</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713277051781847</v>
+        <v>0.713223824286415</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372081457311591</v>
+        <v>1.371946092128418</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.829341377028233</v>
+        <v>6.825653767021842</v>
       </c>
       <c r="E11" t="n">
-        <v>384.9993053820516</v>
+        <v>384.805545029052</v>
       </c>
       <c r="F11" t="n">
-        <v>1.060773694087836</v>
+        <v>1.053756458547146</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272524141341449</v>
+        <v>0.8272292571248979</v>
       </c>
       <c r="H11" t="n">
-        <v>1.282285401606364</v>
+        <v>1.27383847883906</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626976792534135</v>
+        <v>0.6626720015372827</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092221416593812</v>
+        <v>1.092238657295543</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.591317520919583</v>
+        <v>6.539816049314431</v>
       </c>
       <c r="E12" t="n">
-        <v>111.3747628199867</v>
+        <v>112.4318775838725</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2342180542677315</v>
+        <v>-0.2432926409446743</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6637407733637992</v>
+        <v>0.6633397957275512</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3528757967974879</v>
+        <v>-0.3667692523676058</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7881196852013633</v>
+        <v>0.788206361019349</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042192317262046</v>
+        <v>1.041763228211883</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.866810080551587</v>
+        <v>4.875819179864434</v>
       </c>
       <c r="E13" t="n">
-        <v>298.3553100918571</v>
+        <v>301.4781284426566</v>
       </c>
       <c r="F13" t="n">
-        <v>1.912487327388501</v>
+        <v>1.92212323499305</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8668221203972292</v>
+        <v>0.8669845945646142</v>
       </c>
       <c r="H13" t="n">
-        <v>2.206320399982509</v>
+        <v>2.2170212101154</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6021838319662253</v>
+        <v>0.6019149376988098</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039959129036965</v>
+        <v>1.03977539838424</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.7167989705284</v>
+        <v>4.701317318272734</v>
       </c>
       <c r="E14" t="n">
-        <v>104.1603016363839</v>
+        <v>104.6804524925175</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3797676404064466</v>
+        <v>-0.3841507477623464</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8572305243620787</v>
+        <v>0.8571884254440747</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4430169360675258</v>
+        <v>-0.4481520472740091</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601572796798557</v>
+        <v>0.7601019865256314</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298249849982494</v>
+        <v>1.298198794204855</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.298038847195821</v>
+        <v>4.269961666020021</v>
       </c>
       <c r="E15" t="n">
-        <v>218.9455621834759</v>
+        <v>239.4171689794137</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6230736458341817</v>
+        <v>0.008072851566971906</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9625723582299568</v>
+        <v>0.7965100489068071</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6473005800622944</v>
+        <v>0.01013527899371982</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J15" t="n">
         <v>265</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5131821606633191</v>
+        <v>0.7166629119015838</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9841518929351383</v>
+        <v>1.137363337530819</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.28266012119688</v>
+        <v>4.269575087696866</v>
       </c>
       <c r="E16" t="n">
-        <v>239.8706116206648</v>
+        <v>217.1098868370048</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01475512060342288</v>
+        <v>0.6019148565861956</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7965455133205728</v>
+        <v>0.9624425934715461</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01852388891365787</v>
+        <v>0.6254033857906048</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J16" t="n">
         <v>265</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7167243860476726</v>
+        <v>0.5130360511879276</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137417673489102</v>
+        <v>0.9838202436063838</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.555873200206476</v>
+        <v>3.551753516090874</v>
       </c>
       <c r="E17" t="n">
-        <v>81.55677440761164</v>
+        <v>82.1644729087466</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1561202376823965</v>
+        <v>-0.1597073170027824</v>
       </c>
       <c r="G17" t="n">
-        <v>0.757191313957899</v>
+        <v>0.7570487917976103</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2061833446904503</v>
+        <v>-0.2109604014076263</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7227052711673302</v>
+        <v>0.7226329346735025</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090244842327706</v>
+        <v>1.090020479034951</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.227504487655262</v>
+        <v>3.22106448090422</v>
       </c>
       <c r="E18" t="n">
-        <v>55.51937331443419</v>
+        <v>55.91231223379731</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4482867667298573</v>
+        <v>-0.4496756631833149</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519661623437764</v>
+        <v>0.7519545377449193</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5961528446075397</v>
+        <v>-0.5980091090770908</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641731955244749</v>
+        <v>0.7641728486862329</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144846586301246</v>
+        <v>1.144922850513006</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.011794557950215</v>
+        <v>3.0090016887073</v>
       </c>
       <c r="E19" t="n">
-        <v>99.44534125416172</v>
+        <v>99.72217548329489</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1387560044208436</v>
+        <v>0.1378020535587696</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4852550681327761</v>
+        <v>0.4852343839709286</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2859444723674209</v>
+        <v>0.2839907024540652</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174995119088015</v>
+        <v>0.7174267479383334</v>
       </c>
       <c r="N19" t="n">
-        <v>0.693663567382922</v>
+        <v>0.6936208953999994</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.665269865655668</v>
+        <v>2.656405964824687</v>
       </c>
       <c r="E20" t="n">
-        <v>118.6439302462653</v>
+        <v>118.7256307585359</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2983272116132374</v>
+        <v>-0.3019327666519241</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7846883190667817</v>
+        <v>0.7846036880857606</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3801856155677627</v>
+        <v>-0.3848220078961974</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321895765977342</v>
+        <v>0.7321401607326132</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14466373773752</v>
+        <v>1.144557488479578</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>584.3293887397488</v>
+        <v>583.3516928534407</v>
       </c>
       <c r="E2" t="n">
-        <v>9535.881226972724</v>
+        <v>9780.177728290386</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6936301261909572</v>
+        <v>0.6920973714902705</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5018881760754469</v>
+        <v>0.501877191410169</v>
       </c>
       <c r="H2" t="n">
-        <v>1.382041178205972</v>
+        <v>1.379017383805833</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.8098747367606</v>
+        <v>226.3865445001242</v>
       </c>
       <c r="E3" t="n">
-        <v>5037.271348854534</v>
+        <v>5169.667603423427</v>
       </c>
       <c r="F3" t="n">
-        <v>0.283574233274388</v>
+        <v>0.2830397202107109</v>
       </c>
       <c r="G3" t="n">
-        <v>0.602751850696612</v>
+        <v>0.6027458610178742</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4704659686181897</v>
+        <v>0.4695838470507845</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908496211436537</v>
+        <v>0.8908436790061268</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069882263486505</v>
+        <v>1.069887911873731</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.74878415032926</v>
+        <v>38.70867624883576</v>
       </c>
       <c r="E4" t="n">
-        <v>1702.607976489818</v>
+        <v>1698.150293810802</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8915285995971107</v>
+        <v>0.8936493643763674</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117222154089103</v>
+        <v>1.117225005706741</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7979868608352062</v>
+        <v>0.7998830672529184</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.471517468251654</v>
+        <v>0.4715341309050868</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049615804241546</v>
+        <v>1.049678549071208</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.29442443731321</v>
+        <v>37.22926188533137</v>
       </c>
       <c r="E5" t="n">
-        <v>304.0282889349202</v>
+        <v>302.7083288160088</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3346371565240859</v>
+        <v>-0.336149591703329</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663173311248766</v>
+        <v>0.5662980902253903</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5909004336127164</v>
+        <v>-0.5935912508013921</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7368418200762594</v>
+        <v>0.7368191002930584</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8314328029597864</v>
+        <v>0.8313971156273088</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.09060463577539</v>
+        <v>11.05738883682173</v>
       </c>
       <c r="E6" t="n">
-        <v>179.2273409750812</v>
+        <v>178.9108596889148</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2891587650373231</v>
+        <v>-0.29070503877807</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7195674356544943</v>
+        <v>0.7195050965275779</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4018508213539624</v>
+        <v>-0.4040347180041518</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500764668417257</v>
+        <v>0.7500696809617244</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075400110061466</v>
+        <v>1.075320750652946</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.03779161654295</v>
+        <v>10.05086579894771</v>
       </c>
       <c r="E7" t="n">
-        <v>306.2055123777851</v>
+        <v>307.7905664335755</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5459583610547024</v>
+        <v>-0.5448210791450383</v>
       </c>
       <c r="G7" t="n">
-        <v>0.80983572508492</v>
+        <v>0.8098883111620816</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6741593932491097</v>
+        <v>-0.672711374687323</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6836534081371687</v>
+        <v>0.6836241151874175</v>
       </c>
       <c r="N7" t="n">
-        <v>1.10312810677236</v>
+        <v>1.103176612914296</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.02891658134405</v>
+        <v>9.954146820591212</v>
       </c>
       <c r="E8" t="n">
-        <v>385.0998127264202</v>
+        <v>390.3857440902569</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3130740616474305</v>
+        <v>-0.3195539303433211</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176868061730813</v>
+        <v>1.17681507890942</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2660230758467471</v>
+        <v>-0.2715413288547074</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385869638934196</v>
+        <v>0.7385286170017564</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731898558387692</v>
+        <v>1.731721679265332</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.468270797734267</v>
+        <v>7.459533992813804</v>
       </c>
       <c r="E9" t="n">
-        <v>257.8133306234775</v>
+        <v>255.9892267377442</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4585464102903125</v>
+        <v>0.4568562605178832</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4834934085770315</v>
+        <v>0.4835174980122778</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9484026093341367</v>
+        <v>0.9448598290568635</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6775318953829481</v>
+        <v>0.677522475196539</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6526995875454019</v>
+        <v>0.6527373183340852</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.059869834256479</v>
+        <v>7.039831757481432</v>
       </c>
       <c r="E10" t="n">
-        <v>215.3446778900959</v>
+        <v>217.2061942488256</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2166067055472244</v>
+        <v>-0.2170348534084335</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9654241745795313</v>
+        <v>0.9654170793645803</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2243642859280612</v>
+        <v>-0.2248094197290169</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713223824286415</v>
+        <v>0.7132144762370584</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371946092128418</v>
+        <v>1.371948055010512</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.825653767021842</v>
+        <v>6.792994975226206</v>
       </c>
       <c r="E11" t="n">
-        <v>384.805545029052</v>
+        <v>386.8092051023611</v>
       </c>
       <c r="F11" t="n">
-        <v>1.053756458547146</v>
+        <v>1.046441122901851</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272292571248979</v>
+        <v>0.8272160144105543</v>
       </c>
       <c r="H11" t="n">
-        <v>1.27383847883906</v>
+        <v>1.265015551769157</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626720015372827</v>
+        <v>0.6626381722197028</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092238657295543</v>
+        <v>1.092189318824602</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.539816049314431</v>
+        <v>6.55201232287263</v>
       </c>
       <c r="E12" t="n">
-        <v>112.4318775838725</v>
+        <v>114.2072809521594</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2432926409446743</v>
+        <v>-0.2444489631594539</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6633397957275512</v>
+        <v>0.6633001216378458</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3667692523676058</v>
+        <v>-0.3685344766044233</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.788206361019349</v>
+        <v>0.7881961478611192</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041763228211883</v>
+        <v>1.041710222538256</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.875819179864434</v>
+        <v>4.852459659792961</v>
       </c>
       <c r="E13" t="n">
-        <v>301.4781284426566</v>
+        <v>305.1303021065124</v>
       </c>
       <c r="F13" t="n">
-        <v>1.92212323499305</v>
+        <v>1.906068236182396</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8669845945646142</v>
+        <v>0.866719257036492</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2170212101154</v>
+        <v>2.199176054654274</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6019149376988098</v>
+        <v>0.6019486111698322</v>
       </c>
       <c r="N13" t="n">
-        <v>1.03977539838424</v>
+        <v>1.039538082177715</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.701317318272734</v>
+        <v>4.685569499920682</v>
       </c>
       <c r="E14" t="n">
-        <v>104.6804524925175</v>
+        <v>105.6497617865931</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3841507477623464</v>
+        <v>-0.3854014985997186</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571884254440747</v>
+        <v>0.8571841884866382</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4481520472740091</v>
+        <v>-0.4496134013859336</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601019865256314</v>
+        <v>0.7600900051070498</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298198794204855</v>
+        <v>1.298200327402426</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.269961666020021</v>
+        <v>4.270165254036151</v>
       </c>
       <c r="E15" t="n">
-        <v>239.4171689794137</v>
+        <v>215.0418882422057</v>
       </c>
       <c r="F15" t="n">
-        <v>0.008072851566971906</v>
+        <v>0.6089593316895374</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7965100489068071</v>
+        <v>0.9624712760792307</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01013527899371982</v>
+        <v>0.6327039017415912</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J15" t="n">
         <v>265</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7166629119015838</v>
+        <v>0.5130755609130202</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137363337530819</v>
+        <v>0.9839468664624712</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.269575087696866</v>
+        <v>4.245746111672176</v>
       </c>
       <c r="E16" t="n">
-        <v>217.1098868370048</v>
+        <v>249.0960165224879</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6019148565861956</v>
+        <v>0.005262886554384671</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9624425934715461</v>
+        <v>0.7965069789632533</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6254033857906048</v>
+        <v>0.006607458181012968</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J16" t="n">
         <v>265</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5130360511879276</v>
+        <v>0.7166371043353964</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9838202436063838</v>
+        <v>1.137342889369638</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.551753516090874</v>
+        <v>3.545695083670845</v>
       </c>
       <c r="E17" t="n">
-        <v>82.1644729087466</v>
+        <v>82.55334915381229</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1597073170027824</v>
+        <v>-0.1600846606791331</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7570487917976103</v>
+        <v>0.7570348374869998</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2109604014076263</v>
+        <v>-0.2114627395623416</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7226329346735025</v>
+        <v>0.7225995696964811</v>
       </c>
       <c r="N17" t="n">
-        <v>1.090020479034951</v>
+        <v>1.089973916280802</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.22106448090422</v>
+        <v>3.20934896399173</v>
       </c>
       <c r="E18" t="n">
-        <v>55.91231223379731</v>
+        <v>56.15933585788733</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4496756631833149</v>
+        <v>-0.4513900337220136</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7519545377449193</v>
+        <v>0.751948575255201</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5980091090770908</v>
+        <v>-0.6002937548871849</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641728486862329</v>
+        <v>0.7641421853281239</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144922850513006</v>
+        <v>1.14489288890652</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.0090016887073</v>
+        <v>3.003519844355152</v>
       </c>
       <c r="E19" t="n">
-        <v>99.72217548329489</v>
+        <v>99.20127110401657</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1378020535587696</v>
+        <v>0.134941515754567</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4852343839709286</v>
+        <v>0.4851787040101186</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2839907024540652</v>
+        <v>0.2781274500287069</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174267479383334</v>
+        <v>0.7174218519008473</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6936208953999994</v>
+        <v>0.6935517498927721</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.656405964824687</v>
+        <v>2.6528013389696</v>
       </c>
       <c r="E20" t="n">
-        <v>118.7256307585359</v>
+        <v>120.738696025873</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3019327666519241</v>
+        <v>-0.3024474303049676</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7846036880857606</v>
+        <v>0.7845936252028315</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3848220078961974</v>
+        <v>-0.3854829055318663</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321401607326132</v>
+        <v>0.7321295909906252</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144557488479578</v>
+        <v>1.144551335954499</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-23.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>583.3516928534407</v>
+        <v>584.5016993802383</v>
       </c>
       <c r="E2" t="n">
-        <v>9780.177728290386</v>
+        <v>9423.657374599446</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6920973714902705</v>
+        <v>0.6959486155379477</v>
       </c>
       <c r="G2" t="n">
-        <v>0.501877191410169</v>
+        <v>0.5019070429276408</v>
       </c>
       <c r="H2" t="n">
-        <v>1.379017383805833</v>
+        <v>1.386608586877873</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.3865445001242</v>
+        <v>226.8329380153764</v>
       </c>
       <c r="E3" t="n">
-        <v>5169.667603423427</v>
+        <v>4646.04599142772</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2830397202107109</v>
+        <v>0.2862852465684882</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6027458610178742</v>
+        <v>0.6027854527534379</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4695838470507845</v>
+        <v>0.4749372189736465</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908436790061268</v>
+        <v>0.8908581650593422</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069887911873731</v>
+        <v>1.069911948698856</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.70867624883576</v>
+        <v>38.7672604150323</v>
       </c>
       <c r="E4" t="n">
-        <v>1698.150293810802</v>
+        <v>1584.577967957136</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8936493643763674</v>
+        <v>0.8915285995971107</v>
       </c>
       <c r="G4" t="n">
-        <v>1.117225005706741</v>
+        <v>1.117222154089103</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7998830672529184</v>
+        <v>0.7979868608352062</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4715341309050868</v>
+        <v>0.4715057054661659</v>
       </c>
       <c r="N4" t="n">
-        <v>1.049678549071208</v>
+        <v>1.049550165412117</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.22926188533137</v>
+        <v>37.30634116957278</v>
       </c>
       <c r="E5" t="n">
-        <v>302.7083288160088</v>
+        <v>286.9934915111369</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.336149591703329</v>
+        <v>-0.3338805854433086</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5662980902253903</v>
+        <v>0.5663294272989022</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5935912508013921</v>
+        <v>-0.5895518921482605</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7368191002930584</v>
+        <v>0.7368550746372399</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8313971156273088</v>
+        <v>0.8314342631804029</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.05738883682173</v>
+        <v>11.09771103843281</v>
       </c>
       <c r="E6" t="n">
-        <v>178.9108596889148</v>
+        <v>172.1765349092254</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.29070503877807</v>
+        <v>-0.2876115692212508</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7195050965275779</v>
+        <v>0.7196346802987578</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4040347180041518</v>
+        <v>-0.399663297357832</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500696809617244</v>
+        <v>0.7501036092076443</v>
       </c>
       <c r="N6" t="n">
-        <v>1.075320750652946</v>
+        <v>1.075499096116309</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.05086579894771</v>
+        <v>10.10124791777361</v>
       </c>
       <c r="E7" t="n">
-        <v>307.7905664335755</v>
+        <v>290.7068237043719</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5448210791450383</v>
+        <v>-0.5422812596489273</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8098883111620816</v>
+        <v>0.8100261733048931</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.672711374687323</v>
+        <v>-0.6694614044833007</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6836241151874175</v>
+        <v>0.6836693123333961</v>
       </c>
       <c r="N7" t="n">
-        <v>1.103176612914296</v>
+        <v>1.103371719283182</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.954146820591212</v>
+        <v>10.02846425703456</v>
       </c>
       <c r="E8" t="n">
-        <v>390.3857440902569</v>
+        <v>342.0238359410183</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3195539303433211</v>
+        <v>-0.312692369320084</v>
       </c>
       <c r="G8" t="n">
-        <v>1.17681507890942</v>
+        <v>1.176872906234279</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2715413288547074</v>
+        <v>-0.265697653216121</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7385286170017564</v>
+        <v>0.7385863972355674</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731721679265332</v>
+        <v>1.731839256029412</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.459533992813804</v>
+        <v>7.476807805475005</v>
       </c>
       <c r="E9" t="n">
-        <v>255.9892267377442</v>
+        <v>248.3659484197574</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4568562605178832</v>
+        <v>0.4626532938295718</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4835174980122778</v>
+        <v>0.4834430443550466</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9448598290568635</v>
+        <v>0.9569964843465477</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.677522475196539</v>
+        <v>0.6776063144100596</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6527373183340852</v>
+        <v>0.6526787462510851</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.039831757481432</v>
+        <v>7.064515019328153</v>
       </c>
       <c r="E10" t="n">
-        <v>217.2061942488256</v>
+        <v>204.9174063236555</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2170348534084335</v>
+        <v>-0.2136078761012444</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9654170793645803</v>
+        <v>0.9654802093559696</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2248094197290169</v>
+        <v>-0.2212452145898807</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132144762370584</v>
+        <v>0.7132502578504618</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371948055010512</v>
+        <v>1.372024995417213</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.792994975226206</v>
+        <v>6.837353219708206</v>
       </c>
       <c r="E11" t="n">
-        <v>386.8092051023611</v>
+        <v>364.667051075465</v>
       </c>
       <c r="F11" t="n">
-        <v>1.046441122901851</v>
+        <v>1.065353682917257</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8272160144105543</v>
+        <v>0.8272730347848479</v>
       </c>
       <c r="H11" t="n">
-        <v>1.265015551769157</v>
+        <v>1.287789687469178</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626381722197028</v>
+        <v>0.6627271310231714</v>
       </c>
       <c r="N11" t="n">
-        <v>1.092189318824602</v>
+        <v>1.092346267384089</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.55201232287263</v>
+        <v>6.561866319949352</v>
       </c>
       <c r="E12" t="n">
-        <v>114.2072809521594</v>
+        <v>111.4934085892861</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2444489631594539</v>
+        <v>-0.2429070925665769</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6633001216378458</v>
+        <v>0.6633536000712896</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3685344766044233</v>
+        <v>-0.3661804089711311</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7881961478611192</v>
+        <v>0.7882442284563528</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041710222538256</v>
+        <v>1.041795794758994</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.852459659792961</v>
+        <v>4.861867195332834</v>
       </c>
       <c r="E13" t="n">
-        <v>305.1303021065124</v>
+        <v>297.1570391813451</v>
       </c>
       <c r="F13" t="n">
-        <v>1.906068236182396</v>
+        <v>1.915698327633483</v>
       </c>
       <c r="G13" t="n">
-        <v>0.866719257036492</v>
+        <v>0.8668751881031341</v>
       </c>
       <c r="H13" t="n">
-        <v>2.199176054654274</v>
+        <v>2.209889444206319</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6019486111698322</v>
+        <v>0.6020626947707209</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039538082177715</v>
+        <v>1.039860307069833</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.685569499920682</v>
+        <v>4.698777541719562</v>
       </c>
       <c r="E14" t="n">
-        <v>105.6497617865931</v>
+        <v>95.35766982666122</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3854014985997186</v>
+        <v>-0.3810208256140726</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8571841884866382</v>
+        <v>0.8572141677790761</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4496134013859336</v>
+        <v>-0.4444873170974823</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600900051070498</v>
+        <v>0.7601456753490942</v>
       </c>
       <c r="N14" t="n">
-        <v>1.298200327402426</v>
+        <v>1.298263596151965</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.270165254036151</v>
+        <v>4.263039836778631</v>
       </c>
       <c r="E15" t="n">
-        <v>215.0418882422057</v>
+        <v>207.5823709372922</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6089593316895374</v>
+        <v>0.5976922394125246</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9624712760792307</v>
+        <v>0.9624323795004839</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6327039017415912</v>
+        <v>0.6210225800203598</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5130755609130202</v>
+        <v>0.5129950614435684</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9839468664624712</v>
+        <v>0.9836942210996427</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.245746111672176</v>
+        <v>4.253652471685405</v>
       </c>
       <c r="E16" t="n">
-        <v>249.0960165224879</v>
+        <v>232.6824968921851</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005262886554384671</v>
+        <v>0.007370158872505916</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7965069789632533</v>
+        <v>0.7965086223778127</v>
       </c>
       <c r="H16" t="n">
-        <v>0.006607458181012968</v>
+        <v>0.009253081090953947</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7166371043353964</v>
+        <v>0.7166308666714657</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137342889369638</v>
+        <v>1.137267692113655</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.545695083670845</v>
+        <v>3.557757166153</v>
       </c>
       <c r="E17" t="n">
-        <v>82.55334915381229</v>
+        <v>78.81250705817311</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1600846606791331</v>
+        <v>-0.1529072003106685</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7570348374869998</v>
+        <v>0.7573340990728453</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2114627395623416</v>
+        <v>-0.2019019089433089</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7225995696964811</v>
+        <v>0.7225777102884606</v>
       </c>
       <c r="N17" t="n">
-        <v>1.089973916280802</v>
+        <v>1.090306954131194</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.20934896399173</v>
+        <v>3.221225731828402</v>
       </c>
       <c r="E18" t="n">
-        <v>56.15933585788733</v>
+        <v>53.92842680237986</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4513900337220136</v>
+        <v>-0.4486136521758401</v>
       </c>
       <c r="G18" t="n">
-        <v>0.751948575255201</v>
+        <v>0.7519628799646498</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6002937548871849</v>
+        <v>-0.5965901564142764</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641421853281239</v>
+        <v>0.7641826517283129</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14489288890652</v>
+        <v>1.144907200864862</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.003519844355152</v>
+        <v>2.999939560518819</v>
       </c>
       <c r="E19" t="n">
-        <v>99.20127110401657</v>
+        <v>97.07532878744338</v>
       </c>
       <c r="F19" t="n">
-        <v>0.134941515754567</v>
+        <v>0.131130536280069</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4851787040101186</v>
+        <v>0.485119337642432</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2781274500287069</v>
+        <v>0.2703057291373564</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174218519008473</v>
+        <v>0.717455743772754</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935517498927721</v>
+        <v>0.69345840053688</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.6528013389696</v>
+        <v>2.659855989125887</v>
       </c>
       <c r="E20" t="n">
-        <v>120.738696025873</v>
+        <v>115.6511107256038</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3024474303049676</v>
+        <v>-0.2998730725984257</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7845936252028315</v>
+        <v>0.7846490079849733</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3854829055318663</v>
+        <v>-0.3821747935022796</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321295909906252</v>
+        <v>0.7321640942728911</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144551335954499</v>
+        <v>1.144617989224479</v>
       </c>
     </row>
   </sheetData>
